--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="291">
   <si>
     <t>Id</t>
   </si>
@@ -928,6 +928,15 @@
   </si>
   <si>
     <t>WJBeta143</t>
+  </si>
+  <si>
+    <t>湖光月色</t>
+  </si>
+  <si>
+    <t>WJBeta144</t>
+  </si>
+  <si>
+    <t>无尽王国</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2002,7 +2011,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I150"/>
+  <dimension ref="C3:I151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4614,40 +4623,59 @@
       <c r="F148" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G148" s="12"/>
+      <c r="G148" s="12" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="149" spans="3:7">
       <c r="C149" s="3">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E149" s="5">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G149" s="2" t="s">
         <v>285</v>
+      </c>
+      <c r="G149" s="12" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="150" spans="3:7">
       <c r="C150" s="3">
+        <v>202</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="5">
+        <v>202</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="151" spans="3:7">
+      <c r="C151" s="3">
         <v>203</v>
       </c>
-      <c r="D150" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" s="5">
+      <c r="D151" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="5">
         <v>203</v>
       </c>
-      <c r="F150" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>287</v>
+      <c r="F151" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="292">
   <si>
     <t>Id</t>
   </si>
@@ -937,6 +937,9 @@
   </si>
   <si>
     <t>无尽王国</t>
+  </si>
+  <si>
+    <t>WJBeta145</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1145,12 +1148,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2011,7 +2014,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I151"/>
+  <dimension ref="C3:I152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4646,36 +4649,51 @@
     </row>
     <row r="150" spans="3:7">
       <c r="C150" s="3">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E150" s="5">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G150" s="2" t="s">
-        <v>288</v>
-      </c>
+      <c r="G150" s="12"/>
     </row>
     <row r="151" spans="3:7">
       <c r="C151" s="3">
+        <v>202</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="5">
+        <v>202</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="152" spans="3:7">
+      <c r="C152" s="3">
         <v>203</v>
       </c>
-      <c r="D151" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" s="5">
+      <c r="D152" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="5">
         <v>203</v>
       </c>
-      <c r="F151" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G151" s="2" t="s">
+      <c r="F152" s="5" t="s">
         <v>290</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="293">
   <si>
     <t>Id</t>
   </si>
@@ -940,6 +940,9 @@
   </si>
   <si>
     <t>WJBeta145</t>
+  </si>
+  <si>
+    <t>一统山河</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1148,12 +1151,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4660,7 +4663,9 @@
       <c r="F150" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G150" s="12"/>
+      <c r="G150" s="12" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="151" spans="3:7">
       <c r="C151" s="3">
@@ -4673,10 +4678,10 @@
         <v>202</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="3:7">
@@ -4690,10 +4695,10 @@
         <v>203</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="294">
   <si>
     <t>Id</t>
   </si>
@@ -943,6 +943,9 @@
   </si>
   <si>
     <t>一统山河</t>
+  </si>
+  <si>
+    <t>WJBeta146</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2017,7 +2020,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I152"/>
+  <dimension ref="C3:I153"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4669,36 +4672,51 @@
     </row>
     <row r="151" spans="3:7">
       <c r="C151" s="3">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E151" s="5">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="G151" s="2" t="s">
-        <v>290</v>
-      </c>
+      <c r="G151" s="12"/>
     </row>
     <row r="152" spans="3:7">
       <c r="C152" s="3">
+        <v>202</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="5">
+        <v>202</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="153" spans="3:7">
+      <c r="C153" s="3">
         <v>203</v>
       </c>
-      <c r="D152" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E152" s="5">
+      <c r="D153" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="5">
         <v>203</v>
       </c>
-      <c r="F152" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G152" s="2" t="s">
+      <c r="F153" s="5" t="s">
         <v>292</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="295">
   <si>
     <t>Id</t>
   </si>
@@ -946,6 +946,9 @@
   </si>
   <si>
     <t>WJBeta146</t>
+  </si>
+  <si>
+    <t>星辰坠落</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -4683,7 +4686,9 @@
       <c r="F151" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="G151" s="12"/>
+      <c r="G151" s="12" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="152" spans="3:7">
       <c r="C152" s="3">
@@ -4696,10 +4701,10 @@
         <v>202</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="153" spans="3:7">
@@ -4713,10 +4718,10 @@
         <v>203</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="296">
   <si>
     <t>Id</t>
   </si>
@@ -949,6 +949,9 @@
   </si>
   <si>
     <t>星辰坠落</t>
+  </si>
+  <si>
+    <t>WJBeta147</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2023,7 +2026,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I153"/>
+  <dimension ref="C3:I154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4692,36 +4695,53 @@
     </row>
     <row r="152" spans="3:7">
       <c r="C152" s="3">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E152" s="5">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="G152" s="2" t="s">
-        <v>292</v>
+      <c r="G152" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="153" spans="3:7">
       <c r="C153" s="3">
+        <v>202</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="5">
+        <v>202</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="154" spans="3:7">
+      <c r="C154" s="3">
         <v>203</v>
       </c>
-      <c r="D153" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="5">
+      <c r="D154" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="5">
         <v>203</v>
       </c>
-      <c r="F153" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G153" s="2" t="s">
+      <c r="F154" s="5" t="s">
         <v>294</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="297">
   <si>
     <t>Id</t>
   </si>
@@ -952,6 +952,9 @@
   </si>
   <si>
     <t>WJBeta147</t>
+  </si>
+  <si>
+    <t>WJBeta148</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2026,7 +2029,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I154"/>
+  <dimension ref="C3:I155"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4712,36 +4715,51 @@
     </row>
     <row r="153" spans="3:7">
       <c r="C153" s="3">
-        <v>202</v>
+        <v>148</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E153" s="5">
-        <v>202</v>
+        <v>148</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G153" s="2" t="s">
-        <v>293</v>
-      </c>
+      <c r="G153" s="12"/>
     </row>
     <row r="154" spans="3:7">
       <c r="C154" s="3">
+        <v>202</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="5">
+        <v>202</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="155" spans="3:7">
+      <c r="C155" s="3">
         <v>203</v>
       </c>
-      <c r="D154" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="5">
+      <c r="D155" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="5">
         <v>203</v>
       </c>
-      <c r="F154" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G154" s="2" t="s">
+      <c r="F155" s="5" t="s">
         <v>295</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="298">
   <si>
     <t>Id</t>
   </si>
@@ -955,6 +955,9 @@
   </si>
   <si>
     <t>WJBeta148</t>
+  </si>
+  <si>
+    <t>威震天下</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -4504,7 +4507,7 @@
       <c r="G140" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="H140" s="10"/>
+      <c r="H140" s="11"/>
     </row>
     <row r="141" spans="3:8">
       <c r="C141" s="3">
@@ -4522,7 +4525,7 @@
       <c r="G141" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="H141" s="10"/>
+      <c r="H141" s="11"/>
     </row>
     <row r="142" spans="3:8">
       <c r="C142" s="3">
@@ -4532,7 +4535,7 @@
         <v>9</v>
       </c>
       <c r="E142" s="5">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>274</v>
@@ -4540,7 +4543,7 @@
       <c r="G142" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="H142" s="8"/>
+      <c r="H142" s="11"/>
     </row>
     <row r="143" spans="3:8">
       <c r="C143" s="3">
@@ -4550,7 +4553,7 @@
         <v>9</v>
       </c>
       <c r="E143" s="5">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>276</v>
@@ -4558,9 +4561,9 @@
       <c r="G143" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="H143" s="8"/>
-    </row>
-    <row r="144" spans="3:7">
+      <c r="H143" s="11"/>
+    </row>
+    <row r="144" spans="3:8">
       <c r="C144" s="3">
         <v>139</v>
       </c>
@@ -4576,8 +4579,9 @@
       <c r="G144" s="12" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="145" spans="3:7">
+      <c r="H144" s="10"/>
+    </row>
+    <row r="145" spans="3:8">
       <c r="C145" s="3">
         <v>140</v>
       </c>
@@ -4585,7 +4589,7 @@
         <v>9</v>
       </c>
       <c r="E145" s="5">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>280</v>
@@ -4593,8 +4597,9 @@
       <c r="G145" s="12" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="146" spans="3:7">
+      <c r="H145" s="10"/>
+    </row>
+    <row r="146" spans="3:8">
       <c r="C146" s="3">
         <v>141</v>
       </c>
@@ -4610,8 +4615,9 @@
       <c r="G146" s="12" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="147" spans="3:7">
+      <c r="H146" s="6"/>
+    </row>
+    <row r="147" spans="3:8">
       <c r="C147" s="3">
         <v>142</v>
       </c>
@@ -4619,7 +4625,7 @@
         <v>9</v>
       </c>
       <c r="E147" s="5">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>282</v>
@@ -4627,6 +4633,7 @@
       <c r="G147" s="12" t="s">
         <v>36</v>
       </c>
+      <c r="H147" s="6"/>
     </row>
     <row r="148" spans="3:7">
       <c r="C148" s="3">
@@ -4726,7 +4733,9 @@
       <c r="F153" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G153" s="12"/>
+      <c r="G153" s="12" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="154" spans="3:7">
       <c r="C154" s="3">
@@ -4739,10 +4748,10 @@
         <v>202</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="155" spans="3:7">
@@ -4756,10 +4765,10 @@
         <v>203</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="300">
   <si>
     <t>Id</t>
   </si>
@@ -958,6 +958,12 @@
   </si>
   <si>
     <t>威震天下</t>
+  </si>
+  <si>
+    <t>WJBeta149</t>
+  </si>
+  <si>
+    <t>春暖花开</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1166,12 +1172,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2032,7 +2038,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I155"/>
+  <dimension ref="C3:I156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4739,36 +4745,53 @@
     </row>
     <row r="154" spans="3:7">
       <c r="C154" s="3">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E154" s="5">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G154" s="2" t="s">
+      <c r="G154" s="12" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="155" spans="3:7">
       <c r="C155" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>297</v>
+      </c>
+    </row>
+    <row r="156" spans="3:7">
+      <c r="C156" s="3">
+        <v>203</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="5">
+        <v>203</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="302">
   <si>
     <t>Id</t>
   </si>
@@ -964,6 +964,12 @@
   </si>
   <si>
     <t>春暖花开</t>
+  </si>
+  <si>
+    <t>WJBeta150</t>
+  </si>
+  <si>
+    <t>破晓之战</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1172,18 +1178,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1217,6 +1223,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1543,7 +1555,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1567,16 +1579,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1585,89 +1597,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1690,6 +1702,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2038,7 +2052,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I156"/>
+  <dimension ref="C3:I157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4261,7 +4275,7 @@
       <c r="G126" t="s">
         <v>244</v>
       </c>
-      <c r="H126" s="13"/>
+      <c r="H126" s="8"/>
     </row>
     <row r="127" spans="3:8">
       <c r="C127" s="3">
@@ -4279,7 +4293,7 @@
       <c r="G127" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H127" s="13"/>
+      <c r="H127" s="8"/>
     </row>
     <row r="128" spans="3:8">
       <c r="C128" s="3">
@@ -4297,7 +4311,7 @@
       <c r="G128" t="s">
         <v>247</v>
       </c>
-      <c r="H128" s="13"/>
+      <c r="H128" s="8"/>
     </row>
     <row r="129" spans="3:8">
       <c r="C129" s="3">
@@ -4325,7 +4339,7 @@
         <v>9</v>
       </c>
       <c r="E130" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>250</v>
@@ -4343,7 +4357,7 @@
         <v>9</v>
       </c>
       <c r="E131" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>252</v>
@@ -4361,7 +4375,7 @@
         <v>9</v>
       </c>
       <c r="E132" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>254</v>
@@ -4387,7 +4401,7 @@
       <c r="G133" t="s">
         <v>257</v>
       </c>
-      <c r="I133" s="13"/>
+      <c r="I133" s="14"/>
     </row>
     <row r="134" spans="3:8">
       <c r="C134" s="3">
@@ -4397,7 +4411,7 @@
         <v>9</v>
       </c>
       <c r="E134" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>258</v>
@@ -4415,7 +4429,7 @@
         <v>9</v>
       </c>
       <c r="E135" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>260</v>
@@ -4441,7 +4455,7 @@
       <c r="G136" t="s">
         <v>263</v>
       </c>
-      <c r="H136" s="13"/>
+      <c r="H136" s="14"/>
     </row>
     <row r="137" spans="3:8">
       <c r="C137" s="3">
@@ -4459,7 +4473,7 @@
       <c r="G137" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="H137" s="13"/>
+      <c r="H137" s="14"/>
     </row>
     <row r="138" spans="3:8">
       <c r="C138" s="3">
@@ -4477,7 +4491,7 @@
       <c r="G138" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="H138" s="13"/>
+      <c r="H138" s="14"/>
     </row>
     <row r="139" spans="3:8">
       <c r="C139" s="3">
@@ -4495,7 +4509,7 @@
       <c r="G139" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="H139" s="13"/>
+      <c r="H139" s="14"/>
     </row>
     <row r="140" spans="3:8">
       <c r="C140" s="3">
@@ -4641,7 +4655,7 @@
       </c>
       <c r="H147" s="6"/>
     </row>
-    <row r="148" spans="3:7">
+    <row r="148" spans="3:8">
       <c r="C148" s="3">
         <v>143</v>
       </c>
@@ -4657,8 +4671,9 @@
       <c r="G148" s="12" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="149" spans="3:7">
+      <c r="H148" s="8"/>
+    </row>
+    <row r="149" spans="3:8">
       <c r="C149" s="3">
         <v>144</v>
       </c>
@@ -4666,7 +4681,7 @@
         <v>9</v>
       </c>
       <c r="E149" s="5">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>285</v>
@@ -4674,8 +4689,9 @@
       <c r="G149" s="12" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="150" spans="3:7">
+      <c r="H149" s="8"/>
+    </row>
+    <row r="150" spans="3:8">
       <c r="C150" s="3">
         <v>145</v>
       </c>
@@ -4691,8 +4707,9 @@
       <c r="G150" s="12" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="151" spans="3:7">
+      <c r="H150" s="6"/>
+    </row>
+    <row r="151" spans="3:8">
       <c r="C151" s="3">
         <v>146</v>
       </c>
@@ -4700,7 +4717,7 @@
         <v>9</v>
       </c>
       <c r="E151" s="5">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>289</v>
@@ -4708,6 +4725,7 @@
       <c r="G151" s="12" t="s">
         <v>290</v>
       </c>
+      <c r="H151" s="6"/>
     </row>
     <row r="152" spans="3:7">
       <c r="C152" s="3">
@@ -4762,36 +4780,53 @@
     </row>
     <row r="155" spans="3:7">
       <c r="C155" s="3">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G155" s="2" t="s">
+      <c r="G155" s="15" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="156" spans="3:7">
       <c r="C156" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E156" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>299</v>
+      </c>
+    </row>
+    <row r="157" spans="3:7">
+      <c r="C157" s="3">
+        <v>203</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="5">
+        <v>203</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="304">
   <si>
     <t>Id</t>
   </si>
@@ -970,6 +970,12 @@
   </si>
   <si>
     <t>破晓之战</t>
+  </si>
+  <si>
+    <t>WJBeta151</t>
+  </si>
+  <si>
+    <t>龙裔国度</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -994,7 +1000,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1031,6 +1037,12 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1189,7 +1201,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1223,12 +1235,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1549,137 +1555,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1702,8 +1708,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2052,7 +2057,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I157"/>
+  <dimension ref="C3:I158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4329,7 +4334,7 @@
       <c r="G129" t="s">
         <v>249</v>
       </c>
-      <c r="H129" s="13"/>
+      <c r="H129" s="8"/>
     </row>
     <row r="130" spans="3:8">
       <c r="C130" s="3">
@@ -4401,7 +4406,7 @@
       <c r="G133" t="s">
         <v>257</v>
       </c>
-      <c r="I133" s="14"/>
+      <c r="I133" s="13"/>
     </row>
     <row r="134" spans="3:8">
       <c r="C134" s="3">
@@ -4455,7 +4460,7 @@
       <c r="G136" t="s">
         <v>263</v>
       </c>
-      <c r="H136" s="14"/>
+      <c r="H136" s="13"/>
     </row>
     <row r="137" spans="3:8">
       <c r="C137" s="3">
@@ -4473,7 +4478,7 @@
       <c r="G137" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="H137" s="14"/>
+      <c r="H137" s="13"/>
     </row>
     <row r="138" spans="3:8">
       <c r="C138" s="3">
@@ -4491,7 +4496,7 @@
       <c r="G138" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="H138" s="14"/>
+      <c r="H138" s="13"/>
     </row>
     <row r="139" spans="3:8">
       <c r="C139" s="3">
@@ -4509,7 +4514,7 @@
       <c r="G139" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="H139" s="14"/>
+      <c r="H139" s="13"/>
     </row>
     <row r="140" spans="3:8">
       <c r="C140" s="3">
@@ -4791,42 +4796,59 @@
       <c r="F155" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G155" s="15" t="s">
+      <c r="G155" s="12" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="156" spans="3:7">
       <c r="C156" s="3">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E156" s="5">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="G156" s="14" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="157" spans="3:7">
       <c r="C157" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>301</v>
+      </c>
+    </row>
+    <row r="158" spans="3:7">
+      <c r="C158" s="3">
+        <v>203</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="5">
+        <v>203</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="306">
   <si>
     <t>Id</t>
   </si>
@@ -976,6 +976,12 @@
   </si>
   <si>
     <t>龙裔国度</t>
+  </si>
+  <si>
+    <t>WJBeta152</t>
+  </si>
+  <si>
+    <t>秘境森林</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2057,7 +2063,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I158"/>
+  <dimension ref="C3:I159"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4819,36 +4825,53 @@
     </row>
     <row r="157" spans="3:7">
       <c r="C157" s="3">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G157" s="2" t="s">
+      <c r="G157" s="12" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="158" spans="3:7">
       <c r="C158" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>303</v>
+      </c>
+    </row>
+    <row r="159" spans="3:7">
+      <c r="C159" s="3">
+        <v>203</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="5">
+        <v>203</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="308">
   <si>
     <t>Id</t>
   </si>
@@ -982,6 +982,12 @@
   </si>
   <si>
     <t>秘境森林</t>
+  </si>
+  <si>
+    <t>WJBeta153</t>
+  </si>
+  <si>
+    <t>荣耀之路</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2063,7 +2069,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I159"/>
+  <dimension ref="C3:I160"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4842,36 +4848,53 @@
     </row>
     <row r="158" spans="3:7">
       <c r="C158" s="3">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="G158" s="2" t="s">
+      <c r="G158" s="12" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="159" spans="3:7">
       <c r="C159" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>305</v>
+      </c>
+    </row>
+    <row r="160" spans="3:7">
+      <c r="C160" s="3">
+        <v>203</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="5">
+        <v>203</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="310">
   <si>
     <t>Id</t>
   </si>
@@ -988,6 +988,12 @@
   </si>
   <si>
     <t>荣耀之路</t>
+  </si>
+  <si>
+    <t>WJBeta154</t>
+  </si>
+  <si>
+    <t>龙息之境</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2069,7 +2075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I160"/>
+  <dimension ref="C3:I161"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4865,36 +4871,53 @@
     </row>
     <row r="159" spans="3:7">
       <c r="C159" s="3">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G159" s="2" t="s">
+      <c r="G159" s="12" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="160" spans="3:7">
       <c r="C160" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E160" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>306</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>307</v>
+      </c>
+    </row>
+    <row r="161" spans="3:7">
+      <c r="C161" s="3">
+        <v>203</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="5">
+        <v>203</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="312">
   <si>
     <t>Id</t>
   </si>
@@ -994,6 +994,12 @@
   </si>
   <si>
     <t>龙息之境</t>
+  </si>
+  <si>
+    <t>WJBeta155</t>
+  </si>
+  <si>
+    <t>雷霆万钧</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1703,7 +1709,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1727,6 +1733,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2075,7 +2082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I161"/>
+  <dimension ref="C3:I162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4888,36 +4895,53 @@
     </row>
     <row r="160" spans="3:7">
       <c r="C160" s="3">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E160" s="5">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G160" s="2" t="s">
+      <c r="G160" s="15" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="161" spans="3:7">
       <c r="C161" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E161" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>308</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="162" spans="3:7">
+      <c r="C162" s="3">
+        <v>203</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="5">
+        <v>203</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="314">
   <si>
     <t>Id</t>
   </si>
@@ -1000,6 +1000,12 @@
   </si>
   <si>
     <t>雷霆万钧</t>
+  </si>
+  <si>
+    <t>WJBeta156</t>
+  </si>
+  <si>
+    <t>龙翔九天</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2082,7 +2088,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I162"/>
+  <dimension ref="C3:I163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4906,42 +4912,59 @@
       <c r="F160" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G160" s="15" t="s">
+      <c r="G160" s="12" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="161" spans="3:7">
       <c r="C161" s="3">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E161" s="5">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="G161" s="2" t="s">
+      <c r="G161" s="15" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="162" spans="3:7">
       <c r="C162" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E162" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>310</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>311</v>
+      </c>
+    </row>
+    <row r="163" spans="3:7">
+      <c r="C163" s="3">
+        <v>203</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="5">
+        <v>203</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="316">
   <si>
     <t>Id</t>
   </si>
@@ -1006,6 +1006,12 @@
   </si>
   <si>
     <t>龙翔九天</t>
+  </si>
+  <si>
+    <t>WJBeta157</t>
+  </si>
+  <si>
+    <t>神谕森林</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1220,12 +1226,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1738,8 +1744,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2088,7 +2094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I163"/>
+  <dimension ref="C3:I164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4663,7 +4669,7 @@
         <v>9</v>
       </c>
       <c r="E146" s="5">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>281</v>
@@ -4671,7 +4677,7 @@
       <c r="G146" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="H146" s="6"/>
+      <c r="H146" s="10"/>
     </row>
     <row r="147" spans="3:8">
       <c r="C147" s="3">
@@ -4681,7 +4687,7 @@
         <v>9</v>
       </c>
       <c r="E147" s="5">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>282</v>
@@ -4689,7 +4695,7 @@
       <c r="G147" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H147" s="6"/>
+      <c r="H147" s="10"/>
     </row>
     <row r="148" spans="3:8">
       <c r="C148" s="3">
@@ -4707,7 +4713,7 @@
       <c r="G148" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="H148" s="8"/>
+      <c r="H148" s="14"/>
     </row>
     <row r="149" spans="3:8">
       <c r="C149" s="3">
@@ -4725,7 +4731,7 @@
       <c r="G149" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="H149" s="8"/>
+      <c r="H149" s="14"/>
     </row>
     <row r="150" spans="3:8">
       <c r="C150" s="3">
@@ -4735,7 +4741,7 @@
         <v>9</v>
       </c>
       <c r="E150" s="5">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>287</v>
@@ -4743,7 +4749,7 @@
       <c r="G150" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="H150" s="6"/>
+      <c r="H150" s="14"/>
     </row>
     <row r="151" spans="3:8">
       <c r="C151" s="3">
@@ -4753,7 +4759,7 @@
         <v>9</v>
       </c>
       <c r="E151" s="5">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>289</v>
@@ -4761,9 +4767,9 @@
       <c r="G151" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="H151" s="6"/>
-    </row>
-    <row r="152" spans="3:7">
+      <c r="H151" s="14"/>
+    </row>
+    <row r="152" spans="3:8">
       <c r="C152" s="3">
         <v>147</v>
       </c>
@@ -4779,8 +4785,9 @@
       <c r="G152" s="12" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="153" spans="3:7">
+      <c r="H152" s="10"/>
+    </row>
+    <row r="153" spans="3:8">
       <c r="C153" s="3">
         <v>148</v>
       </c>
@@ -4788,7 +4795,7 @@
         <v>9</v>
       </c>
       <c r="E153" s="5">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>292</v>
@@ -4796,8 +4803,9 @@
       <c r="G153" s="12" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="154" spans="3:7">
+      <c r="H153" s="10"/>
+    </row>
+    <row r="154" spans="3:8">
       <c r="C154" s="3">
         <v>149</v>
       </c>
@@ -4813,8 +4821,9 @@
       <c r="G154" s="12" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="155" spans="3:7">
+      <c r="H154" s="8"/>
+    </row>
+    <row r="155" spans="3:8">
       <c r="C155" s="3">
         <v>150</v>
       </c>
@@ -4822,7 +4831,7 @@
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
@@ -4830,6 +4839,7 @@
       <c r="G155" s="12" t="s">
         <v>297</v>
       </c>
+      <c r="H155" s="8"/>
     </row>
     <row r="156" spans="3:7">
       <c r="C156" s="3">
@@ -4844,7 +4854,7 @@
       <c r="F156" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="G156" s="14" t="s">
+      <c r="G156" s="15" t="s">
         <v>299</v>
       </c>
     </row>
@@ -4929,42 +4939,59 @@
       <c r="F161" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="G161" s="15" t="s">
+      <c r="G161" s="12" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="162" spans="3:7">
       <c r="C162" s="3">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E162" s="5">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="G162" s="2" t="s">
+      <c r="G162" s="12" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="163" spans="3:7">
       <c r="C163" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E163" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>312</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>313</v>
+      </c>
+    </row>
+    <row r="164" spans="3:7">
+      <c r="C164" s="3">
+        <v>203</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="5">
+        <v>203</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="318">
   <si>
     <t>Id</t>
   </si>
@@ -1012,6 +1012,12 @@
   </si>
   <si>
     <t>神谕森林</t>
+  </si>
+  <si>
+    <t>WJBeta158</t>
+  </si>
+  <si>
+    <t>泰坦神殿</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1226,12 +1232,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1742,8 +1748,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2094,7 +2100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I164"/>
+  <dimension ref="C3:I165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -3741,7 +3747,7 @@
       <c r="G94" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H94" s="11"/>
+      <c r="H94" s="10"/>
     </row>
     <row r="95" spans="3:8">
       <c r="C95" s="3">
@@ -3759,7 +3765,7 @@
       <c r="G95" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="H95" s="11"/>
+      <c r="H95" s="10"/>
     </row>
     <row r="96" spans="3:8">
       <c r="C96" s="3">
@@ -3777,7 +3783,7 @@
       <c r="G96" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H96" s="11"/>
+      <c r="H96" s="10"/>
     </row>
     <row r="97" spans="3:8">
       <c r="C97" s="3">
@@ -3795,7 +3801,7 @@
       <c r="G97" t="s">
         <v>186</v>
       </c>
-      <c r="H97" s="11"/>
+      <c r="H97" s="10"/>
     </row>
     <row r="98" spans="3:8">
       <c r="C98" s="3">
@@ -3813,7 +3819,7 @@
       <c r="G98" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="H98" s="11"/>
+      <c r="H98" s="10"/>
     </row>
     <row r="99" spans="3:8">
       <c r="C99" s="3">
@@ -3831,7 +3837,7 @@
       <c r="G99" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="H99" s="11"/>
+      <c r="H99" s="10"/>
     </row>
     <row r="100" spans="3:8">
       <c r="C100" s="3">
@@ -3849,7 +3855,7 @@
       <c r="G100" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="H100" s="11"/>
+      <c r="H100" s="10"/>
     </row>
     <row r="101" spans="3:8">
       <c r="C101" s="3">
@@ -3867,7 +3873,7 @@
       <c r="G101" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="H101" s="11"/>
+      <c r="H101" s="10"/>
     </row>
     <row r="102" spans="3:8">
       <c r="C102" s="3">
@@ -3877,7 +3883,7 @@
         <v>9</v>
       </c>
       <c r="E102" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>195</v>
@@ -3895,7 +3901,7 @@
         <v>9</v>
       </c>
       <c r="E103" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>197</v>
@@ -3913,7 +3919,7 @@
         <v>9</v>
       </c>
       <c r="E104" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>199</v>
@@ -3931,7 +3937,7 @@
         <v>9</v>
       </c>
       <c r="E105" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>201</v>
@@ -3949,7 +3955,7 @@
         <v>9</v>
       </c>
       <c r="E106" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>203</v>
@@ -3967,7 +3973,7 @@
         <v>9</v>
       </c>
       <c r="E107" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>205</v>
@@ -3985,7 +3991,7 @@
         <v>9</v>
       </c>
       <c r="E108" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>207</v>
@@ -4003,7 +4009,7 @@
         <v>9</v>
       </c>
       <c r="E109" s="5">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>209</v>
@@ -4029,7 +4035,7 @@
       <c r="G110" t="s">
         <v>212</v>
       </c>
-      <c r="H110" s="11"/>
+      <c r="H110" s="12"/>
     </row>
     <row r="111" spans="3:8">
       <c r="C111" s="3">
@@ -4047,7 +4053,7 @@
       <c r="G111" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="H111" s="11"/>
+      <c r="H111" s="12"/>
     </row>
     <row r="112" spans="3:8">
       <c r="C112" s="3">
@@ -4065,7 +4071,7 @@
       <c r="G112" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="H112" s="11"/>
+      <c r="H112" s="12"/>
     </row>
     <row r="113" spans="3:8">
       <c r="C113" s="3">
@@ -4083,7 +4089,7 @@
       <c r="G113" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="H113" s="11"/>
+      <c r="H113" s="12"/>
     </row>
     <row r="114" spans="3:8">
       <c r="C114" s="3">
@@ -4101,7 +4107,7 @@
       <c r="G114" t="s">
         <v>220</v>
       </c>
-      <c r="H114" s="11"/>
+      <c r="H114" s="12"/>
     </row>
     <row r="115" spans="3:8">
       <c r="C115" s="3">
@@ -4119,7 +4125,7 @@
       <c r="G115" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="H115" s="11"/>
+      <c r="H115" s="12"/>
     </row>
     <row r="116" spans="3:8">
       <c r="C116" s="3">
@@ -4137,7 +4143,7 @@
       <c r="G116" t="s">
         <v>224</v>
       </c>
-      <c r="H116" s="11"/>
+      <c r="H116" s="12"/>
     </row>
     <row r="117" spans="3:8">
       <c r="C117" s="3">
@@ -4155,7 +4161,7 @@
       <c r="G117" t="s">
         <v>226</v>
       </c>
-      <c r="H117" s="11"/>
+      <c r="H117" s="12"/>
     </row>
     <row r="118" spans="3:8">
       <c r="C118" s="3">
@@ -4165,7 +4171,7 @@
         <v>9</v>
       </c>
       <c r="E118" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>227</v>
@@ -4173,7 +4179,7 @@
       <c r="G118" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="H118" s="10"/>
+      <c r="H118" s="12"/>
     </row>
     <row r="119" spans="3:8">
       <c r="C119" s="3">
@@ -4183,15 +4189,15 @@
         <v>9</v>
       </c>
       <c r="E119" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G119" s="12" t="s">
+      <c r="G119" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="H119" s="10"/>
+      <c r="H119" s="12"/>
     </row>
     <row r="120" spans="3:8">
       <c r="C120" s="3">
@@ -4201,7 +4207,7 @@
         <v>9</v>
       </c>
       <c r="E120" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>231</v>
@@ -4209,7 +4215,7 @@
       <c r="G120" t="s">
         <v>232</v>
       </c>
-      <c r="H120" s="10"/>
+      <c r="H120" s="12"/>
     </row>
     <row r="121" spans="3:8">
       <c r="C121" s="3">
@@ -4219,7 +4225,7 @@
         <v>9</v>
       </c>
       <c r="E121" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>233</v>
@@ -4227,7 +4233,7 @@
       <c r="G121" t="s">
         <v>234</v>
       </c>
-      <c r="H121" s="10"/>
+      <c r="H121" s="12"/>
     </row>
     <row r="122" spans="3:8">
       <c r="C122" s="3">
@@ -4237,7 +4243,7 @@
         <v>9</v>
       </c>
       <c r="E122" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>235</v>
@@ -4245,7 +4251,7 @@
       <c r="G122" t="s">
         <v>236</v>
       </c>
-      <c r="H122" s="10"/>
+      <c r="H122" s="12"/>
     </row>
     <row r="123" spans="3:8">
       <c r="C123" s="3">
@@ -4255,15 +4261,15 @@
         <v>9</v>
       </c>
       <c r="E123" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="G123" s="12" t="s">
+      <c r="G123" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="H123" s="10"/>
+      <c r="H123" s="12"/>
     </row>
     <row r="124" spans="3:8">
       <c r="C124" s="3">
@@ -4273,7 +4279,7 @@
         <v>9</v>
       </c>
       <c r="E124" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>239</v>
@@ -4281,7 +4287,7 @@
       <c r="G124" t="s">
         <v>240</v>
       </c>
-      <c r="H124" s="10"/>
+      <c r="H124" s="12"/>
     </row>
     <row r="125" spans="3:8">
       <c r="C125" s="3">
@@ -4291,7 +4297,7 @@
         <v>9</v>
       </c>
       <c r="E125" s="5">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>241</v>
@@ -4299,7 +4305,7 @@
       <c r="G125" t="s">
         <v>242</v>
       </c>
-      <c r="H125" s="10"/>
+      <c r="H125" s="12"/>
     </row>
     <row r="126" spans="3:8">
       <c r="C126" s="3">
@@ -4332,7 +4338,7 @@
       <c r="F127" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="G127" s="12" t="s">
+      <c r="G127" s="13" t="s">
         <v>106</v>
       </c>
       <c r="H127" s="8"/>
@@ -4443,7 +4449,7 @@
       <c r="G133" t="s">
         <v>257</v>
       </c>
-      <c r="I133" s="13"/>
+      <c r="I133" s="12"/>
     </row>
     <row r="134" spans="3:8">
       <c r="C134" s="3">
@@ -4458,7 +4464,7 @@
       <c r="F134" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G134" s="12" t="s">
+      <c r="G134" s="13" t="s">
         <v>259</v>
       </c>
       <c r="H134" s="8"/>
@@ -4497,7 +4503,7 @@
       <c r="G136" t="s">
         <v>263</v>
       </c>
-      <c r="H136" s="13"/>
+      <c r="H136" s="12"/>
     </row>
     <row r="137" spans="3:8">
       <c r="C137" s="3">
@@ -4512,10 +4518,10 @@
       <c r="F137" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="G137" s="12" t="s">
+      <c r="G137" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="H137" s="13"/>
+      <c r="H137" s="12"/>
     </row>
     <row r="138" spans="3:8">
       <c r="C138" s="3">
@@ -4530,10 +4536,10 @@
       <c r="F138" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="G138" s="12" t="s">
+      <c r="G138" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="H138" s="13"/>
+      <c r="H138" s="12"/>
     </row>
     <row r="139" spans="3:8">
       <c r="C139" s="3">
@@ -4548,10 +4554,10 @@
       <c r="F139" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="G139" s="12" t="s">
+      <c r="G139" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="H139" s="13"/>
+      <c r="H139" s="12"/>
     </row>
     <row r="140" spans="3:8">
       <c r="C140" s="3">
@@ -4561,15 +4567,15 @@
         <v>9</v>
       </c>
       <c r="E140" s="5">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G140" s="12" t="s">
+      <c r="G140" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="H140" s="11"/>
+      <c r="H140" s="12"/>
     </row>
     <row r="141" spans="3:8">
       <c r="C141" s="3">
@@ -4579,15 +4585,15 @@
         <v>9</v>
       </c>
       <c r="E141" s="5">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G141" s="12" t="s">
+      <c r="G141" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="H141" s="11"/>
+      <c r="H141" s="12"/>
     </row>
     <row r="142" spans="3:8">
       <c r="C142" s="3">
@@ -4597,15 +4603,15 @@
         <v>9</v>
       </c>
       <c r="E142" s="5">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G142" s="12" t="s">
+      <c r="G142" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="H142" s="11"/>
+      <c r="H142" s="12"/>
     </row>
     <row r="143" spans="3:8">
       <c r="C143" s="3">
@@ -4615,15 +4621,15 @@
         <v>9</v>
       </c>
       <c r="E143" s="5">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="G143" s="12" t="s">
+      <c r="G143" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="H143" s="11"/>
+      <c r="H143" s="12"/>
     </row>
     <row r="144" spans="3:8">
       <c r="C144" s="3">
@@ -4638,7 +4644,7 @@
       <c r="F144" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G144" s="12" t="s">
+      <c r="G144" s="13" t="s">
         <v>279</v>
       </c>
       <c r="H144" s="10"/>
@@ -4656,7 +4662,7 @@
       <c r="F145" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="G145" s="12" t="s">
+      <c r="G145" s="13" t="s">
         <v>131</v>
       </c>
       <c r="H145" s="10"/>
@@ -4674,7 +4680,7 @@
       <c r="F146" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G146" s="12" t="s">
+      <c r="G146" s="13" t="s">
         <v>150</v>
       </c>
       <c r="H146" s="10"/>
@@ -4692,7 +4698,7 @@
       <c r="F147" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G147" s="12" t="s">
+      <c r="G147" s="13" t="s">
         <v>36</v>
       </c>
       <c r="H147" s="10"/>
@@ -4710,7 +4716,7 @@
       <c r="F148" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G148" s="12" t="s">
+      <c r="G148" s="13" t="s">
         <v>284</v>
       </c>
       <c r="H148" s="14"/>
@@ -4728,7 +4734,7 @@
       <c r="F149" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="G149" s="12" t="s">
+      <c r="G149" s="13" t="s">
         <v>286</v>
       </c>
       <c r="H149" s="14"/>
@@ -4746,7 +4752,7 @@
       <c r="F150" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G150" s="12" t="s">
+      <c r="G150" s="13" t="s">
         <v>288</v>
       </c>
       <c r="H150" s="14"/>
@@ -4764,7 +4770,7 @@
       <c r="F151" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="G151" s="12" t="s">
+      <c r="G151" s="13" t="s">
         <v>290</v>
       </c>
       <c r="H151" s="14"/>
@@ -4782,7 +4788,7 @@
       <c r="F152" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="G152" s="12" t="s">
+      <c r="G152" s="13" t="s">
         <v>66</v>
       </c>
       <c r="H152" s="10"/>
@@ -4800,7 +4806,7 @@
       <c r="F153" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G153" s="12" t="s">
+      <c r="G153" s="13" t="s">
         <v>293</v>
       </c>
       <c r="H153" s="10"/>
@@ -4818,7 +4824,7 @@
       <c r="F154" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G154" s="12" t="s">
+      <c r="G154" s="13" t="s">
         <v>295</v>
       </c>
       <c r="H154" s="8"/>
@@ -4836,12 +4842,12 @@
       <c r="F155" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G155" s="12" t="s">
+      <c r="G155" s="13" t="s">
         <v>297</v>
       </c>
       <c r="H155" s="8"/>
     </row>
-    <row r="156" spans="3:7">
+    <row r="156" spans="3:8">
       <c r="C156" s="3">
         <v>151</v>
       </c>
@@ -4857,8 +4863,9 @@
       <c r="G156" s="15" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="157" spans="3:7">
+      <c r="H156" s="12"/>
+    </row>
+    <row r="157" spans="3:8">
       <c r="C157" s="3">
         <v>152</v>
       </c>
@@ -4866,14 +4873,15 @@
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G157" s="12" t="s">
+      <c r="G157" s="13" t="s">
         <v>301</v>
       </c>
+      <c r="H157" s="12"/>
     </row>
     <row r="158" spans="3:7">
       <c r="C158" s="3">
@@ -4888,7 +4896,7 @@
       <c r="F158" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="G158" s="12" t="s">
+      <c r="G158" s="13" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4905,7 +4913,7 @@
       <c r="F159" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G159" s="12" t="s">
+      <c r="G159" s="13" t="s">
         <v>305</v>
       </c>
     </row>
@@ -4922,7 +4930,7 @@
       <c r="F160" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G160" s="12" t="s">
+      <c r="G160" s="13" t="s">
         <v>307</v>
       </c>
     </row>
@@ -4939,7 +4947,7 @@
       <c r="F161" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="G161" s="12" t="s">
+      <c r="G161" s="13" t="s">
         <v>309</v>
       </c>
     </row>
@@ -4956,42 +4964,59 @@
       <c r="F162" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="G162" s="12" t="s">
+      <c r="G162" s="13" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="163" spans="3:7">
       <c r="C163" s="3">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E163" s="5">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="G163" s="2" t="s">
+      <c r="G163" s="13" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="164" spans="3:7">
       <c r="C164" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E164" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>314</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>315</v>
+      </c>
+    </row>
+    <row r="165" spans="3:7">
+      <c r="C165" s="3">
+        <v>203</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="5">
+        <v>203</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="320">
   <si>
     <t>Id</t>
   </si>
@@ -1018,6 +1018,12 @@
   </si>
   <si>
     <t>泰坦神殿</t>
+  </si>
+  <si>
+    <t>WJBeta159</t>
+  </si>
+  <si>
+    <t>星辰之巅</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1727,7 +1733,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1752,6 +1758,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1811,6 +1818,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2100,7 +2114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I165"/>
+  <dimension ref="C3:I166"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4987,36 +5001,53 @@
     </row>
     <row r="164" spans="3:7">
       <c r="C164" s="3">
-        <v>202</v>
+        <v>159</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E164" s="5">
-        <v>202</v>
+        <v>159</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G164" s="2" t="s">
+      <c r="G164" s="16" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="165" spans="3:7">
       <c r="C165" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E165" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>316</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>317</v>
+      </c>
+    </row>
+    <row r="166" spans="3:7">
+      <c r="C166" s="3">
+        <v>203</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="5">
+        <v>203</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="322">
   <si>
     <t>Id</t>
   </si>
@@ -1024,6 +1024,12 @@
   </si>
   <si>
     <t>星辰之巅</t>
+  </si>
+  <si>
+    <t>WJBeta160</t>
+  </si>
+  <si>
+    <t>微风草原</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1733,7 +1739,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1756,9 +1762,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2114,7 +2119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I166"/>
+  <dimension ref="C3:I167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -2125,7 +2130,8 @@
     <col min="6" max="6" width="21" style="3" customWidth="1"/>
     <col min="7" max="7" width="9" style="2"/>
     <col min="8" max="8" width="23.75" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="16.375" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:6">
@@ -3656,7 +3662,7 @@
       </c>
       <c r="H88" s="6"/>
     </row>
-    <row r="89" spans="3:7">
+    <row r="89" spans="3:9">
       <c r="C89" s="3">
         <v>84</v>
       </c>
@@ -3672,6 +3678,7 @@
       <c r="G89" s="2" t="s">
         <v>170</v>
       </c>
+      <c r="I89" s="6"/>
     </row>
     <row r="90" spans="3:8">
       <c r="C90" s="3">
@@ -3681,7 +3688,7 @@
         <v>9</v>
       </c>
       <c r="E90" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>171</v>
@@ -3699,7 +3706,7 @@
         <v>9</v>
       </c>
       <c r="E91" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>173</v>
@@ -3717,7 +3724,7 @@
         <v>9</v>
       </c>
       <c r="E92" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>175</v>
@@ -3735,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="E93" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>177</v>
@@ -4661,7 +4668,7 @@
       <c r="G144" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="H144" s="10"/>
+      <c r="H144" s="11"/>
     </row>
     <row r="145" spans="3:8">
       <c r="C145" s="3">
@@ -4679,7 +4686,7 @@
       <c r="G145" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="H145" s="10"/>
+      <c r="H145" s="11"/>
     </row>
     <row r="146" spans="3:8">
       <c r="C146" s="3">
@@ -4697,7 +4704,7 @@
       <c r="G146" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="H146" s="10"/>
+      <c r="H146" s="11"/>
     </row>
     <row r="147" spans="3:8">
       <c r="C147" s="3">
@@ -4715,7 +4722,7 @@
       <c r="G147" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H147" s="10"/>
+      <c r="H147" s="11"/>
     </row>
     <row r="148" spans="3:8">
       <c r="C148" s="3">
@@ -4725,7 +4732,7 @@
         <v>9</v>
       </c>
       <c r="E148" s="5">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>283</v>
@@ -4743,7 +4750,7 @@
         <v>9</v>
       </c>
       <c r="E149" s="5">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>285</v>
@@ -4761,7 +4768,7 @@
         <v>9</v>
       </c>
       <c r="E150" s="5">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>287</v>
@@ -4779,7 +4786,7 @@
         <v>9</v>
       </c>
       <c r="E151" s="5">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>289</v>
@@ -4833,7 +4840,7 @@
         <v>9</v>
       </c>
       <c r="E154" s="5">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>294</v>
@@ -4841,7 +4848,7 @@
       <c r="G154" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="H154" s="8"/>
+      <c r="H154" s="10"/>
     </row>
     <row r="155" spans="3:8">
       <c r="C155" s="3">
@@ -4851,7 +4858,7 @@
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
@@ -4859,7 +4866,7 @@
       <c r="G155" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="H155" s="8"/>
+      <c r="H155" s="10"/>
     </row>
     <row r="156" spans="3:8">
       <c r="C156" s="3">
@@ -4897,7 +4904,7 @@
       </c>
       <c r="H157" s="12"/>
     </row>
-    <row r="158" spans="3:7">
+    <row r="158" spans="3:8">
       <c r="C158" s="3">
         <v>153</v>
       </c>
@@ -4913,8 +4920,9 @@
       <c r="G158" s="13" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="159" spans="3:7">
+      <c r="H158" s="10"/>
+    </row>
+    <row r="159" spans="3:8">
       <c r="C159" s="3">
         <v>154</v>
       </c>
@@ -4922,7 +4930,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
@@ -4930,6 +4938,7 @@
       <c r="G159" s="13" t="s">
         <v>305</v>
       </c>
+      <c r="H159" s="10"/>
     </row>
     <row r="160" spans="3:7">
       <c r="C160" s="3">
@@ -5012,42 +5021,59 @@
       <c r="F164" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G164" s="16" t="s">
+      <c r="G164" s="13" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="165" spans="3:7">
       <c r="C165" s="3">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E165" s="5">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="G165" s="2" t="s">
+      <c r="G165" s="13" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="166" spans="3:7">
       <c r="C166" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E166" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>318</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>319</v>
+      </c>
+    </row>
+    <row r="167" spans="3:7">
+      <c r="C167" s="3">
+        <v>203</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="5">
+        <v>203</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="324">
   <si>
     <t>Id</t>
   </si>
@@ -1030,6 +1030,12 @@
   </si>
   <si>
     <t>微风草原</t>
+  </si>
+  <si>
+    <t>WJBeta161</t>
+  </si>
+  <si>
+    <t>时光镇</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1739,7 +1745,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1764,6 +1770,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2119,7 +2126,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I167"/>
+  <dimension ref="C3:I168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5044,36 +5051,53 @@
     </row>
     <row r="166" spans="3:7">
       <c r="C166" s="3">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E166" s="5">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="G166" s="16" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="167" spans="3:7">
       <c r="C167" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>321</v>
+      </c>
+    </row>
+    <row r="168" spans="3:7">
+      <c r="C168" s="3">
+        <v>203</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="5">
+        <v>203</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="326">
   <si>
     <t>Id</t>
   </si>
@@ -1036,6 +1036,12 @@
   </si>
   <si>
     <t>时光镇</t>
+  </si>
+  <si>
+    <t>WJBeta162</t>
+  </si>
+  <si>
+    <t>棉花糖</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1832,13 +1838,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
@@ -2126,7 +2125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I168"/>
+  <dimension ref="C3:I169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5062,42 +5061,59 @@
       <c r="F166" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="G166" s="16" t="s">
+      <c r="G166" s="13" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="167" spans="3:7">
       <c r="C167" s="3">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="G167" s="2" t="s">
+      <c r="G167" s="16" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="168" spans="3:7">
       <c r="C168" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E168" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>322</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>323</v>
+      </c>
+    </row>
+    <row r="169" spans="3:7">
+      <c r="C169" s="3">
+        <v>203</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="5">
+        <v>203</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="327">
   <si>
     <t>Id</t>
   </si>
@@ -1042,6 +1042,9 @@
   </si>
   <si>
     <t>棉花糖</t>
+  </si>
+  <si>
+    <t>WJBeta163</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1751,7 +1754,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1776,7 +1779,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2125,7 +2127,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I169"/>
+  <dimension ref="C3:I170"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5078,42 +5080,57 @@
       <c r="F167" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="G167" s="16" t="s">
+      <c r="G167" s="13" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="168" spans="3:7">
       <c r="C168" s="3">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E168" s="5">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="G168" s="2" t="s">
-        <v>323</v>
-      </c>
+      <c r="G168" s="13"/>
     </row>
     <row r="169" spans="3:7">
       <c r="C169" s="3">
+        <v>202</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="5">
+        <v>202</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="170" spans="3:7">
+      <c r="C170" s="3">
         <v>203</v>
       </c>
-      <c r="D169" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E169" s="5">
+      <c r="D170" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" s="5">
         <v>203</v>
       </c>
-      <c r="F169" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G169" s="2" t="s">
+      <c r="F170" s="5" t="s">
         <v>325</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="328">
   <si>
     <t>Id</t>
   </si>
@@ -1045,6 +1045,9 @@
   </si>
   <si>
     <t>WJBeta163</t>
+  </si>
+  <si>
+    <t>破晓战歌</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5097,7 +5100,9 @@
       <c r="F168" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="G168" s="13"/>
+      <c r="G168" s="13" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="169" spans="3:7">
       <c r="C169" s="3">
@@ -5110,10 +5115,10 @@
         <v>202</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="170" spans="3:7">
@@ -5127,10 +5132,10 @@
         <v>203</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="330">
   <si>
     <t>Id</t>
   </si>
@@ -1048,6 +1048,12 @@
   </si>
   <si>
     <t>破晓战歌</t>
+  </si>
+  <si>
+    <t>WJBeta164</t>
+  </si>
+  <si>
+    <t>翡翠仙境</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2130,7 +2136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I170"/>
+  <dimension ref="C3:I171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4895,7 +4901,7 @@
       <c r="G156" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="12"/>
+      <c r="H156" s="6"/>
     </row>
     <row r="157" spans="3:8">
       <c r="C157" s="3">
@@ -4913,7 +4919,7 @@
       <c r="G157" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="12"/>
+      <c r="H157" s="6"/>
     </row>
     <row r="158" spans="3:8">
       <c r="C158" s="3">
@@ -4923,7 +4929,7 @@
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
@@ -4931,7 +4937,7 @@
       <c r="G158" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="10"/>
+      <c r="H158" s="6"/>
     </row>
     <row r="159" spans="3:8">
       <c r="C159" s="3">
@@ -4941,7 +4947,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
@@ -4949,9 +4955,9 @@
       <c r="G159" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="10"/>
-    </row>
-    <row r="160" spans="3:7">
+      <c r="H159" s="6"/>
+    </row>
+    <row r="160" spans="3:8">
       <c r="C160" s="3">
         <v>155</v>
       </c>
@@ -4967,8 +4973,9 @@
       <c r="G160" s="13" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="161" spans="3:7">
+      <c r="H160" s="10"/>
+    </row>
+    <row r="161" spans="3:8">
       <c r="C161" s="3">
         <v>156</v>
       </c>
@@ -4976,7 +4983,7 @@
         <v>9</v>
       </c>
       <c r="E161" s="5">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>308</v>
@@ -4984,8 +4991,9 @@
       <c r="G161" s="13" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="162" spans="3:7">
+      <c r="H161" s="10"/>
+    </row>
+    <row r="162" spans="3:8">
       <c r="C162" s="3">
         <v>157</v>
       </c>
@@ -5001,8 +5009,9 @@
       <c r="G162" s="13" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="163" spans="3:7">
+      <c r="H162" s="8"/>
+    </row>
+    <row r="163" spans="3:8">
       <c r="C163" s="3">
         <v>158</v>
       </c>
@@ -5010,7 +5019,7 @@
         <v>9</v>
       </c>
       <c r="E163" s="5">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>312</v>
@@ -5018,8 +5027,9 @@
       <c r="G163" s="13" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="164" spans="3:7">
+      <c r="H163" s="8"/>
+    </row>
+    <row r="164" spans="3:8">
       <c r="C164" s="3">
         <v>159</v>
       </c>
@@ -5035,8 +5045,9 @@
       <c r="G164" s="13" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="165" spans="3:7">
+      <c r="H164" s="10"/>
+    </row>
+    <row r="165" spans="3:8">
       <c r="C165" s="3">
         <v>160</v>
       </c>
@@ -5044,7 +5055,7 @@
         <v>9</v>
       </c>
       <c r="E165" s="5">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>316</v>
@@ -5052,6 +5063,7 @@
       <c r="G165" s="13" t="s">
         <v>317</v>
       </c>
+      <c r="H165" s="10"/>
     </row>
     <row r="166" spans="3:7">
       <c r="C166" s="3">
@@ -5106,36 +5118,53 @@
     </row>
     <row r="169" spans="3:7">
       <c r="C169" s="3">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E169" s="5">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="G169" s="2" t="s">
+      <c r="G169" s="13" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="170" spans="3:7">
       <c r="C170" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E170" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>326</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>327</v>
+      </c>
+    </row>
+    <row r="171" spans="3:7">
+      <c r="C171" s="3">
+        <v>203</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" s="5">
+        <v>203</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="332">
   <si>
     <t>Id</t>
   </si>
@@ -1054,6 +1054,12 @@
   </si>
   <si>
     <t>翡翠仙境</t>
+  </si>
+  <si>
+    <t>WJBeta165</t>
+  </si>
+  <si>
+    <t>繁花谷</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2136,7 +2142,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I171"/>
+  <dimension ref="C3:I172"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5135,36 +5141,53 @@
     </row>
     <row r="170" spans="3:7">
       <c r="C170" s="3">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E170" s="5">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="G170" s="2" t="s">
+      <c r="G170" s="13" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="171" spans="3:7">
       <c r="C171" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E171" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>328</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>329</v>
+      </c>
+    </row>
+    <row r="172" spans="3:7">
+      <c r="C172" s="3">
+        <v>203</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="5">
+        <v>203</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="333">
   <si>
     <t>Id</t>
   </si>
@@ -1060,6 +1060,9 @@
   </si>
   <si>
     <t>繁花谷</t>
+  </si>
+  <si>
+    <t>WJBeta166</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2142,7 +2145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I172"/>
+  <dimension ref="C3:I173"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5158,36 +5161,53 @@
     </row>
     <row r="171" spans="3:7">
       <c r="C171" s="3">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E171" s="5">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>329</v>
+      <c r="G171" s="13" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="172" spans="3:7">
       <c r="C172" s="3">
+        <v>202</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="5">
+        <v>202</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="173" spans="3:7">
+      <c r="C173" s="3">
         <v>203</v>
       </c>
-      <c r="D172" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E172" s="5">
+      <c r="D173" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" s="5">
         <v>203</v>
       </c>
-      <c r="F172" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G172" s="2" t="s">
+      <c r="F173" s="5" t="s">
         <v>331</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="335">
   <si>
     <t>Id</t>
   </si>
@@ -1063,6 +1063,12 @@
   </si>
   <si>
     <t>WJBeta166</t>
+  </si>
+  <si>
+    <t>WJBeta167</t>
+  </si>
+  <si>
+    <t>青云之巅</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1277,12 +1283,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1772,7 +1778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1797,6 +1803,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2145,7 +2152,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I173"/>
+  <dimension ref="C3:I174"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -4370,7 +4377,7 @@
       <c r="G126" t="s">
         <v>244</v>
       </c>
-      <c r="H126" s="8"/>
+      <c r="H126" s="10"/>
     </row>
     <row r="127" spans="3:8">
       <c r="C127" s="3">
@@ -4388,7 +4395,7 @@
       <c r="G127" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="H127" s="8"/>
+      <c r="H127" s="10"/>
     </row>
     <row r="128" spans="3:8">
       <c r="C128" s="3">
@@ -4406,7 +4413,7 @@
       <c r="G128" t="s">
         <v>247</v>
       </c>
-      <c r="H128" s="8"/>
+      <c r="H128" s="10"/>
     </row>
     <row r="129" spans="3:8">
       <c r="C129" s="3">
@@ -4424,7 +4431,7 @@
       <c r="G129" t="s">
         <v>249</v>
       </c>
-      <c r="H129" s="8"/>
+      <c r="H129" s="10"/>
     </row>
     <row r="130" spans="3:8">
       <c r="C130" s="3">
@@ -4442,7 +4449,7 @@
       <c r="G130" t="s">
         <v>251</v>
       </c>
-      <c r="H130" s="8"/>
+      <c r="H130" s="10"/>
     </row>
     <row r="131" spans="3:8">
       <c r="C131" s="3">
@@ -4460,7 +4467,7 @@
       <c r="G131" t="s">
         <v>253</v>
       </c>
-      <c r="H131" s="8"/>
+      <c r="H131" s="10"/>
     </row>
     <row r="132" spans="3:8">
       <c r="C132" s="3">
@@ -4478,7 +4485,7 @@
       <c r="G132" t="s">
         <v>255</v>
       </c>
-      <c r="H132" s="8"/>
+      <c r="H132" s="10"/>
     </row>
     <row r="133" spans="3:9">
       <c r="C133" s="3">
@@ -4514,7 +4521,7 @@
       <c r="G134" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="H134" s="8"/>
+      <c r="H134" s="10"/>
     </row>
     <row r="135" spans="3:8">
       <c r="C135" s="3">
@@ -4532,7 +4539,7 @@
       <c r="G135" t="s">
         <v>261</v>
       </c>
-      <c r="H135" s="8"/>
+      <c r="H135" s="10"/>
     </row>
     <row r="136" spans="3:8">
       <c r="C136" s="3">
@@ -4542,7 +4549,7 @@
         <v>9</v>
       </c>
       <c r="E136" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>262</v>
@@ -4550,7 +4557,7 @@
       <c r="G136" t="s">
         <v>263</v>
       </c>
-      <c r="H136" s="12"/>
+      <c r="H136" s="10"/>
     </row>
     <row r="137" spans="3:8">
       <c r="C137" s="3">
@@ -4560,7 +4567,7 @@
         <v>9</v>
       </c>
       <c r="E137" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>264</v>
@@ -4568,7 +4575,7 @@
       <c r="G137" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="H137" s="12"/>
+      <c r="H137" s="10"/>
     </row>
     <row r="138" spans="3:8">
       <c r="C138" s="3">
@@ -4578,7 +4585,7 @@
         <v>9</v>
       </c>
       <c r="E138" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>266</v>
@@ -4586,7 +4593,7 @@
       <c r="G138" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="H138" s="12"/>
+      <c r="H138" s="10"/>
     </row>
     <row r="139" spans="3:8">
       <c r="C139" s="3">
@@ -4596,7 +4603,7 @@
         <v>9</v>
       </c>
       <c r="E139" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>268</v>
@@ -4604,7 +4611,7 @@
       <c r="G139" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="H139" s="12"/>
+      <c r="H139" s="10"/>
     </row>
     <row r="140" spans="3:8">
       <c r="C140" s="3">
@@ -4614,7 +4621,7 @@
         <v>9</v>
       </c>
       <c r="E140" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>270</v>
@@ -4622,7 +4629,7 @@
       <c r="G140" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="H140" s="12"/>
+      <c r="H140" s="10"/>
     </row>
     <row r="141" spans="3:8">
       <c r="C141" s="3">
@@ -4632,7 +4639,7 @@
         <v>9</v>
       </c>
       <c r="E141" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>272</v>
@@ -4640,7 +4647,7 @@
       <c r="G141" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="H141" s="12"/>
+      <c r="H141" s="10"/>
     </row>
     <row r="142" spans="3:8">
       <c r="C142" s="3">
@@ -4650,7 +4657,7 @@
         <v>9</v>
       </c>
       <c r="E142" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>274</v>
@@ -4658,7 +4665,7 @@
       <c r="G142" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="H142" s="12"/>
+      <c r="H142" s="10"/>
     </row>
     <row r="143" spans="3:8">
       <c r="C143" s="3">
@@ -4668,7 +4675,7 @@
         <v>9</v>
       </c>
       <c r="E143" s="5">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>276</v>
@@ -4676,7 +4683,7 @@
       <c r="G143" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="H143" s="12"/>
+      <c r="H143" s="10"/>
     </row>
     <row r="144" spans="3:8">
       <c r="C144" s="3">
@@ -4982,7 +4989,7 @@
       <c r="G160" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="H160" s="10"/>
+      <c r="H160" s="11"/>
     </row>
     <row r="161" spans="3:8">
       <c r="C161" s="3">
@@ -5000,7 +5007,7 @@
       <c r="G161" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="10"/>
+      <c r="H161" s="11"/>
     </row>
     <row r="162" spans="3:8">
       <c r="C162" s="3">
@@ -5010,7 +5017,7 @@
         <v>9</v>
       </c>
       <c r="E162" s="5">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>310</v>
@@ -5018,7 +5025,7 @@
       <c r="G162" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="H162" s="8"/>
+      <c r="H162" s="11"/>
     </row>
     <row r="163" spans="3:8">
       <c r="C163" s="3">
@@ -5028,7 +5035,7 @@
         <v>9</v>
       </c>
       <c r="E163" s="5">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>312</v>
@@ -5036,7 +5043,7 @@
       <c r="G163" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="H163" s="8"/>
+      <c r="H163" s="11"/>
     </row>
     <row r="164" spans="3:8">
       <c r="C164" s="3">
@@ -5074,7 +5081,7 @@
       </c>
       <c r="H165" s="10"/>
     </row>
-    <row r="166" spans="3:7">
+    <row r="166" spans="3:8">
       <c r="C166" s="3">
         <v>161</v>
       </c>
@@ -5090,8 +5097,9 @@
       <c r="G166" s="13" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="167" spans="3:7">
+      <c r="H166" s="11"/>
+    </row>
+    <row r="167" spans="3:8">
       <c r="C167" s="3">
         <v>162</v>
       </c>
@@ -5099,7 +5107,7 @@
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
@@ -5107,6 +5115,7 @@
       <c r="G167" s="13" t="s">
         <v>321</v>
       </c>
+      <c r="H167" s="11"/>
     </row>
     <row r="168" spans="3:7">
       <c r="C168" s="3">
@@ -5178,36 +5187,53 @@
     </row>
     <row r="172" spans="3:7">
       <c r="C172" s="3">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E172" s="5">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="G172" s="2" t="s">
+      <c r="G172" s="16" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="173" spans="3:7">
       <c r="C173" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E173" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>331</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>332</v>
+      </c>
+    </row>
+    <row r="174" spans="3:7">
+      <c r="C174" s="3">
+        <v>203</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="5">
+        <v>203</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="336">
   <si>
     <t>Id</t>
   </si>
@@ -1069,6 +1069,9 @@
   </si>
   <si>
     <t>青云之巅</t>
+  </si>
+  <si>
+    <t>WJBeta168</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1778,7 +1781,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1803,7 +1806,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2152,7 +2154,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I174"/>
+  <dimension ref="C3:I175"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5198,42 +5200,57 @@
       <c r="F172" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="G172" s="16" t="s">
+      <c r="G172" s="13" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="173" spans="3:7">
       <c r="C173" s="3">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E173" s="5">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G173" s="2" t="s">
-        <v>332</v>
-      </c>
+      <c r="G173" s="13"/>
     </row>
     <row r="174" spans="3:7">
       <c r="C174" s="3">
+        <v>202</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="5">
+        <v>202</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="175" spans="3:7">
+      <c r="C175" s="3">
         <v>203</v>
       </c>
-      <c r="D174" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E174" s="5">
+      <c r="D175" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="5">
         <v>203</v>
       </c>
-      <c r="F174" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="G174" s="2" t="s">
+      <c r="F175" s="5" t="s">
         <v>334</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="337">
   <si>
     <t>Id</t>
   </si>
@@ -1072,6 +1072,9 @@
   </si>
   <si>
     <t>WJBeta168</t>
+  </si>
+  <si>
+    <t>时光之歌</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1286,12 +1289,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1781,7 +1784,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1806,6 +1809,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5217,7 +5221,9 @@
       <c r="F173" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G173" s="13"/>
+      <c r="G173" s="16" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="174" spans="3:7">
       <c r="C174" s="3">
@@ -5230,10 +5236,10 @@
         <v>202</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="175" spans="3:7">
@@ -5247,10 +5253,10 @@
         <v>203</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="339">
   <si>
     <t>Id</t>
   </si>
@@ -1075,6 +1075,12 @@
   </si>
   <si>
     <t>时光之歌</t>
+  </si>
+  <si>
+    <t>WJBeta169</t>
+  </si>
+  <si>
+    <t>决战之巅</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2158,7 +2164,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I175"/>
+  <dimension ref="C3:I176"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5221,42 +5227,59 @@
       <c r="F173" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G173" s="16" t="s">
+      <c r="G173" s="13" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="174" spans="3:7">
       <c r="C174" s="3">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E174" s="5">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="G174" s="2" t="s">
+      <c r="G174" s="16" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="175" spans="3:7">
       <c r="C175" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="176" spans="3:7">
+      <c r="C176" s="3">
+        <v>203</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="5">
+        <v>203</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="341">
   <si>
     <t>Id</t>
   </si>
@@ -1081,6 +1081,12 @@
   </si>
   <si>
     <t>决战之巅</t>
+  </si>
+  <si>
+    <t>WJBeta170</t>
+  </si>
+  <si>
+    <t>迷雾森境</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1790,7 +1796,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1815,7 +1821,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2164,7 +2169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I176"/>
+  <dimension ref="C3:I177"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5244,42 +5249,59 @@
       <c r="F174" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="G174" s="16" t="s">
+      <c r="G174" s="13" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="175" spans="3:7">
       <c r="C175" s="3">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="G175" s="2" t="s">
+      <c r="G175" s="13" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="176" spans="3:7">
       <c r="C176" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E176" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>337</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>338</v>
+      </c>
+    </row>
+    <row r="177" spans="3:7">
+      <c r="C177" s="3">
+        <v>203</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="5">
+        <v>203</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="343">
   <si>
     <t>Id</t>
   </si>
@@ -1087,6 +1087,12 @@
   </si>
   <si>
     <t>迷雾森境</t>
+  </si>
+  <si>
+    <t>WJBeta171</t>
+  </si>
+  <si>
+    <t>WJBeta172</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2169,7 +2175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I177"/>
+  <dimension ref="C3:I179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5272,36 +5278,66 @@
     </row>
     <row r="176" spans="3:7">
       <c r="C176" s="3">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E176" s="5">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="G176" s="2" t="s">
-        <v>338</v>
-      </c>
+      <c r="G176" s="13"/>
     </row>
     <row r="177" spans="3:7">
       <c r="C177" s="3">
+        <v>172</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="5">
+        <v>172</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G177" s="13"/>
+    </row>
+    <row r="178" spans="3:7">
+      <c r="C178" s="3">
+        <v>202</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="5">
+        <v>202</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="179" spans="3:7">
+      <c r="C179" s="3">
         <v>203</v>
       </c>
-      <c r="D177" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E177" s="5">
+      <c r="D179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="5">
         <v>203</v>
       </c>
-      <c r="F177" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>340</v>
+      <c r="F179" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="344">
   <si>
     <t>Id</t>
   </si>
@@ -1090,6 +1090,9 @@
   </si>
   <si>
     <t>WJBeta171</t>
+  </si>
+  <si>
+    <t>ValorArena</t>
   </si>
   <si>
     <t>WJBeta172</t>
@@ -1307,12 +1310,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5289,7 +5292,9 @@
       <c r="F176" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="G176" s="13"/>
+      <c r="G176" s="13" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="177" spans="3:7">
       <c r="C177" s="3">
@@ -5302,7 +5307,7 @@
         <v>172</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G177" s="13"/>
     </row>
@@ -5317,10 +5322,10 @@
         <v>202</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="179" spans="3:7">
@@ -5334,10 +5339,10 @@
         <v>203</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="342">
   <si>
     <t>Id</t>
   </si>
@@ -1087,12 +1087,6 @@
   </si>
   <si>
     <t>迷雾森境</t>
-  </si>
-  <si>
-    <t>WJBeta171</t>
-  </si>
-  <si>
-    <t>ValorArena</t>
   </si>
   <si>
     <t>WJBeta172</t>
@@ -1310,12 +1304,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2178,7 +2172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I179"/>
+  <dimension ref="C3:I178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5281,68 +5275,51 @@
     </row>
     <row r="176" spans="3:7">
       <c r="C176" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E176" s="5">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="G176" s="13" t="s">
-        <v>338</v>
-      </c>
+      <c r="G176" s="13"/>
     </row>
     <row r="177" spans="3:7">
       <c r="C177" s="3">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E177" s="5">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="F177" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G177" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="13"/>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E178" s="5">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>340</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>341</v>
-      </c>
-    </row>
-    <row r="179" spans="3:7">
-      <c r="C179" s="3">
-        <v>203</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E179" s="5">
-        <v>203</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="G179" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="343">
   <si>
     <t>Id</t>
   </si>
@@ -1090,6 +1090,9 @@
   </si>
   <si>
     <t>WJBeta172</t>
+  </si>
+  <si>
+    <t>星辰殿堂</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5286,7 +5289,9 @@
       <c r="F176" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="G176" s="13"/>
+      <c r="G176" s="13" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="177" spans="3:7">
       <c r="C177" s="3">
@@ -5299,10 +5304,10 @@
         <v>202</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="178" spans="3:7">
@@ -5316,10 +5321,10 @@
         <v>203</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -4932,7 +4932,7 @@
         <v>9</v>
       </c>
       <c r="E156" s="5">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>298</v>
@@ -4940,7 +4940,7 @@
       <c r="G156" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="6"/>
+      <c r="H156" s="10"/>
     </row>
     <row r="157" spans="3:8">
       <c r="C157" s="3">
@@ -4950,7 +4950,7 @@
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
@@ -4958,7 +4958,7 @@
       <c r="G157" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="6"/>
+      <c r="H157" s="10"/>
     </row>
     <row r="158" spans="3:8">
       <c r="C158" s="3">
@@ -4968,7 +4968,7 @@
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
@@ -4976,7 +4976,7 @@
       <c r="G158" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="6"/>
+      <c r="H158" s="10"/>
     </row>
     <row r="159" spans="3:8">
       <c r="C159" s="3">
@@ -4986,7 +4986,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
@@ -4994,7 +4994,7 @@
       <c r="G159" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="6"/>
+      <c r="H159" s="10"/>
     </row>
     <row r="160" spans="3:8">
       <c r="C160" s="3">
@@ -5084,7 +5084,7 @@
       <c r="G164" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="H164" s="10"/>
+      <c r="H164" s="12"/>
     </row>
     <row r="165" spans="3:8">
       <c r="C165" s="3">
@@ -5102,7 +5102,7 @@
       <c r="G165" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="H165" s="10"/>
+      <c r="H165" s="12"/>
     </row>
     <row r="166" spans="3:8">
       <c r="C166" s="3">
@@ -5112,7 +5112,7 @@
         <v>9</v>
       </c>
       <c r="E166" s="5">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>318</v>
@@ -5120,7 +5120,7 @@
       <c r="G166" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="H166" s="11"/>
+      <c r="H166" s="12"/>
     </row>
     <row r="167" spans="3:8">
       <c r="C167" s="3">
@@ -5130,7 +5130,7 @@
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
@@ -5138,9 +5138,9 @@
       <c r="G167" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H167" s="11"/>
-    </row>
-    <row r="168" spans="3:7">
+      <c r="H167" s="12"/>
+    </row>
+    <row r="168" spans="3:8">
       <c r="C168" s="3">
         <v>163</v>
       </c>
@@ -5156,8 +5156,9 @@
       <c r="G168" s="13" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="169" spans="3:7">
+      <c r="H168" s="11"/>
+    </row>
+    <row r="169" spans="3:8">
       <c r="C169" s="3">
         <v>164</v>
       </c>
@@ -5165,7 +5166,7 @@
         <v>9</v>
       </c>
       <c r="E169" s="5">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>324</v>
@@ -5173,8 +5174,9 @@
       <c r="G169" s="13" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="170" spans="3:7">
+      <c r="H169" s="11"/>
+    </row>
+    <row r="170" spans="3:8">
       <c r="C170" s="3">
         <v>165</v>
       </c>
@@ -5190,8 +5192,9 @@
       <c r="G170" s="13" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="171" spans="3:7">
+      <c r="H170" s="10"/>
+    </row>
+    <row r="171" spans="3:8">
       <c r="C171" s="3">
         <v>166</v>
       </c>
@@ -5199,7 +5202,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="5">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>328</v>
@@ -5207,6 +5210,7 @@
       <c r="G171" s="13" t="s">
         <v>196</v>
       </c>
+      <c r="H171" s="10"/>
     </row>
     <row r="172" spans="3:7">
       <c r="C172" s="3">

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="344">
   <si>
     <t>Id</t>
   </si>
@@ -1093,6 +1093,9 @@
   </si>
   <si>
     <t>星辰殿堂</t>
+  </si>
+  <si>
+    <t>WJBeta173</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2175,7 +2178,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I178"/>
+  <dimension ref="C3:I179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5299,36 +5302,51 @@
     </row>
     <row r="177" spans="3:7">
       <c r="C177" s="3">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E177" s="5">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="2" t="s">
-        <v>340</v>
-      </c>
+      <c r="G177" s="13"/>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
+        <v>202</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="5">
+        <v>202</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="179" spans="3:7">
+      <c r="C179" s="3">
         <v>203</v>
       </c>
-      <c r="D178" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E178" s="5">
+      <c r="D179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="5">
         <v>203</v>
       </c>
-      <c r="F178" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="G178" s="2" t="s">
+      <c r="F179" s="5" t="s">
         <v>342</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="345">
   <si>
     <t>Id</t>
   </si>
@@ -1096,6 +1096,9 @@
   </si>
   <si>
     <t>WJBeta173</t>
+  </si>
+  <si>
+    <t>童话森林</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1805,7 +1808,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1830,6 +1833,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5313,7 +5317,9 @@
       <c r="F177" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="13"/>
+      <c r="G177" s="16" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
@@ -5326,10 +5332,10 @@
         <v>202</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="179" spans="3:7">
@@ -5343,10 +5349,10 @@
         <v>203</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="346">
   <si>
     <t>Id</t>
   </si>
@@ -1099,6 +1099,9 @@
   </si>
   <si>
     <t>童话森林</t>
+  </si>
+  <si>
+    <t>WJBeta174</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1808,7 +1811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1833,7 +1836,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2182,7 +2184,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I179"/>
+  <dimension ref="C3:I180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5317,42 +5319,57 @@
       <c r="F177" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="16" t="s">
+      <c r="G177" s="13" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E178" s="5">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G178" s="2" t="s">
-        <v>342</v>
-      </c>
+      <c r="G178" s="13"/>
     </row>
     <row r="179" spans="3:7">
       <c r="C179" s="3">
+        <v>202</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="5">
+        <v>202</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="180" spans="3:7">
+      <c r="C180" s="3">
         <v>203</v>
       </c>
-      <c r="D179" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E179" s="5">
+      <c r="D180" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="5">
         <v>203</v>
       </c>
-      <c r="F179" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="G179" s="2" t="s">
+      <c r="F180" s="5" t="s">
         <v>344</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="347">
   <si>
     <t>Id</t>
   </si>
@@ -1102,6 +1102,9 @@
   </si>
   <si>
     <t>WJBeta174</t>
+  </si>
+  <si>
+    <t>龙息之谷</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1811,7 +1814,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1836,6 +1839,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5336,7 +5340,9 @@
       <c r="F178" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G178" s="13"/>
+      <c r="G178" s="16" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="179" spans="3:7">
       <c r="C179" s="3">
@@ -5349,10 +5355,10 @@
         <v>202</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="180" spans="3:7">
@@ -5366,10 +5372,10 @@
         <v>203</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="348">
   <si>
     <t>Id</t>
   </si>
@@ -1105,6 +1105,9 @@
   </si>
   <si>
     <t>龙息之谷</t>
+  </si>
+  <si>
+    <t>WJBeta175</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1814,7 +1817,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1839,7 +1842,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2188,7 +2190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I180"/>
+  <dimension ref="C3:I181"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5340,42 +5342,57 @@
       <c r="F178" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G178" s="16" t="s">
+      <c r="G178" s="13" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="179" spans="3:7">
       <c r="C179" s="3">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E179" s="5">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="G179" s="2" t="s">
-        <v>344</v>
-      </c>
+      <c r="G179" s="13"/>
     </row>
     <row r="180" spans="3:7">
       <c r="C180" s="3">
+        <v>202</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="5">
+        <v>202</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="181" spans="3:7">
+      <c r="C181" s="3">
         <v>203</v>
       </c>
-      <c r="D180" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E180" s="5">
+      <c r="D181" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="5">
         <v>203</v>
       </c>
-      <c r="F180" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="G180" s="2" t="s">
+      <c r="F181" s="5" t="s">
         <v>346</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="349">
   <si>
     <t>Id</t>
   </si>
@@ -1108,6 +1108,9 @@
   </si>
   <si>
     <t>WJBeta175</t>
+  </si>
+  <si>
+    <t>星界回廊</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5227,7 +5230,7 @@
       </c>
       <c r="H171" s="10"/>
     </row>
-    <row r="172" spans="3:7">
+    <row r="172" spans="3:8">
       <c r="C172" s="3">
         <v>167</v>
       </c>
@@ -5243,8 +5246,9 @@
       <c r="G172" s="13" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="173" spans="3:7">
+      <c r="H172" s="6"/>
+    </row>
+    <row r="173" spans="3:8">
       <c r="C173" s="3">
         <v>168</v>
       </c>
@@ -5252,7 +5256,7 @@
         <v>9</v>
       </c>
       <c r="E173" s="5">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>331</v>
@@ -5260,8 +5264,9 @@
       <c r="G173" s="13" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="174" spans="3:7">
+      <c r="H173" s="6"/>
+    </row>
+    <row r="174" spans="3:8">
       <c r="C174" s="3">
         <v>169</v>
       </c>
@@ -5277,8 +5282,9 @@
       <c r="G174" s="13" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="175" spans="3:7">
+      <c r="H174" s="11"/>
+    </row>
+    <row r="175" spans="3:8">
       <c r="C175" s="3">
         <v>170</v>
       </c>
@@ -5286,7 +5292,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
@@ -5294,6 +5300,7 @@
       <c r="G175" s="13" t="s">
         <v>336</v>
       </c>
+      <c r="H175" s="11"/>
     </row>
     <row r="176" spans="3:7">
       <c r="C176" s="3">
@@ -5359,7 +5366,9 @@
       <c r="F179" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="G179" s="13"/>
+      <c r="G179" s="13" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="180" spans="3:7">
       <c r="C180" s="3">
@@ -5372,10 +5381,10 @@
         <v>202</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="181" spans="3:7">
@@ -5389,10 +5398,10 @@
         <v>203</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="350">
   <si>
     <t>Id</t>
   </si>
@@ -1111,6 +1111,9 @@
   </si>
   <si>
     <t>星界回廊</t>
+  </si>
+  <si>
+    <t>WJBeta176</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2193,7 +2196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I181"/>
+  <dimension ref="C3:I182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5372,36 +5375,51 @@
     </row>
     <row r="180" spans="3:7">
       <c r="C180" s="3">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E180" s="5">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="G180" s="2" t="s">
-        <v>346</v>
-      </c>
+      <c r="G180" s="13"/>
     </row>
     <row r="181" spans="3:7">
       <c r="C181" s="3">
+        <v>202</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="5">
+        <v>202</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="182" spans="3:7">
+      <c r="C182" s="3">
         <v>203</v>
       </c>
-      <c r="D181" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E181" s="5">
+      <c r="D182" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="5">
         <v>203</v>
       </c>
-      <c r="F181" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="G181" s="2" t="s">
+      <c r="F182" s="5" t="s">
         <v>348</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="351">
   <si>
     <t>Id</t>
   </si>
@@ -1114,6 +1114,9 @@
   </si>
   <si>
     <t>WJBeta176</t>
+  </si>
+  <si>
+    <t>普天同庆</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1823,7 +1826,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1848,6 +1851,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5386,7 +5390,9 @@
       <c r="F180" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="G180" s="13"/>
+      <c r="G180" s="16" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="181" spans="3:7">
       <c r="C181" s="3">
@@ -5399,10 +5405,10 @@
         <v>202</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="182" spans="3:7">
@@ -5416,10 +5422,10 @@
         <v>203</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="353">
   <si>
     <t>Id</t>
   </si>
@@ -1117,6 +1117,12 @@
   </si>
   <si>
     <t>普天同庆</t>
+  </si>
+  <si>
+    <t>WJBeta177</t>
+  </si>
+  <si>
+    <t>长安旧梦</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1826,7 +1832,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1851,7 +1857,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2200,7 +2205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I182"/>
+  <dimension ref="C3:I183"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5390,42 +5395,59 @@
       <c r="F180" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="G180" s="16" t="s">
+      <c r="G180" s="13" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="181" spans="3:7">
       <c r="C181" s="3">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E181" s="5">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="G181" s="2" t="s">
+      <c r="G181" s="13" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="182" spans="3:7">
       <c r="C182" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E182" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>349</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>350</v>
+      </c>
+    </row>
+    <row r="183" spans="3:7">
+      <c r="C183" s="3">
+        <v>203</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" s="5">
+        <v>203</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="355">
   <si>
     <t>Id</t>
   </si>
@@ -1123,6 +1123,12 @@
   </si>
   <si>
     <t>长安旧梦</t>
+  </si>
+  <si>
+    <t>WJBeta178</t>
+  </si>
+  <si>
+    <t>风暴之地</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2205,7 +2211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I183"/>
+  <dimension ref="C3:I184"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5418,36 +5424,53 @@
     </row>
     <row r="182" spans="3:7">
       <c r="C182" s="3">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E182" s="5">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G182" s="2" t="s">
+      <c r="G182" s="13" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="183" spans="3:7">
       <c r="C183" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E183" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>351</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>352</v>
+      </c>
+    </row>
+    <row r="184" spans="3:7">
+      <c r="C184" s="3">
+        <v>203</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" s="5">
+        <v>203</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="357">
   <si>
     <t>Id</t>
   </si>
@@ -1129,6 +1129,12 @@
   </si>
   <si>
     <t>风暴之地</t>
+  </si>
+  <si>
+    <t>WJBeta179</t>
+  </si>
+  <si>
+    <t>巨刃降临</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2211,7 +2217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I184"/>
+  <dimension ref="C3:I185"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5048,7 +5054,7 @@
       <c r="G160" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="H160" s="11"/>
+      <c r="H160" s="6"/>
     </row>
     <row r="161" spans="3:8">
       <c r="C161" s="3">
@@ -5066,7 +5072,7 @@
       <c r="G161" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="11"/>
+      <c r="H161" s="6"/>
     </row>
     <row r="162" spans="3:8">
       <c r="C162" s="3">
@@ -5084,7 +5090,7 @@
       <c r="G162" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="H162" s="11"/>
+      <c r="H162" s="6"/>
     </row>
     <row r="163" spans="3:8">
       <c r="C163" s="3">
@@ -5102,7 +5108,7 @@
       <c r="G163" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="H163" s="11"/>
+      <c r="H163" s="6"/>
     </row>
     <row r="164" spans="3:8">
       <c r="C164" s="3">
@@ -5112,7 +5118,7 @@
         <v>9</v>
       </c>
       <c r="E164" s="5">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>314</v>
@@ -5120,7 +5126,7 @@
       <c r="G164" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="H164" s="12"/>
+      <c r="H164" s="6"/>
     </row>
     <row r="165" spans="3:8">
       <c r="C165" s="3">
@@ -5130,7 +5136,7 @@
         <v>9</v>
       </c>
       <c r="E165" s="5">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>316</v>
@@ -5138,7 +5144,7 @@
       <c r="G165" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="H165" s="12"/>
+      <c r="H165" s="6"/>
     </row>
     <row r="166" spans="3:8">
       <c r="C166" s="3">
@@ -5148,7 +5154,7 @@
         <v>9</v>
       </c>
       <c r="E166" s="5">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>318</v>
@@ -5156,7 +5162,7 @@
       <c r="G166" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="H166" s="12"/>
+      <c r="H166" s="6"/>
     </row>
     <row r="167" spans="3:8">
       <c r="C167" s="3">
@@ -5166,7 +5172,7 @@
         <v>9</v>
       </c>
       <c r="E167" s="5">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>320</v>
@@ -5174,7 +5180,7 @@
       <c r="G167" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H167" s="12"/>
+      <c r="H167" s="6"/>
     </row>
     <row r="168" spans="3:8">
       <c r="C168" s="3">
@@ -5192,7 +5198,7 @@
       <c r="G168" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="H168" s="11"/>
+      <c r="H168" s="10"/>
     </row>
     <row r="169" spans="3:8">
       <c r="C169" s="3">
@@ -5210,7 +5216,7 @@
       <c r="G169" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="H169" s="11"/>
+      <c r="H169" s="10"/>
     </row>
     <row r="170" spans="3:8">
       <c r="C170" s="3">
@@ -5220,7 +5226,7 @@
         <v>9</v>
       </c>
       <c r="E170" s="5">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>326</v>
@@ -5238,7 +5244,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="5">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>328</v>
@@ -5320,7 +5326,7 @@
       </c>
       <c r="H175" s="11"/>
     </row>
-    <row r="176" spans="3:7">
+    <row r="176" spans="3:8">
       <c r="C176" s="3">
         <v>172</v>
       </c>
@@ -5336,8 +5342,9 @@
       <c r="G176" s="13" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="177" spans="3:7">
+      <c r="H176" s="10"/>
+    </row>
+    <row r="177" spans="3:8">
       <c r="C177" s="3">
         <v>173</v>
       </c>
@@ -5345,7 +5352,7 @@
         <v>9</v>
       </c>
       <c r="E177" s="5">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>339</v>
@@ -5353,6 +5360,7 @@
       <c r="G177" s="13" t="s">
         <v>340</v>
       </c>
+      <c r="H177" s="10"/>
     </row>
     <row r="178" spans="3:7">
       <c r="C178" s="3">
@@ -5441,36 +5449,53 @@
     </row>
     <row r="183" spans="3:7">
       <c r="C183" s="3">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E183" s="5">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="G183" s="2" t="s">
+      <c r="G183" s="13" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="184" spans="3:7">
       <c r="C184" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E184" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>353</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>354</v>
+      </c>
+    </row>
+    <row r="185" spans="3:7">
+      <c r="C185" s="3">
+        <v>203</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="5">
+        <v>203</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="358">
   <si>
     <t>Id</t>
   </si>
@@ -1135,6 +1135,9 @@
   </si>
   <si>
     <t>巨刃降临</t>
+  </si>
+  <si>
+    <t>WJBeta180</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2217,7 +2220,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I185"/>
+  <dimension ref="C3:I186"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5466,36 +5469,51 @@
     </row>
     <row r="184" spans="3:7">
       <c r="C184" s="3">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E184" s="5">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="G184" s="2" t="s">
-        <v>354</v>
-      </c>
+      <c r="G184" s="13"/>
     </row>
     <row r="185" spans="3:7">
       <c r="C185" s="3">
+        <v>202</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="5">
+        <v>202</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="186" spans="3:7">
+      <c r="C186" s="3">
         <v>203</v>
       </c>
-      <c r="D185" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E185" s="5">
+      <c r="D186" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" s="5">
         <v>203</v>
       </c>
-      <c r="F185" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="G185" s="2" t="s">
+      <c r="F186" s="5" t="s">
         <v>356</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="359">
   <si>
     <t>Id</t>
   </si>
@@ -1138,6 +1138,9 @@
   </si>
   <si>
     <t>WJBeta180</t>
+  </si>
+  <si>
+    <t>生命之树</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5480,7 +5483,9 @@
       <c r="F184" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="G184" s="13"/>
+      <c r="G184" s="13" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="185" spans="3:7">
       <c r="C185" s="3">
@@ -5493,10 +5498,10 @@
         <v>202</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="186" spans="3:7">
@@ -5510,10 +5515,10 @@
         <v>203</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="361">
   <si>
     <t>Id</t>
   </si>
@@ -1141,6 +1141,12 @@
   </si>
   <si>
     <t>生命之树</t>
+  </si>
+  <si>
+    <t>WJBeta181</t>
+  </si>
+  <si>
+    <t>浮生若梦</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1355,12 +1361,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1850,7 +1856,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1875,6 +1881,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2223,7 +2230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I186"/>
+  <dimension ref="C3:I187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -2238,7 +2245,7 @@
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" spans="3:8">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -2252,7 +2259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:6">
+    <row r="4" spans="3:8">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2266,7 +2273,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" spans="3:8">
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2280,7 +2287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:6">
+    <row r="6" s="1" customFormat="1" spans="3:8">
       <c r="C6" s="5">
         <v>1</v>
       </c>
@@ -2294,7 +2301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="3:7">
+    <row r="7" spans="3:8">
       <c r="C7" s="3">
         <v>2</v>
       </c>
@@ -2311,7 +2318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="3:7">
+    <row r="8" spans="3:8">
       <c r="C8" s="3">
         <v>3</v>
       </c>
@@ -2328,7 +2335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="3:7">
+    <row r="9" spans="3:8">
       <c r="C9" s="3">
         <v>4</v>
       </c>
@@ -2365,7 +2372,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="3:7">
+    <row r="11" spans="3:8">
       <c r="C11" s="3">
         <v>6</v>
       </c>
@@ -2382,7 +2389,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="3:7">
+    <row r="12" spans="3:8">
       <c r="C12" s="5">
         <v>7</v>
       </c>
@@ -2399,7 +2406,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:7">
+    <row r="13" spans="3:8">
       <c r="C13" s="3">
         <v>8</v>
       </c>
@@ -2436,7 +2443,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="3:7">
+    <row r="15" spans="3:8">
       <c r="C15" s="3">
         <v>10</v>
       </c>
@@ -2453,7 +2460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="3:7">
+    <row r="16" spans="3:8">
       <c r="C16" s="5">
         <v>11</v>
       </c>
@@ -3622,7 +3629,7 @@
       </c>
       <c r="H80" s="11"/>
     </row>
-    <row r="81" spans="3:8">
+    <row r="81" spans="3:9">
       <c r="C81" s="3">
         <v>76</v>
       </c>
@@ -3640,7 +3647,7 @@
       </c>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="3:8">
+    <row r="82" spans="3:9">
       <c r="C82" s="3">
         <v>77</v>
       </c>
@@ -3658,7 +3665,7 @@
       </c>
       <c r="H82" s="11"/>
     </row>
-    <row r="83" spans="3:8">
+    <row r="83" spans="3:9">
       <c r="C83" s="3">
         <v>78</v>
       </c>
@@ -3676,7 +3683,7 @@
       </c>
       <c r="H83" s="11"/>
     </row>
-    <row r="84" spans="3:8">
+    <row r="84" spans="3:9">
       <c r="C84" s="3">
         <v>79</v>
       </c>
@@ -3694,7 +3701,7 @@
       </c>
       <c r="H84" s="11"/>
     </row>
-    <row r="85" spans="3:8">
+    <row r="85" spans="3:9">
       <c r="C85" s="3">
         <v>80</v>
       </c>
@@ -3712,7 +3719,7 @@
       </c>
       <c r="H85" s="6"/>
     </row>
-    <row r="86" spans="3:8">
+    <row r="86" spans="3:9">
       <c r="C86" s="3">
         <v>81</v>
       </c>
@@ -3730,7 +3737,7 @@
       </c>
       <c r="H86" s="6"/>
     </row>
-    <row r="87" spans="3:8">
+    <row r="87" spans="3:9">
       <c r="C87" s="3">
         <v>82</v>
       </c>
@@ -3748,7 +3755,7 @@
       </c>
       <c r="H87" s="6"/>
     </row>
-    <row r="88" spans="3:8">
+    <row r="88" spans="3:9">
       <c r="C88" s="3">
         <v>83</v>
       </c>
@@ -3784,7 +3791,7 @@
       </c>
       <c r="I89" s="6"/>
     </row>
-    <row r="90" spans="3:8">
+    <row r="90" spans="3:9">
       <c r="C90" s="3">
         <v>85</v>
       </c>
@@ -3802,7 +3809,7 @@
       </c>
       <c r="H90" s="6"/>
     </row>
-    <row r="91" spans="3:8">
+    <row r="91" spans="3:9">
       <c r="C91" s="3">
         <v>86</v>
       </c>
@@ -3820,7 +3827,7 @@
       </c>
       <c r="H91" s="6"/>
     </row>
-    <row r="92" spans="3:8">
+    <row r="92" spans="3:9">
       <c r="C92" s="3">
         <v>87</v>
       </c>
@@ -3838,7 +3845,7 @@
       </c>
       <c r="H92" s="6"/>
     </row>
-    <row r="93" spans="3:8">
+    <row r="93" spans="3:9">
       <c r="C93" s="3">
         <v>88</v>
       </c>
@@ -3856,7 +3863,7 @@
       </c>
       <c r="H93" s="6"/>
     </row>
-    <row r="94" spans="3:8">
+    <row r="94" spans="3:9">
       <c r="C94" s="3">
         <v>89</v>
       </c>
@@ -3874,7 +3881,7 @@
       </c>
       <c r="H94" s="10"/>
     </row>
-    <row r="95" spans="3:8">
+    <row r="95" spans="3:9">
       <c r="C95" s="3">
         <v>90</v>
       </c>
@@ -3892,7 +3899,7 @@
       </c>
       <c r="H95" s="10"/>
     </row>
-    <row r="96" spans="3:8">
+    <row r="96" spans="3:9">
       <c r="C96" s="3">
         <v>91</v>
       </c>
@@ -4486,7 +4493,7 @@
       </c>
       <c r="H128" s="10"/>
     </row>
-    <row r="129" spans="3:8">
+    <row r="129" spans="3:9">
       <c r="C129" s="3">
         <v>124</v>
       </c>
@@ -4504,7 +4511,7 @@
       </c>
       <c r="H129" s="10"/>
     </row>
-    <row r="130" spans="3:8">
+    <row r="130" spans="3:9">
       <c r="C130" s="3">
         <v>125</v>
       </c>
@@ -4522,7 +4529,7 @@
       </c>
       <c r="H130" s="10"/>
     </row>
-    <row r="131" spans="3:8">
+    <row r="131" spans="3:9">
       <c r="C131" s="3">
         <v>126</v>
       </c>
@@ -4540,7 +4547,7 @@
       </c>
       <c r="H131" s="10"/>
     </row>
-    <row r="132" spans="3:8">
+    <row r="132" spans="3:9">
       <c r="C132" s="3">
         <v>127</v>
       </c>
@@ -4576,7 +4583,7 @@
       </c>
       <c r="I133" s="12"/>
     </row>
-    <row r="134" spans="3:8">
+    <row r="134" spans="3:9">
       <c r="C134" s="3">
         <v>129</v>
       </c>
@@ -4594,7 +4601,7 @@
       </c>
       <c r="H134" s="10"/>
     </row>
-    <row r="135" spans="3:8">
+    <row r="135" spans="3:9">
       <c r="C135" s="3">
         <v>130</v>
       </c>
@@ -4612,7 +4619,7 @@
       </c>
       <c r="H135" s="10"/>
     </row>
-    <row r="136" spans="3:8">
+    <row r="136" spans="3:9">
       <c r="C136" s="3">
         <v>131</v>
       </c>
@@ -4630,7 +4637,7 @@
       </c>
       <c r="H136" s="10"/>
     </row>
-    <row r="137" spans="3:8">
+    <row r="137" spans="3:9">
       <c r="C137" s="3">
         <v>132</v>
       </c>
@@ -4648,7 +4655,7 @@
       </c>
       <c r="H137" s="10"/>
     </row>
-    <row r="138" spans="3:8">
+    <row r="138" spans="3:9">
       <c r="C138" s="3">
         <v>133</v>
       </c>
@@ -4666,7 +4673,7 @@
       </c>
       <c r="H138" s="10"/>
     </row>
-    <row r="139" spans="3:8">
+    <row r="139" spans="3:9">
       <c r="C139" s="3">
         <v>134</v>
       </c>
@@ -4684,7 +4691,7 @@
       </c>
       <c r="H139" s="10"/>
     </row>
-    <row r="140" spans="3:8">
+    <row r="140" spans="3:9">
       <c r="C140" s="3">
         <v>135</v>
       </c>
@@ -4702,7 +4709,7 @@
       </c>
       <c r="H140" s="10"/>
     </row>
-    <row r="141" spans="3:8">
+    <row r="141" spans="3:9">
       <c r="C141" s="3">
         <v>136</v>
       </c>
@@ -4720,7 +4727,7 @@
       </c>
       <c r="H141" s="10"/>
     </row>
-    <row r="142" spans="3:8">
+    <row r="142" spans="3:9">
       <c r="C142" s="3">
         <v>137</v>
       </c>
@@ -4738,7 +4745,7 @@
       </c>
       <c r="H142" s="10"/>
     </row>
-    <row r="143" spans="3:8">
+    <row r="143" spans="3:9">
       <c r="C143" s="3">
         <v>138</v>
       </c>
@@ -4756,7 +4763,7 @@
       </c>
       <c r="H143" s="10"/>
     </row>
-    <row r="144" spans="3:8">
+    <row r="144" spans="3:9">
       <c r="C144" s="3">
         <v>139</v>
       </c>
@@ -5368,7 +5375,7 @@
       </c>
       <c r="H177" s="10"/>
     </row>
-    <row r="178" spans="3:7">
+    <row r="178" spans="3:8">
       <c r="C178" s="3">
         <v>174</v>
       </c>
@@ -5385,7 +5392,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="179" spans="3:7">
+    <row r="179" spans="3:8">
       <c r="C179" s="3">
         <v>175</v>
       </c>
@@ -5402,7 +5409,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="180" spans="3:7">
+    <row r="180" spans="3:8">
       <c r="C180" s="3">
         <v>176</v>
       </c>
@@ -5419,7 +5426,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="181" spans="3:7">
+    <row r="181" spans="3:8">
       <c r="C181" s="3">
         <v>177</v>
       </c>
@@ -5436,7 +5443,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="182" spans="3:7">
+    <row r="182" spans="3:8">
       <c r="C182" s="3">
         <v>178</v>
       </c>
@@ -5453,7 +5460,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="183" spans="3:7">
+    <row r="183" spans="3:8">
       <c r="C183" s="3">
         <v>179</v>
       </c>
@@ -5470,7 +5477,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="184" spans="3:7">
+    <row r="184" spans="3:8">
       <c r="C184" s="3">
         <v>180</v>
       </c>
@@ -5487,38 +5494,55 @@
         <v>354</v>
       </c>
     </row>
-    <row r="185" spans="3:7">
+    <row r="185" spans="3:8">
       <c r="C185" s="3">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="D185" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E185" s="5">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G185" s="2" t="s">
+      <c r="G185" s="16" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="186" spans="3:7">
+    <row r="186" spans="3:8">
       <c r="C186" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E186" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>357</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>358</v>
+      </c>
+    </row>
+    <row r="187" spans="3:8">
+      <c r="C187" s="3">
+        <v>203</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="5">
+        <v>203</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="362">
   <si>
     <t>Id</t>
   </si>
@@ -1147,6 +1147,9 @@
   </si>
   <si>
     <t>浮生若梦</t>
+  </si>
+  <si>
+    <t>WJBeta182</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1361,12 +1364,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1856,7 +1859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1881,7 +1884,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2230,7 +2232,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I187"/>
+  <dimension ref="C3:I188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5507,42 +5509,57 @@
       <c r="F185" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G185" s="16" t="s">
+      <c r="G185" s="13" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="186" spans="3:8">
       <c r="C186" s="3">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E186" s="5">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="G186" s="2" t="s">
-        <v>358</v>
-      </c>
+      <c r="G186" s="13"/>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
+        <v>202</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="5">
+        <v>202</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="188" spans="3:8">
+      <c r="C188" s="3">
         <v>203</v>
       </c>
-      <c r="D187" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E187" s="5">
+      <c r="D188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="5">
         <v>203</v>
       </c>
-      <c r="F187" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="G187" s="2" t="s">
+      <c r="F188" s="5" t="s">
         <v>360</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="363">
   <si>
     <t>Id</t>
   </si>
@@ -1150,6 +1150,9 @@
   </si>
   <si>
     <t>WJBeta182</t>
+  </si>
+  <si>
+    <t>泰坦之锤</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5313,7 +5316,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="5">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>333</v>
@@ -5321,7 +5324,7 @@
       <c r="G174" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="H174" s="11"/>
+      <c r="H174" s="6"/>
     </row>
     <row r="175" spans="3:8">
       <c r="C175" s="3">
@@ -5331,7 +5334,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
@@ -5339,7 +5342,7 @@
       <c r="G175" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H175" s="11"/>
+      <c r="H175" s="6"/>
     </row>
     <row r="176" spans="3:8">
       <c r="C176" s="3">
@@ -5393,6 +5396,7 @@
       <c r="G178" s="13" t="s">
         <v>342</v>
       </c>
+      <c r="H178" s="6"/>
     </row>
     <row r="179" spans="3:8">
       <c r="C179" s="3">
@@ -5402,7 +5406,7 @@
         <v>9</v>
       </c>
       <c r="E179" s="5">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>343</v>
@@ -5410,6 +5414,7 @@
       <c r="G179" s="13" t="s">
         <v>344</v>
       </c>
+      <c r="H179" s="6"/>
     </row>
     <row r="180" spans="3:8">
       <c r="C180" s="3">
@@ -5427,6 +5432,7 @@
       <c r="G180" s="13" t="s">
         <v>346</v>
       </c>
+      <c r="H180" s="10"/>
     </row>
     <row r="181" spans="3:8">
       <c r="C181" s="3">
@@ -5436,7 +5442,7 @@
         <v>9</v>
       </c>
       <c r="E181" s="5">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>347</v>
@@ -5444,6 +5450,7 @@
       <c r="G181" s="13" t="s">
         <v>348</v>
       </c>
+      <c r="H181" s="10"/>
     </row>
     <row r="182" spans="3:8">
       <c r="C182" s="3">
@@ -5526,7 +5533,9 @@
       <c r="F186" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="G186" s="13"/>
+      <c r="G186" s="13" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
@@ -5539,10 +5548,10 @@
         <v>202</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="188" spans="3:8">
@@ -5556,10 +5565,10 @@
         <v>203</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="364">
   <si>
     <t>Id</t>
   </si>
@@ -1153,6 +1153,9 @@
   </si>
   <si>
     <t>泰坦之锤</t>
+  </si>
+  <si>
+    <t>WJBeta183</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2235,7 +2238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I188"/>
+  <dimension ref="C3:I189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5539,36 +5542,51 @@
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E187" s="5">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="G187" s="2" t="s">
-        <v>360</v>
-      </c>
+      <c r="G187" s="13"/>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
+        <v>202</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="5">
+        <v>202</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="189" spans="3:8">
+      <c r="C189" s="3">
         <v>203</v>
       </c>
-      <c r="D188" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E188" s="5">
+      <c r="D189" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="5">
         <v>203</v>
       </c>
-      <c r="F188" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="G188" s="2" t="s">
+      <c r="F189" s="5" t="s">
         <v>362</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="365">
   <si>
     <t>Id</t>
   </si>
@@ -1156,6 +1156,9 @@
   </si>
   <si>
     <t>WJBeta183</t>
+  </si>
+  <si>
+    <t>圣光神域</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1370,12 +1373,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1865,7 +1868,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1890,6 +1893,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5553,7 +5557,9 @@
       <c r="F187" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="G187" s="13"/>
+      <c r="G187" s="16" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
@@ -5566,10 +5572,10 @@
         <v>202</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="189" spans="3:8">
@@ -5583,10 +5589,10 @@
         <v>203</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="366">
   <si>
     <t>Id</t>
   </si>
@@ -1159,6 +1159,9 @@
   </si>
   <si>
     <t>圣光神域</t>
+  </si>
+  <si>
+    <t>WJBeta184</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1373,12 +1376,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1868,7 +1871,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1893,7 +1896,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2242,7 +2244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I189"/>
+  <dimension ref="C3:I190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5557,42 +5559,57 @@
       <c r="F187" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="G187" s="16" t="s">
+      <c r="G187" s="13" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E188" s="5">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="G188" s="2" t="s">
-        <v>362</v>
-      </c>
+      <c r="G188" s="13"/>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="3">
+        <v>202</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="5">
+        <v>202</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="190" spans="3:8">
+      <c r="C190" s="3">
         <v>203</v>
       </c>
-      <c r="D189" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E189" s="5">
+      <c r="D190" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="5">
         <v>203</v>
       </c>
-      <c r="F189" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="G189" s="2" t="s">
+      <c r="F190" s="5" t="s">
         <v>364</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -1376,12 +1376,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="367">
   <si>
     <t>Id</t>
   </si>
@@ -1162,6 +1162,9 @@
   </si>
   <si>
     <t>WJBeta184</t>
+  </si>
+  <si>
+    <t>炽焰神殿</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1376,12 +1379,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1871,7 +1874,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1896,6 +1899,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5576,7 +5580,9 @@
       <c r="F188" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="G188" s="13"/>
+      <c r="G188" s="16" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="3">
@@ -5589,10 +5595,10 @@
         <v>202</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="190" spans="3:8">
@@ -5606,10 +5612,10 @@
         <v>203</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="368">
   <si>
     <t>Id</t>
   </si>
@@ -1165,6 +1165,9 @@
   </si>
   <si>
     <t>炽焰神殿</t>
+  </si>
+  <si>
+    <t>WJBeta185</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1379,12 +1382,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1874,7 +1877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1899,7 +1902,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2248,7 +2250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I190"/>
+  <dimension ref="C3:I191"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5580,42 +5582,57 @@
       <c r="F188" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="G188" s="16" t="s">
+      <c r="G188" s="13" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="3">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E189" s="5">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G189" s="2" t="s">
-        <v>364</v>
-      </c>
+      <c r="G189" s="13"/>
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="3">
+        <v>202</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="5">
+        <v>202</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="191" spans="3:8">
+      <c r="C191" s="3">
         <v>203</v>
       </c>
-      <c r="D190" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E190" s="5">
+      <c r="D191" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="5">
         <v>203</v>
       </c>
-      <c r="F190" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G190" s="2" t="s">
+      <c r="F191" s="5" t="s">
         <v>366</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="369">
   <si>
     <t>Id</t>
   </si>
@@ -1168,6 +1168,9 @@
   </si>
   <si>
     <t>WJBeta185</t>
+  </si>
+  <si>
+    <t>山河万里</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1382,12 +1385,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5599,7 +5602,9 @@
       <c r="F189" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G189" s="13"/>
+      <c r="G189" s="15" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="3">
@@ -5612,10 +5617,10 @@
         <v>202</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="3:8">
@@ -5629,10 +5634,10 @@
         <v>203</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="370">
   <si>
     <t>Id</t>
   </si>
@@ -1171,6 +1171,9 @@
   </si>
   <si>
     <t>山河万里</t>
+  </si>
+  <si>
+    <t>WJBeta186</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2253,7 +2256,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I191"/>
+  <dimension ref="C3:I192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5608,36 +5611,51 @@
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="3">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E190" s="5">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="G190" s="2" t="s">
-        <v>366</v>
-      </c>
+      <c r="G190" s="13"/>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="3">
+        <v>202</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="5">
+        <v>202</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="192" spans="3:8">
+      <c r="C192" s="3">
         <v>203</v>
       </c>
-      <c r="D191" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E191" s="5">
+      <c r="D192" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="5">
         <v>203</v>
       </c>
-      <c r="F191" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="G191" s="2" t="s">
+      <c r="F192" s="5" t="s">
         <v>368</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="371">
   <si>
     <t>Id</t>
   </si>
@@ -1174,6 +1174,9 @@
   </si>
   <si>
     <t>WJBeta186</t>
+  </si>
+  <si>
+    <t>忘川彼岸</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5622,7 +5625,9 @@
       <c r="F190" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="G190" s="13"/>
+      <c r="G190" s="15" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="3">
@@ -5635,10 +5640,10 @@
         <v>202</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="192" spans="3:8">
@@ -5652,10 +5657,10 @@
         <v>203</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="373">
   <si>
     <t>Id</t>
   </si>
@@ -1177,6 +1177,12 @@
   </si>
   <si>
     <t>忘川彼岸</t>
+  </si>
+  <si>
+    <t>WJBeta187</t>
+  </si>
+  <si>
+    <t>花涧语</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2259,7 +2265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I192"/>
+  <dimension ref="C3:I193"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5240,7 +5246,7 @@
       <c r="G168" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="H168" s="10"/>
+      <c r="H168" s="11"/>
     </row>
     <row r="169" spans="3:8">
       <c r="C169" s="3">
@@ -5258,7 +5264,7 @@
       <c r="G169" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="H169" s="10"/>
+      <c r="H169" s="11"/>
     </row>
     <row r="170" spans="3:8">
       <c r="C170" s="3">
@@ -5276,7 +5282,7 @@
       <c r="G170" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="H170" s="10"/>
+      <c r="H170" s="11"/>
     </row>
     <row r="171" spans="3:8">
       <c r="C171" s="3">
@@ -5294,7 +5300,7 @@
       <c r="G171" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="H171" s="10"/>
+      <c r="H171" s="11"/>
     </row>
     <row r="172" spans="3:8">
       <c r="C172" s="3">
@@ -5304,7 +5310,7 @@
         <v>9</v>
       </c>
       <c r="E172" s="5">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>329</v>
@@ -5312,7 +5318,7 @@
       <c r="G172" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="H172" s="6"/>
+      <c r="H172" s="11"/>
     </row>
     <row r="173" spans="3:8">
       <c r="C173" s="3">
@@ -5322,7 +5328,7 @@
         <v>9</v>
       </c>
       <c r="E173" s="5">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>331</v>
@@ -5330,7 +5336,7 @@
       <c r="G173" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="H173" s="6"/>
+      <c r="H173" s="11"/>
     </row>
     <row r="174" spans="3:8">
       <c r="C174" s="3">
@@ -5340,7 +5346,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="5">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>333</v>
@@ -5348,7 +5354,7 @@
       <c r="G174" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="H174" s="6"/>
+      <c r="H174" s="11"/>
     </row>
     <row r="175" spans="3:8">
       <c r="C175" s="3">
@@ -5358,7 +5364,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="5">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>335</v>
@@ -5366,7 +5372,7 @@
       <c r="G175" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H175" s="6"/>
+      <c r="H175" s="11"/>
     </row>
     <row r="176" spans="3:8">
       <c r="C176" s="3">
@@ -5384,7 +5390,7 @@
       <c r="G176" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="H176" s="10"/>
+      <c r="H176" s="6"/>
     </row>
     <row r="177" spans="3:8">
       <c r="C177" s="3">
@@ -5402,7 +5408,7 @@
       <c r="G177" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="H177" s="10"/>
+      <c r="H177" s="6"/>
     </row>
     <row r="178" spans="3:8">
       <c r="C178" s="3">
@@ -5412,7 +5418,7 @@
         <v>9</v>
       </c>
       <c r="E178" s="5">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>341</v>
@@ -5430,7 +5436,7 @@
         <v>9</v>
       </c>
       <c r="E179" s="5">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>343</v>
@@ -5492,6 +5498,7 @@
       <c r="G182" s="13" t="s">
         <v>350</v>
       </c>
+      <c r="H182" s="6"/>
     </row>
     <row r="183" spans="3:8">
       <c r="C183" s="3">
@@ -5501,7 +5508,7 @@
         <v>9</v>
       </c>
       <c r="E183" s="5">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>351</v>
@@ -5509,6 +5516,7 @@
       <c r="G183" s="13" t="s">
         <v>352</v>
       </c>
+      <c r="H183" s="6"/>
     </row>
     <row r="184" spans="3:8">
       <c r="C184" s="3">
@@ -5526,6 +5534,7 @@
       <c r="G184" s="13" t="s">
         <v>354</v>
       </c>
+      <c r="H184" s="10"/>
     </row>
     <row r="185" spans="3:8">
       <c r="C185" s="3">
@@ -5535,7 +5544,7 @@
         <v>9</v>
       </c>
       <c r="E185" s="5">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>355</v>
@@ -5543,6 +5552,7 @@
       <c r="G185" s="13" t="s">
         <v>356</v>
       </c>
+      <c r="H185" s="10"/>
     </row>
     <row r="186" spans="3:8">
       <c r="C186" s="3">
@@ -5631,36 +5641,53 @@
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="3">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E191" s="5">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="G191" s="2" t="s">
+      <c r="G191" s="13" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E192" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>369</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>370</v>
+      </c>
+    </row>
+    <row r="193" spans="3:7">
+      <c r="C193" s="3">
+        <v>203</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="5">
+        <v>203</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="375">
   <si>
     <t>Id</t>
   </si>
@@ -1183,6 +1183,12 @@
   </si>
   <si>
     <t>花涧语</t>
+  </si>
+  <si>
+    <t>WJBeta188</t>
+  </si>
+  <si>
+    <t>九天境</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2265,7 +2271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I193"/>
+  <dimension ref="C3:I194"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5658,36 +5664,53 @@
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="3">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E192" s="5">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="G192" s="2" t="s">
+      <c r="G192" s="15" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="193" spans="3:7">
       <c r="C193" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E193" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>371</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="194" spans="3:7">
+      <c r="C194" s="3">
+        <v>203</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="5">
+        <v>203</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="376">
   <si>
     <t>Id</t>
   </si>
@@ -1189,6 +1189,9 @@
   </si>
   <si>
     <t>九天境</t>
+  </si>
+  <si>
+    <t>WJBeta189</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2271,7 +2274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I194"/>
+  <dimension ref="C3:I195"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5681,36 +5684,51 @@
     </row>
     <row r="193" spans="3:7">
       <c r="C193" s="3">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E193" s="5">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G193" s="2" t="s">
-        <v>372</v>
-      </c>
+      <c r="G193" s="15"/>
     </row>
     <row r="194" spans="3:7">
       <c r="C194" s="3">
+        <v>202</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="5">
+        <v>202</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="195" spans="3:7">
+      <c r="C195" s="3">
         <v>203</v>
       </c>
-      <c r="D194" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E194" s="5">
+      <c r="D195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="5">
         <v>203</v>
       </c>
-      <c r="F194" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="G194" s="2" t="s">
+      <c r="F195" s="5" t="s">
         <v>374</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="379">
   <si>
     <t>Id</t>
   </si>
@@ -1192,6 +1192,15 @@
   </si>
   <si>
     <t>WJBeta189</t>
+  </si>
+  <si>
+    <t>吉星高照</t>
+  </si>
+  <si>
+    <t>WJBeta190</t>
+  </si>
+  <si>
+    <t>逐月谷</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2274,7 +2283,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I195"/>
+  <dimension ref="C3:I196"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5695,40 +5704,59 @@
       <c r="F193" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G193" s="15"/>
+      <c r="G193" s="15" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="194" spans="3:7">
       <c r="C194" s="3">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E194" s="5">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="G194" s="2" t="s">
         <v>373</v>
+      </c>
+      <c r="G194" s="15" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="195" spans="3:7">
       <c r="C195" s="3">
+        <v>202</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="5">
+        <v>202</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="196" spans="3:7">
+      <c r="C196" s="3">
         <v>203</v>
       </c>
-      <c r="D195" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E195" s="5">
+      <c r="D196" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="5">
         <v>203</v>
       </c>
-      <c r="F195" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>375</v>
+      <c r="F196" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="380">
   <si>
     <t>Id</t>
   </si>
@@ -1201,6 +1201,9 @@
   </si>
   <si>
     <t>逐月谷</t>
+  </si>
+  <si>
+    <t>WJBeta191</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1415,12 +1418,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2283,7 +2286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I196"/>
+  <dimension ref="C3:I197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5727,36 +5730,51 @@
     </row>
     <row r="195" spans="3:7">
       <c r="C195" s="3">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E195" s="5">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="G195" s="2" t="s">
-        <v>376</v>
-      </c>
+      <c r="G195" s="15"/>
     </row>
     <row r="196" spans="3:7">
       <c r="C196" s="3">
+        <v>202</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="5">
+        <v>202</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="197" spans="3:7">
+      <c r="C197" s="3">
         <v>203</v>
       </c>
-      <c r="D196" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E196" s="5">
+      <c r="D197" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" s="5">
         <v>203</v>
       </c>
-      <c r="F196" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="G196" s="2" t="s">
+      <c r="F197" s="5" t="s">
         <v>378</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="381">
   <si>
     <t>Id</t>
   </si>
@@ -1204,6 +1204,9 @@
   </si>
   <si>
     <t>WJBeta191</t>
+  </si>
+  <si>
+    <t>沧澜神域</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1418,12 +1421,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4971,7 +4974,7 @@
         <v>9</v>
       </c>
       <c r="E152" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>291</v>
@@ -4979,7 +4982,7 @@
       <c r="G152" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="H152" s="10"/>
+      <c r="H152" s="11"/>
     </row>
     <row r="153" spans="3:8">
       <c r="C153" s="3">
@@ -4989,7 +4992,7 @@
         <v>9</v>
       </c>
       <c r="E153" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>292</v>
@@ -4997,7 +5000,7 @@
       <c r="G153" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="H153" s="10"/>
+      <c r="H153" s="11"/>
     </row>
     <row r="154" spans="3:8">
       <c r="C154" s="3">
@@ -5007,7 +5010,7 @@
         <v>9</v>
       </c>
       <c r="E154" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>294</v>
@@ -5015,7 +5018,7 @@
       <c r="G154" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="H154" s="10"/>
+      <c r="H154" s="11"/>
     </row>
     <row r="155" spans="3:8">
       <c r="C155" s="3">
@@ -5025,7 +5028,7 @@
         <v>9</v>
       </c>
       <c r="E155" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>296</v>
@@ -5033,7 +5036,7 @@
       <c r="G155" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="H155" s="10"/>
+      <c r="H155" s="11"/>
     </row>
     <row r="156" spans="3:8">
       <c r="C156" s="3">
@@ -5043,7 +5046,7 @@
         <v>9</v>
       </c>
       <c r="E156" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>298</v>
@@ -5051,7 +5054,7 @@
       <c r="G156" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="10"/>
+      <c r="H156" s="11"/>
     </row>
     <row r="157" spans="3:8">
       <c r="C157" s="3">
@@ -5061,7 +5064,7 @@
         <v>9</v>
       </c>
       <c r="E157" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>300</v>
@@ -5069,7 +5072,7 @@
       <c r="G157" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="10"/>
+      <c r="H157" s="11"/>
     </row>
     <row r="158" spans="3:8">
       <c r="C158" s="3">
@@ -5079,7 +5082,7 @@
         <v>9</v>
       </c>
       <c r="E158" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>302</v>
@@ -5087,7 +5090,7 @@
       <c r="G158" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="10"/>
+      <c r="H158" s="11"/>
     </row>
     <row r="159" spans="3:8">
       <c r="C159" s="3">
@@ -5097,7 +5100,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="5">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>304</v>
@@ -5105,7 +5108,7 @@
       <c r="G159" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="10"/>
+      <c r="H159" s="11"/>
     </row>
     <row r="160" spans="3:8">
       <c r="C160" s="3">
@@ -5483,7 +5486,7 @@
       <c r="G180" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="H180" s="10"/>
+      <c r="H180" s="11"/>
     </row>
     <row r="181" spans="3:8">
       <c r="C181" s="3">
@@ -5501,7 +5504,7 @@
       <c r="G181" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="H181" s="10"/>
+      <c r="H181" s="11"/>
     </row>
     <row r="182" spans="3:8">
       <c r="C182" s="3">
@@ -5511,7 +5514,7 @@
         <v>9</v>
       </c>
       <c r="E182" s="5">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>349</v>
@@ -5519,7 +5522,7 @@
       <c r="G182" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="H182" s="6"/>
+      <c r="H182" s="11"/>
     </row>
     <row r="183" spans="3:8">
       <c r="C183" s="3">
@@ -5529,7 +5532,7 @@
         <v>9</v>
       </c>
       <c r="E183" s="5">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>351</v>
@@ -5537,7 +5540,7 @@
       <c r="G183" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="H183" s="6"/>
+      <c r="H183" s="11"/>
     </row>
     <row r="184" spans="3:8">
       <c r="C184" s="3">
@@ -5591,6 +5594,7 @@
       <c r="G186" s="13" t="s">
         <v>358</v>
       </c>
+      <c r="H186" s="11"/>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
@@ -5600,7 +5604,7 @@
         <v>9</v>
       </c>
       <c r="E187" s="5">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>359</v>
@@ -5608,6 +5612,7 @@
       <c r="G187" s="13" t="s">
         <v>360</v>
       </c>
+      <c r="H187" s="11"/>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
@@ -5625,6 +5630,7 @@
       <c r="G188" s="13" t="s">
         <v>362</v>
       </c>
+      <c r="H188" s="10"/>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="3">
@@ -5634,7 +5640,7 @@
         <v>9</v>
       </c>
       <c r="E189" s="5">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>363</v>
@@ -5642,6 +5648,7 @@
       <c r="G189" s="15" t="s">
         <v>364</v>
       </c>
+      <c r="H189" s="10"/>
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="3">
@@ -5741,7 +5748,9 @@
       <c r="F195" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="G195" s="15"/>
+      <c r="G195" s="15" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="196" spans="3:7">
       <c r="C196" s="3">
@@ -5754,10 +5763,10 @@
         <v>202</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="197" spans="3:7">
@@ -5771,10 +5780,10 @@
         <v>203</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="383">
   <si>
     <t>Id</t>
   </si>
@@ -1207,6 +1207,12 @@
   </si>
   <si>
     <t>沧澜神域</t>
+  </si>
+  <si>
+    <t>WJBeta192</t>
+  </si>
+  <si>
+    <t>剑啸山河</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2289,7 +2295,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I197"/>
+  <dimension ref="C3:I198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5754,36 +5760,53 @@
     </row>
     <row r="196" spans="3:7">
       <c r="C196" s="3">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E196" s="5">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="G196" s="2" t="s">
+      <c r="G196" s="15" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="197" spans="3:7">
       <c r="C197" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E197" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>379</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>380</v>
+      </c>
+    </row>
+    <row r="198" spans="3:7">
+      <c r="C198" s="3">
+        <v>203</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="5">
+        <v>203</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="385">
   <si>
     <t>Id</t>
   </si>
@@ -1213,6 +1213,12 @@
   </si>
   <si>
     <t>剑啸山河</t>
+  </si>
+  <si>
+    <t>WJBeta193</t>
+  </si>
+  <si>
+    <t>精灵之森</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2295,7 +2301,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I198"/>
+  <dimension ref="C3:I199"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5777,36 +5783,53 @@
     </row>
     <row r="197" spans="3:7">
       <c r="C197" s="3">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E197" s="5">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="G197" s="2" t="s">
+      <c r="G197" s="15" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="198" spans="3:7">
       <c r="C198" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E198" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>381</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>382</v>
+      </c>
+    </row>
+    <row r="199" spans="3:7">
+      <c r="C199" s="3">
+        <v>203</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="5">
+        <v>203</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="386">
   <si>
     <t>Id</t>
   </si>
@@ -1219,6 +1219,9 @@
   </si>
   <si>
     <t>精灵之森</t>
+  </si>
+  <si>
+    <t>WJBeta194</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2301,7 +2304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I199"/>
+  <dimension ref="C3:I200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5800,36 +5803,51 @@
     </row>
     <row r="198" spans="3:7">
       <c r="C198" s="3">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E198" s="5">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="G198" s="2" t="s">
-        <v>382</v>
-      </c>
+      <c r="G198" s="15"/>
     </row>
     <row r="199" spans="3:7">
       <c r="C199" s="3">
+        <v>202</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="5">
+        <v>202</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="200" spans="3:7">
+      <c r="C200" s="3">
         <v>203</v>
       </c>
-      <c r="D199" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E199" s="5">
+      <c r="D200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="5">
         <v>203</v>
       </c>
-      <c r="F199" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="G199" s="2" t="s">
+      <c r="F200" s="5" t="s">
         <v>384</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="387">
   <si>
     <t>Id</t>
   </si>
@@ -1222,6 +1222,9 @@
   </si>
   <si>
     <t>WJBeta194</t>
+  </si>
+  <si>
+    <t>龙焰王座</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1436,12 +1439,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5814,7 +5817,9 @@
       <c r="F198" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="G198" s="15"/>
+      <c r="G198" s="15" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="199" spans="3:7">
       <c r="C199" s="3">
@@ -5827,10 +5832,10 @@
         <v>202</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="200" spans="3:7">
@@ -5844,10 +5849,10 @@
         <v>203</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="388">
   <si>
     <t>Id</t>
   </si>
@@ -1225,6 +1225,9 @@
   </si>
   <si>
     <t>龙焰王座</t>
+  </si>
+  <si>
+    <t>WJBeta195</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1439,12 +1442,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2307,7 +2310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I200"/>
+  <dimension ref="C3:I201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5823,36 +5826,51 @@
     </row>
     <row r="199" spans="3:7">
       <c r="C199" s="3">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D199" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E199" s="5">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="G199" s="2" t="s">
-        <v>384</v>
-      </c>
+      <c r="G199" s="15"/>
     </row>
     <row r="200" spans="3:7">
       <c r="C200" s="3">
+        <v>202</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="5">
+        <v>202</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="201" spans="3:7">
+      <c r="C201" s="3">
         <v>203</v>
       </c>
-      <c r="D200" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E200" s="5">
+      <c r="D201" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="5">
         <v>203</v>
       </c>
-      <c r="F200" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="G200" s="2" t="s">
+      <c r="F201" s="5" t="s">
         <v>386</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="16785" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="389">
   <si>
     <t>Id</t>
   </si>
@@ -1228,6 +1228,9 @@
   </si>
   <si>
     <t>WJBeta195</t>
+  </si>
+  <si>
+    <t>逐鹿天下</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5837,7 +5840,9 @@
       <c r="F199" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="G199" s="15"/>
+      <c r="G199" s="15" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="200" spans="3:7">
       <c r="C200" s="3">
@@ -5850,10 +5855,10 @@
         <v>202</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="201" spans="3:7">
@@ -5867,10 +5872,10 @@
         <v>203</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16785" windowHeight="4560"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="390">
   <si>
     <t>Id</t>
   </si>
@@ -1231,6 +1231,9 @@
   </si>
   <si>
     <t>逐鹿天下</t>
+  </si>
+  <si>
+    <t>WJBeta196</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2313,7 +2316,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I201"/>
+  <dimension ref="C3:I202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5846,36 +5849,51 @@
     </row>
     <row r="200" spans="3:7">
       <c r="C200" s="3">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D200" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E200" s="5">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="G200" s="2" t="s">
-        <v>386</v>
-      </c>
+      <c r="G200" s="15"/>
     </row>
     <row r="201" spans="3:7">
       <c r="C201" s="3">
+        <v>202</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="5">
+        <v>202</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="202" spans="3:7">
+      <c r="C202" s="3">
         <v>203</v>
       </c>
-      <c r="D201" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E201" s="5">
+      <c r="D202" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202" s="5">
         <v>203</v>
       </c>
-      <c r="F201" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="G201" s="2" t="s">
+      <c r="F202" s="5" t="s">
         <v>388</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="391">
   <si>
     <t>Id</t>
   </si>
@@ -1234,6 +1234,9 @@
   </si>
   <si>
     <t>WJBeta196</t>
+  </si>
+  <si>
+    <t>金马迎春</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1448,12 +1451,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5860,7 +5863,9 @@
       <c r="F200" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="G200" s="15"/>
+      <c r="G200" s="15" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="201" spans="3:7">
       <c r="C201" s="3">
@@ -5873,10 +5878,10 @@
         <v>202</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="202" spans="3:7">
@@ -5890,10 +5895,10 @@
         <v>203</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="393">
   <si>
     <t>Id</t>
   </si>
@@ -1237,6 +1237,12 @@
   </si>
   <si>
     <t>金马迎春</t>
+  </si>
+  <si>
+    <t>WJBeta197</t>
+  </si>
+  <si>
+    <t>御剑天涯</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1451,12 +1457,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2319,7 +2325,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I202"/>
+  <dimension ref="C3:I203"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5869,36 +5875,53 @@
     </row>
     <row r="201" spans="3:7">
       <c r="C201" s="3">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E201" s="5">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="G201" s="2" t="s">
+      <c r="G201" s="15" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="202" spans="3:7">
       <c r="C202" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E202" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>389</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>390</v>
+      </c>
+    </row>
+    <row r="203" spans="3:7">
+      <c r="C203" s="3">
+        <v>203</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" s="5">
+        <v>203</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="395">
   <si>
     <t>Id</t>
   </si>
@@ -1243,6 +1243,12 @@
   </si>
   <si>
     <t>御剑天涯</t>
+  </si>
+  <si>
+    <t>WJBeta198</t>
+  </si>
+  <si>
+    <t>马踏山河</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1267,7 +1273,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1310,6 +1316,12 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1822,16 +1834,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1840,119 +1849,122 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1977,6 +1989,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2325,7 +2338,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I203"/>
+  <dimension ref="C3:I204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5594,7 +5607,7 @@
       <c r="G184" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="H184" s="10"/>
+      <c r="H184" s="6"/>
     </row>
     <row r="185" spans="3:8">
       <c r="C185" s="3">
@@ -5612,7 +5625,7 @@
       <c r="G185" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="H185" s="10"/>
+      <c r="H185" s="6"/>
     </row>
     <row r="186" spans="3:8">
       <c r="C186" s="3">
@@ -5622,7 +5635,7 @@
         <v>9</v>
       </c>
       <c r="E186" s="5">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>357</v>
@@ -5630,7 +5643,7 @@
       <c r="G186" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="H186" s="11"/>
+      <c r="H186" s="6"/>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="3">
@@ -5640,7 +5653,7 @@
         <v>9</v>
       </c>
       <c r="E187" s="5">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>359</v>
@@ -5648,7 +5661,7 @@
       <c r="G187" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="H187" s="11"/>
+      <c r="H187" s="6"/>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="3">
@@ -5702,6 +5715,7 @@
       <c r="G190" s="15" t="s">
         <v>366</v>
       </c>
+      <c r="H190" s="7"/>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="3">
@@ -5711,7 +5725,7 @@
         <v>9</v>
       </c>
       <c r="E191" s="5">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>367</v>
@@ -5719,6 +5733,7 @@
       <c r="G191" s="13" t="s">
         <v>368</v>
       </c>
+      <c r="H191" s="7"/>
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="3">
@@ -5736,8 +5751,9 @@
       <c r="G192" s="15" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="193" spans="3:7">
+      <c r="H192" s="16"/>
+    </row>
+    <row r="193" spans="3:8">
       <c r="C193" s="3">
         <v>189</v>
       </c>
@@ -5745,7 +5761,7 @@
         <v>9</v>
       </c>
       <c r="E193" s="5">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>371</v>
@@ -5753,8 +5769,9 @@
       <c r="G193" s="15" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="194" spans="3:7">
+      <c r="H193" s="16"/>
+    </row>
+    <row r="194" spans="3:8">
       <c r="C194" s="3">
         <v>190</v>
       </c>
@@ -5770,8 +5787,9 @@
       <c r="G194" s="15" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="195" spans="3:7">
+      <c r="H194" s="6"/>
+    </row>
+    <row r="195" spans="3:8">
       <c r="C195" s="3">
         <v>191</v>
       </c>
@@ -5779,7 +5797,7 @@
         <v>9</v>
       </c>
       <c r="E195" s="5">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>375</v>
@@ -5787,8 +5805,9 @@
       <c r="G195" s="15" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="196" spans="3:7">
+      <c r="H195" s="6"/>
+    </row>
+    <row r="196" spans="3:8">
       <c r="C196" s="3">
         <v>192</v>
       </c>
@@ -5804,8 +5823,9 @@
       <c r="G196" s="15" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="197" spans="3:7">
+      <c r="H196" s="10"/>
+    </row>
+    <row r="197" spans="3:8">
       <c r="C197" s="3">
         <v>193</v>
       </c>
@@ -5813,7 +5833,7 @@
         <v>9</v>
       </c>
       <c r="E197" s="5">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>379</v>
@@ -5821,8 +5841,9 @@
       <c r="G197" s="15" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="198" spans="3:7">
+      <c r="H197" s="10"/>
+    </row>
+    <row r="198" spans="3:8">
       <c r="C198" s="3">
         <v>194</v>
       </c>
@@ -5839,7 +5860,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="199" spans="3:7">
+    <row r="199" spans="3:8">
       <c r="C199" s="3">
         <v>195</v>
       </c>
@@ -5856,7 +5877,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="200" spans="3:7">
+    <row r="200" spans="3:8">
       <c r="C200" s="3">
         <v>196</v>
       </c>
@@ -5873,7 +5894,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="201" spans="3:7">
+    <row r="201" spans="3:8">
       <c r="C201" s="3">
         <v>197</v>
       </c>
@@ -5890,38 +5911,55 @@
         <v>388</v>
       </c>
     </row>
-    <row r="202" spans="3:7">
+    <row r="202" spans="3:8">
       <c r="C202" s="3">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E202" s="5">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="G202" s="2" t="s">
+      <c r="G202" s="15" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="203" spans="3:7">
+    <row r="203" spans="3:8">
       <c r="C203" s="3">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E203" s="5">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>391</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>392</v>
+      </c>
+    </row>
+    <row r="204" spans="3:8">
+      <c r="C204" s="3">
+        <v>203</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204" s="5">
+        <v>203</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="396">
   <si>
     <t>Id</t>
   </si>
@@ -1249,6 +1249,9 @@
   </si>
   <si>
     <t>马踏山河</t>
+  </si>
+  <si>
+    <t>WJBeta199</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2338,7 +2341,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I204"/>
+  <dimension ref="C3:I205"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5930,36 +5933,51 @@
     </row>
     <row r="203" spans="3:8">
       <c r="C203" s="3">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E203" s="5">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="G203" s="2" t="s">
-        <v>392</v>
-      </c>
+      <c r="G203" s="15"/>
     </row>
     <row r="204" spans="3:8">
       <c r="C204" s="3">
+        <v>202</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204" s="5">
+        <v>202</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="205" spans="3:8">
+      <c r="C205" s="3">
         <v>203</v>
       </c>
-      <c r="D204" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E204" s="5">
+      <c r="D205" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="5">
         <v>203</v>
       </c>
-      <c r="F204" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="G204" s="2" t="s">
+      <c r="F205" s="5" t="s">
         <v>394</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="397">
   <si>
     <t>Id</t>
   </si>
@@ -1252,6 +1252,9 @@
   </si>
   <si>
     <t>WJBeta199</t>
+  </si>
+  <si>
+    <t>烽火逐鹿</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5944,7 +5947,9 @@
       <c r="F203" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="G203" s="15"/>
+      <c r="G203" s="15" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="204" spans="3:8">
       <c r="C204" s="3">
@@ -5957,10 +5962,10 @@
         <v>202</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="205" spans="3:8">
@@ -5974,10 +5979,10 @@
         <v>203</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="398">
   <si>
     <t>Id</t>
   </si>
@@ -1255,6 +1255,9 @@
   </si>
   <si>
     <t>烽火逐鹿</t>
+  </si>
+  <si>
+    <t>WJBeta200</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -2344,7 +2347,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I205"/>
+  <dimension ref="C3:I206"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5953,36 +5956,51 @@
     </row>
     <row r="204" spans="3:8">
       <c r="C204" s="3">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D204" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E204" s="5">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="G204" s="2" t="s">
-        <v>394</v>
-      </c>
+      <c r="G204" s="15"/>
     </row>
     <row r="205" spans="3:8">
       <c r="C205" s="3">
+        <v>202</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="5">
+        <v>202</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="206" spans="3:8">
+      <c r="C206" s="3">
         <v>203</v>
       </c>
-      <c r="D205" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E205" s="5">
+      <c r="D206" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="5">
         <v>203</v>
       </c>
-      <c r="F205" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="G205" s="2" t="s">
+      <c r="F206" s="5" t="s">
         <v>396</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="399">
   <si>
     <t>Id</t>
   </si>
@@ -1258,6 +1258,9 @@
   </si>
   <si>
     <t>WJBeta200</t>
+  </si>
+  <si>
+    <t>梦幻湖畔</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -5967,7 +5970,9 @@
       <c r="F204" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="G204" s="15"/>
+      <c r="G204" s="15" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="205" spans="3:8">
       <c r="C205" s="3">
@@ -5980,10 +5985,10 @@
         <v>202</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="206" spans="3:8">
@@ -5997,10 +6002,10 @@
         <v>203</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="401">
   <si>
     <t>Id</t>
   </si>
@@ -1273,6 +1273,12 @@
   </si>
   <si>
     <t>#机器人</t>
+  </si>
+  <si>
+    <t>201-210是特殊区服</t>
+  </si>
+  <si>
+    <t>WJBeta211</t>
   </si>
 </sst>
 </file>
@@ -1300,15 +1306,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1976,32 +1982,39 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2350,3663 +2363,3681 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I206"/>
+  <dimension ref="A3:I207"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="41.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="33.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="23.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="41.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="33.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21" style="4" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3"/>
+    <col min="8" max="8" width="23.75" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.375" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:8">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="3:8">
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="3:8">
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="3:8">
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="6">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="3:8">
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="6">
         <v>3</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="3:8">
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="6">
         <v>3</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="3:8">
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>4</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="6">
         <v>3</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="3:8">
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>5</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6">
         <v>5</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="3:8">
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>6</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="6">
         <v>5</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="3:8">
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <v>7</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6">
         <v>5</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="3:8">
-      <c r="C13" s="3">
+      <c r="C13" s="4">
         <v>8</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="6">
         <v>5</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="3:8">
-      <c r="C14" s="3">
-        <v>9</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="3">
-        <v>9</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="C14" s="4">
+        <v>9</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="4">
+        <v>9</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="3:8">
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <v>10</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="5">
-        <v>9</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="D15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="6">
+        <v>9</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="3:8">
-      <c r="C16" s="5">
+      <c r="C16" s="6">
         <v>11</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="3">
-        <v>9</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="D16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="4">
+        <v>9</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="3">
+      <c r="C17" s="4">
         <v>12</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="4">
         <v>12</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="6"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="3">
+      <c r="C18" s="4">
         <v>13</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="6">
         <v>12</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="3">
+      <c r="C19" s="4">
         <v>14</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="6">
         <v>12</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="3:8">
-      <c r="C20" s="5">
+      <c r="C20" s="6">
         <v>15</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="6">
         <v>12</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>16</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="5">
+      <c r="D21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="6">
         <v>12</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="3">
+      <c r="C22" s="4">
         <v>17</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="D22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="6">
         <v>12</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="3">
+      <c r="C23" s="4">
         <v>18</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="5">
+      <c r="D23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="6">
         <v>12</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H23" s="7"/>
+      <c r="H23" s="8"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="3">
+      <c r="C24" s="4">
         <v>19</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="5">
+      <c r="D24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="6">
         <v>12</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="8"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="3">
+      <c r="C25" s="4">
         <v>20</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="6">
         <v>12</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="3">
+      <c r="C26" s="4">
         <v>21</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="5">
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="6">
         <v>12</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="6"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="3">
+      <c r="C27" s="4">
         <v>22</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="4">
         <v>12</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H27" s="7"/>
+      <c r="H27" s="8"/>
     </row>
     <row r="28" spans="3:8">
-      <c r="C28" s="3">
+      <c r="C28" s="4">
         <v>23</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="D28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="6">
         <v>12</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H28" s="7"/>
+      <c r="H28" s="8"/>
     </row>
     <row r="29" spans="3:8">
-      <c r="C29" s="3">
+      <c r="C29" s="4">
         <v>24</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="5">
+      <c r="D29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="6">
         <v>12</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H29" s="7"/>
+      <c r="H29" s="8"/>
     </row>
     <row r="30" spans="3:8">
-      <c r="C30" s="3">
+      <c r="C30" s="4">
         <v>25</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="5">
+      <c r="D30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="6">
         <v>12</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H30" s="7"/>
+      <c r="H30" s="8"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="3">
+      <c r="C31" s="4">
         <v>26</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="5">
+      <c r="D31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="6">
         <v>12</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H31" s="6"/>
+      <c r="H31" s="7"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="3">
+      <c r="C32" s="4">
         <v>27</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="5">
+      <c r="D32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="6">
         <v>12</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H32" s="6"/>
+      <c r="H32" s="7"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="3">
+      <c r="C33" s="4">
         <v>28</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="5">
+      <c r="D33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="6">
         <v>12</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H33" s="6"/>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" spans="3:8">
-      <c r="C34" s="3">
+      <c r="C34" s="4">
         <v>29</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="5">
+      <c r="D34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="6">
         <v>12</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H34" s="7"/>
+      <c r="H34" s="8"/>
     </row>
     <row r="35" spans="3:8">
-      <c r="C35" s="3">
+      <c r="C35" s="4">
         <v>30</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="5">
+      <c r="D35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="6">
         <v>12</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="6"/>
+      <c r="H35" s="7"/>
     </row>
     <row r="36" spans="3:8">
-      <c r="C36" s="3">
+      <c r="C36" s="4">
         <v>31</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="5">
+      <c r="D36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="6">
         <v>12</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H36" s="6"/>
+      <c r="H36" s="7"/>
     </row>
     <row r="37" spans="3:8">
-      <c r="C37" s="3">
+      <c r="C37" s="4">
         <v>32</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="5">
+      <c r="D37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="6">
         <v>32</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H37" s="8"/>
+      <c r="H37" s="9"/>
     </row>
     <row r="38" spans="3:8">
-      <c r="C38" s="3">
+      <c r="C38" s="4">
         <v>33</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="5">
+      <c r="D38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="6">
         <v>32</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H38" s="8"/>
+      <c r="H38" s="9"/>
     </row>
     <row r="39" spans="3:8">
-      <c r="C39" s="3">
+      <c r="C39" s="4">
         <v>34</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="5">
+      <c r="D39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="6">
         <v>32</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H39" s="8"/>
+      <c r="H39" s="9"/>
     </row>
     <row r="40" spans="3:8">
-      <c r="C40" s="3">
+      <c r="C40" s="4">
         <v>35</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="5">
+      <c r="D40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="6">
         <v>32</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H40" s="8"/>
+      <c r="H40" s="9"/>
     </row>
     <row r="41" spans="3:8">
-      <c r="C41" s="3">
+      <c r="C41" s="4">
         <v>36</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="5">
+      <c r="D41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="6">
         <v>32</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H41" s="8"/>
+      <c r="H41" s="9"/>
     </row>
     <row r="42" spans="3:8">
-      <c r="C42" s="3">
+      <c r="C42" s="4">
         <v>37</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="5">
+      <c r="D42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="6">
         <v>32</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H42" s="8"/>
+      <c r="H42" s="9"/>
     </row>
     <row r="43" spans="3:8">
-      <c r="C43" s="3">
+      <c r="C43" s="4">
         <v>38</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="5">
+      <c r="D43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="6">
         <v>32</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H43" s="9"/>
+      <c r="H43" s="10"/>
     </row>
     <row r="44" spans="3:8">
-      <c r="C44" s="3">
+      <c r="C44" s="4">
         <v>39</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="5">
+      <c r="D44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="6">
         <v>32</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H44" s="9"/>
+      <c r="H44" s="10"/>
     </row>
     <row r="45" spans="3:8">
-      <c r="C45" s="3">
+      <c r="C45" s="4">
         <v>40</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="5">
+      <c r="D45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="6">
         <v>32</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H45" s="8"/>
+      <c r="H45" s="9"/>
     </row>
     <row r="46" spans="3:8">
-      <c r="C46" s="3">
+      <c r="C46" s="4">
         <v>41</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="5">
+      <c r="D46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="6">
         <v>32</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H46" s="8"/>
+      <c r="H46" s="9"/>
     </row>
     <row r="47" spans="3:8">
-      <c r="C47" s="3">
+      <c r="C47" s="4">
         <v>42</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="5">
+      <c r="D47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="6">
         <v>32</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H47" s="8"/>
+      <c r="H47" s="9"/>
     </row>
     <row r="48" spans="3:8">
-      <c r="C48" s="3">
+      <c r="C48" s="4">
         <v>43</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="5">
+      <c r="D48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="6">
         <v>32</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H48" s="8"/>
+      <c r="H48" s="9"/>
     </row>
     <row r="49" spans="3:8">
-      <c r="C49" s="3">
+      <c r="C49" s="4">
         <v>44</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="5">
+      <c r="D49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="6">
         <v>32</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H49" s="8"/>
+      <c r="H49" s="9"/>
     </row>
     <row r="50" spans="3:8">
-      <c r="C50" s="3">
+      <c r="C50" s="4">
         <v>45</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="5">
+      <c r="D50" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="6">
         <v>32</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H50" s="8"/>
+      <c r="H50" s="9"/>
     </row>
     <row r="51" spans="3:8">
-      <c r="C51" s="3">
+      <c r="C51" s="4">
         <v>46</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="5">
+      <c r="D51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="6">
         <v>32</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H51" s="8"/>
+      <c r="H51" s="9"/>
     </row>
     <row r="52" ht="13" customHeight="1" spans="3:8">
-      <c r="C52" s="3">
+      <c r="C52" s="4">
         <v>47</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="5">
+      <c r="D52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="6">
         <v>32</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H52" s="8"/>
+      <c r="H52" s="9"/>
     </row>
     <row r="53" spans="3:8">
-      <c r="C53" s="3">
+      <c r="C53" s="4">
         <v>48</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="5">
+      <c r="D53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="6">
         <v>48</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H53" s="10"/>
+      <c r="H53" s="11"/>
     </row>
     <row r="54" spans="3:8">
-      <c r="C54" s="3">
+      <c r="C54" s="4">
         <v>49</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="5">
+      <c r="D54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="6">
         <v>48</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H54" s="10"/>
+      <c r="H54" s="11"/>
     </row>
     <row r="55" spans="3:8">
-      <c r="C55" s="3">
+      <c r="C55" s="4">
         <v>50</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="5">
+      <c r="D55" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="6">
         <v>48</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H55" s="10"/>
+      <c r="H55" s="11"/>
     </row>
     <row r="56" spans="3:8">
-      <c r="C56" s="3">
+      <c r="C56" s="4">
         <v>51</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="5">
+      <c r="D56" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="6">
         <v>48</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H56" s="10"/>
+      <c r="H56" s="11"/>
     </row>
     <row r="57" spans="3:8">
-      <c r="C57" s="3">
+      <c r="C57" s="4">
         <v>52</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="5">
+      <c r="D57" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="6">
         <v>48</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H57" s="10"/>
+      <c r="H57" s="11"/>
     </row>
     <row r="58" spans="3:8">
-      <c r="C58" s="3">
+      <c r="C58" s="4">
         <v>53</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="5">
+      <c r="D58" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="6">
         <v>48</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H58" s="10"/>
+      <c r="H58" s="11"/>
     </row>
     <row r="59" spans="3:8">
-      <c r="C59" s="3">
+      <c r="C59" s="4">
         <v>54</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="5">
+      <c r="D59" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="6">
         <v>48</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="H59" s="10"/>
+      <c r="H59" s="11"/>
     </row>
     <row r="60" spans="3:8">
-      <c r="C60" s="3">
+      <c r="C60" s="4">
         <v>55</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="5">
+      <c r="D60" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="6">
         <v>48</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H60" s="10"/>
+      <c r="H60" s="11"/>
     </row>
     <row r="61" spans="3:8">
-      <c r="C61" s="3">
+      <c r="C61" s="4">
         <v>56</v>
       </c>
-      <c r="D61" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="5">
+      <c r="D61" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="6">
         <v>48</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H61" s="10"/>
+      <c r="H61" s="11"/>
     </row>
     <row r="62" spans="3:8">
-      <c r="C62" s="3">
+      <c r="C62" s="4">
         <v>57</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="5">
+      <c r="D62" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="6">
         <v>48</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G62" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H62" s="10"/>
+      <c r="H62" s="11"/>
     </row>
     <row r="63" spans="3:8">
-      <c r="C63" s="3">
+      <c r="C63" s="4">
         <v>58</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="5">
+      <c r="D63" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="6">
         <v>48</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H63" s="10"/>
+      <c r="H63" s="11"/>
     </row>
     <row r="64" spans="3:8">
-      <c r="C64" s="3">
+      <c r="C64" s="4">
         <v>59</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="5">
+      <c r="D64" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="6">
         <v>48</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G64" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H64" s="10"/>
+      <c r="H64" s="11"/>
     </row>
     <row r="65" spans="3:8">
-      <c r="C65" s="3">
+      <c r="C65" s="4">
         <v>60</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="5">
+      <c r="D65" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="6">
         <v>48</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H65" s="10"/>
+      <c r="H65" s="11"/>
     </row>
     <row r="66" spans="3:8">
-      <c r="C66" s="3">
+      <c r="C66" s="4">
         <v>61</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="5">
+      <c r="D66" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="6">
         <v>48</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H66" s="10"/>
+      <c r="H66" s="11"/>
     </row>
     <row r="67" spans="3:8">
-      <c r="C67" s="3">
+      <c r="C67" s="4">
         <v>62</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="5">
+      <c r="D67" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="6">
         <v>48</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="F67" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H67" s="10"/>
+      <c r="H67" s="11"/>
     </row>
     <row r="68" spans="3:8">
-      <c r="C68" s="3">
+      <c r="C68" s="4">
         <v>63</v>
       </c>
-      <c r="D68" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="5">
+      <c r="D68" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="6">
         <v>48</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F68" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="G68" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H68" s="10"/>
+      <c r="H68" s="11"/>
     </row>
     <row r="69" spans="3:8">
-      <c r="C69" s="3">
+      <c r="C69" s="4">
         <v>64</v>
       </c>
-      <c r="D69" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" s="5">
+      <c r="D69" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="6">
         <v>64</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H69" s="11"/>
+      <c r="H69" s="12"/>
     </row>
     <row r="70" spans="3:8">
-      <c r="C70" s="3">
+      <c r="C70" s="4">
         <v>65</v>
       </c>
-      <c r="D70" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="5">
+      <c r="D70" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="6">
         <v>64</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H70" s="11"/>
+      <c r="H70" s="12"/>
     </row>
     <row r="71" spans="3:8">
-      <c r="C71" s="3">
+      <c r="C71" s="4">
         <v>66</v>
       </c>
-      <c r="D71" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="5">
+      <c r="D71" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="6">
         <v>64</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H71" s="11"/>
+      <c r="H71" s="12"/>
     </row>
     <row r="72" spans="3:8">
-      <c r="C72" s="3">
+      <c r="C72" s="4">
         <v>67</v>
       </c>
-      <c r="D72" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E72" s="5">
+      <c r="D72" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="6">
         <v>64</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="G72" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H72" s="11"/>
+      <c r="H72" s="12"/>
     </row>
     <row r="73" spans="3:8">
-      <c r="C73" s="3">
+      <c r="C73" s="4">
         <v>68</v>
       </c>
-      <c r="D73" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="5">
+      <c r="D73" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="6">
         <v>64</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H73" s="11"/>
+      <c r="H73" s="12"/>
     </row>
     <row r="74" spans="3:8">
-      <c r="C74" s="3">
+      <c r="C74" s="4">
         <v>69</v>
       </c>
-      <c r="D74" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="5">
+      <c r="D74" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="6">
         <v>64</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H74" s="11"/>
+      <c r="H74" s="12"/>
     </row>
     <row r="75" spans="3:8">
-      <c r="C75" s="3">
+      <c r="C75" s="4">
         <v>70</v>
       </c>
-      <c r="D75" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="5">
+      <c r="D75" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="6">
         <v>64</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H75" s="11"/>
+      <c r="H75" s="12"/>
     </row>
     <row r="76" spans="3:8">
-      <c r="C76" s="3">
+      <c r="C76" s="4">
         <v>71</v>
       </c>
-      <c r="D76" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" s="5">
+      <c r="D76" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="6">
         <v>64</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H76" s="11"/>
+      <c r="H76" s="12"/>
     </row>
     <row r="77" spans="3:8">
-      <c r="C77" s="3">
+      <c r="C77" s="4">
         <v>72</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" s="5">
+      <c r="D77" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="6">
         <v>64</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H77" s="11"/>
+      <c r="H77" s="12"/>
     </row>
     <row r="78" spans="3:8">
-      <c r="C78" s="3">
+      <c r="C78" s="4">
         <v>73</v>
       </c>
-      <c r="D78" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" s="5">
+      <c r="D78" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="6">
         <v>64</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F78" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H78" s="11"/>
+      <c r="H78" s="12"/>
     </row>
     <row r="79" spans="3:8">
-      <c r="C79" s="3">
+      <c r="C79" s="4">
         <v>74</v>
       </c>
-      <c r="D79" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E79" s="5">
+      <c r="D79" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="6">
         <v>64</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="F79" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G79" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H79" s="11"/>
+      <c r="H79" s="12"/>
     </row>
     <row r="80" spans="3:8">
-      <c r="C80" s="3">
+      <c r="C80" s="4">
         <v>75</v>
       </c>
-      <c r="D80" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E80" s="5">
+      <c r="D80" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="6">
         <v>64</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="F80" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H80" s="11"/>
+      <c r="H80" s="12"/>
     </row>
     <row r="81" spans="3:9">
-      <c r="C81" s="3">
+      <c r="C81" s="4">
         <v>76</v>
       </c>
-      <c r="D81" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" s="5">
+      <c r="D81" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="6">
         <v>64</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="F81" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H81" s="11"/>
+      <c r="H81" s="12"/>
     </row>
     <row r="82" spans="3:9">
-      <c r="C82" s="3">
+      <c r="C82" s="4">
         <v>77</v>
       </c>
-      <c r="D82" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E82" s="5">
+      <c r="D82" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="6">
         <v>64</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F82" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H82" s="11"/>
+      <c r="H82" s="12"/>
     </row>
     <row r="83" spans="3:9">
-      <c r="C83" s="3">
+      <c r="C83" s="4">
         <v>78</v>
       </c>
-      <c r="D83" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E83" s="5">
+      <c r="D83" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="6">
         <v>64</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="F83" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G83" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H83" s="11"/>
+      <c r="H83" s="12"/>
     </row>
     <row r="84" spans="3:9">
-      <c r="C84" s="3">
+      <c r="C84" s="4">
         <v>79</v>
       </c>
-      <c r="D84" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" s="5">
+      <c r="D84" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="6">
         <v>64</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F84" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H84" s="11"/>
+      <c r="H84" s="12"/>
     </row>
     <row r="85" spans="3:9">
-      <c r="C85" s="3">
+      <c r="C85" s="4">
         <v>80</v>
       </c>
-      <c r="D85" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" s="5">
+      <c r="D85" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="6">
         <v>80</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="F85" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G85" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H85" s="6"/>
+      <c r="H85" s="7"/>
     </row>
     <row r="86" spans="3:9">
-      <c r="C86" s="3">
+      <c r="C86" s="4">
         <v>81</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" s="5">
+      <c r="D86" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="6">
         <v>80</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="F86" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H86" s="6"/>
+      <c r="H86" s="7"/>
     </row>
     <row r="87" spans="3:9">
-      <c r="C87" s="3">
+      <c r="C87" s="4">
         <v>82</v>
       </c>
-      <c r="D87" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87" s="5">
+      <c r="D87" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="6">
         <v>80</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="F87" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H87" s="6"/>
+      <c r="H87" s="7"/>
     </row>
     <row r="88" spans="3:9">
-      <c r="C88" s="3">
+      <c r="C88" s="4">
         <v>83</v>
       </c>
-      <c r="D88" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" s="5">
+      <c r="D88" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="6">
         <v>80</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="F88" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G88" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H88" s="6"/>
+      <c r="H88" s="7"/>
     </row>
     <row r="89" spans="3:9">
-      <c r="C89" s="3">
+      <c r="C89" s="4">
         <v>84</v>
       </c>
-      <c r="D89" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" s="5">
+      <c r="D89" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="6">
         <v>84</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F89" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G89" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I89" s="6"/>
+      <c r="I89" s="7"/>
     </row>
     <row r="90" spans="3:9">
-      <c r="C90" s="3">
+      <c r="C90" s="4">
         <v>85</v>
       </c>
-      <c r="D90" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" s="5">
+      <c r="D90" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="6">
         <v>80</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F90" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G90" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H90" s="6"/>
+      <c r="H90" s="7"/>
     </row>
     <row r="91" spans="3:9">
-      <c r="C91" s="3">
+      <c r="C91" s="4">
         <v>86</v>
       </c>
-      <c r="D91" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" s="5">
+      <c r="D91" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="6">
         <v>80</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="F91" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="H91" s="6"/>
+      <c r="H91" s="7"/>
     </row>
     <row r="92" spans="3:9">
-      <c r="C92" s="3">
+      <c r="C92" s="4">
         <v>87</v>
       </c>
-      <c r="D92" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="5">
+      <c r="D92" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="6">
         <v>80</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="F92" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G92" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H92" s="6"/>
+      <c r="H92" s="7"/>
     </row>
     <row r="93" spans="3:9">
-      <c r="C93" s="3">
+      <c r="C93" s="4">
         <v>88</v>
       </c>
-      <c r="D93" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="5">
+      <c r="D93" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="6">
         <v>80</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="F93" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="G93" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H93" s="6"/>
+      <c r="H93" s="7"/>
     </row>
     <row r="94" spans="3:9">
-      <c r="C94" s="3">
+      <c r="C94" s="4">
         <v>89</v>
       </c>
-      <c r="D94" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" s="5">
+      <c r="D94" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="6">
         <v>89</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F94" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G94" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="H94" s="10"/>
+      <c r="H94" s="11"/>
     </row>
     <row r="95" spans="3:9">
-      <c r="C95" s="3">
+      <c r="C95" s="4">
         <v>90</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="5">
+      <c r="D95" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="6">
         <v>89</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F95" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G95" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="H95" s="10"/>
+      <c r="H95" s="11"/>
     </row>
     <row r="96" spans="3:9">
-      <c r="C96" s="3">
+      <c r="C96" s="4">
         <v>91</v>
       </c>
-      <c r="D96" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="5">
+      <c r="D96" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="6">
         <v>89</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="F96" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="G96" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="H96" s="10"/>
+      <c r="H96" s="11"/>
     </row>
     <row r="97" spans="3:8">
-      <c r="C97" s="3">
+      <c r="C97" s="4">
         <v>92</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E97" s="5">
+      <c r="D97" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="6">
         <v>89</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F97" s="6" t="s">
         <v>185</v>
       </c>
       <c r="G97" t="s">
         <v>186</v>
       </c>
-      <c r="H97" s="10"/>
+      <c r="H97" s="11"/>
     </row>
     <row r="98" spans="3:8">
-      <c r="C98" s="3">
+      <c r="C98" s="4">
         <v>93</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" s="5">
+      <c r="D98" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="6">
         <v>89</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="F98" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G98" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="H98" s="10"/>
+      <c r="H98" s="11"/>
     </row>
     <row r="99" spans="3:8">
-      <c r="C99" s="3">
+      <c r="C99" s="4">
         <v>94</v>
       </c>
-      <c r="D99" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E99" s="5">
+      <c r="D99" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="6">
         <v>89</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="F99" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="G99" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="H99" s="10"/>
+      <c r="H99" s="11"/>
     </row>
     <row r="100" spans="3:8">
-      <c r="C100" s="3">
+      <c r="C100" s="4">
         <v>95</v>
       </c>
-      <c r="D100" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E100" s="5">
+      <c r="D100" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="6">
         <v>89</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="F100" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="G100" s="2" t="s">
+      <c r="G100" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H100" s="10"/>
+      <c r="H100" s="11"/>
     </row>
     <row r="101" spans="3:8">
-      <c r="C101" s="3">
+      <c r="C101" s="4">
         <v>96</v>
       </c>
-      <c r="D101" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" s="5">
+      <c r="D101" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="6">
         <v>89</v>
       </c>
-      <c r="F101" s="5" t="s">
+      <c r="F101" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="G101" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H101" s="10"/>
+      <c r="H101" s="11"/>
     </row>
     <row r="102" spans="3:8">
-      <c r="C102" s="3">
+      <c r="C102" s="4">
         <v>97</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E102" s="5">
+      <c r="D102" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="6">
         <v>89</v>
       </c>
-      <c r="F102" s="5" t="s">
+      <c r="F102" s="6" t="s">
         <v>195</v>
       </c>
       <c r="G102" t="s">
         <v>196</v>
       </c>
-      <c r="H102" s="10"/>
+      <c r="H102" s="11"/>
     </row>
     <row r="103" spans="3:8">
-      <c r="C103" s="3">
+      <c r="C103" s="4">
         <v>98</v>
       </c>
-      <c r="D103" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E103" s="5">
+      <c r="D103" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="6">
         <v>89</v>
       </c>
-      <c r="F103" s="5" t="s">
+      <c r="F103" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G103" s="2" t="s">
+      <c r="G103" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="H103" s="10"/>
+      <c r="H103" s="11"/>
     </row>
     <row r="104" spans="3:8">
-      <c r="C104" s="3">
+      <c r="C104" s="4">
         <v>99</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" s="5">
+      <c r="D104" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="6">
         <v>89</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F104" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="G104" s="2" t="s">
+      <c r="G104" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H104" s="10"/>
+      <c r="H104" s="11"/>
     </row>
     <row r="105" spans="3:8">
-      <c r="C105" s="3">
+      <c r="C105" s="4">
         <v>100</v>
       </c>
-      <c r="D105" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E105" s="5">
+      <c r="D105" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="6">
         <v>89</v>
       </c>
-      <c r="F105" s="5" t="s">
+      <c r="F105" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="G105" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H105" s="10"/>
+      <c r="H105" s="11"/>
     </row>
     <row r="106" spans="3:8">
-      <c r="C106" s="3">
+      <c r="C106" s="4">
         <v>101</v>
       </c>
-      <c r="D106" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E106" s="5">
+      <c r="D106" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="6">
         <v>89</v>
       </c>
-      <c r="F106" s="5" t="s">
+      <c r="F106" s="6" t="s">
         <v>203</v>
       </c>
       <c r="G106" t="s">
         <v>204</v>
       </c>
-      <c r="H106" s="10"/>
+      <c r="H106" s="11"/>
     </row>
     <row r="107" spans="3:8">
-      <c r="C107" s="3">
+      <c r="C107" s="4">
         <v>102</v>
       </c>
-      <c r="D107" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" s="5">
+      <c r="D107" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="6">
         <v>89</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="F107" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="G107" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H107" s="10"/>
+      <c r="H107" s="11"/>
     </row>
     <row r="108" spans="3:8">
-      <c r="C108" s="3">
+      <c r="C108" s="4">
         <v>103</v>
       </c>
-      <c r="D108" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="5">
+      <c r="D108" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="6">
         <v>89</v>
       </c>
-      <c r="F108" s="5" t="s">
+      <c r="F108" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="G108" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="H108" s="10"/>
+      <c r="H108" s="11"/>
     </row>
     <row r="109" spans="3:8">
-      <c r="C109" s="3">
+      <c r="C109" s="4">
         <v>104</v>
       </c>
-      <c r="D109" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" s="5">
+      <c r="D109" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="6">
         <v>89</v>
       </c>
-      <c r="F109" s="5" t="s">
+      <c r="F109" s="6" t="s">
         <v>209</v>
       </c>
       <c r="G109" t="s">
         <v>210</v>
       </c>
-      <c r="H109" s="10"/>
+      <c r="H109" s="11"/>
     </row>
     <row r="110" spans="3:8">
-      <c r="C110" s="3">
+      <c r="C110" s="4">
         <v>105</v>
       </c>
-      <c r="D110" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E110" s="5">
+      <c r="D110" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="6">
         <v>105</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="F110" s="6" t="s">
         <v>211</v>
       </c>
       <c r="G110" t="s">
         <v>212</v>
       </c>
-      <c r="H110" s="12"/>
+      <c r="H110" s="13"/>
     </row>
     <row r="111" spans="3:8">
-      <c r="C111" s="3">
+      <c r="C111" s="4">
         <v>106</v>
       </c>
-      <c r="D111" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E111" s="5">
+      <c r="D111" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="6">
         <v>105</v>
       </c>
-      <c r="F111" s="5" t="s">
+      <c r="F111" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G111" s="2" t="s">
+      <c r="G111" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="H111" s="12"/>
+      <c r="H111" s="13"/>
     </row>
     <row r="112" spans="3:8">
-      <c r="C112" s="3">
+      <c r="C112" s="4">
         <v>107</v>
       </c>
-      <c r="D112" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" s="5">
+      <c r="D112" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="6">
         <v>105</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="F112" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="G112" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="H112" s="12"/>
+      <c r="H112" s="13"/>
     </row>
     <row r="113" spans="3:8">
-      <c r="C113" s="3">
+      <c r="C113" s="4">
         <v>108</v>
       </c>
-      <c r="D113" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="5">
+      <c r="D113" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="6">
         <v>105</v>
       </c>
-      <c r="F113" s="5" t="s">
+      <c r="F113" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="G113" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H113" s="12"/>
+      <c r="H113" s="13"/>
     </row>
     <row r="114" spans="3:8">
-      <c r="C114" s="3">
+      <c r="C114" s="4">
         <v>109</v>
       </c>
-      <c r="D114" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114" s="5">
+      <c r="D114" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="6">
         <v>105</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="F114" s="6" t="s">
         <v>219</v>
       </c>
       <c r="G114" t="s">
         <v>220</v>
       </c>
-      <c r="H114" s="12"/>
+      <c r="H114" s="13"/>
     </row>
     <row r="115" spans="3:8">
-      <c r="C115" s="3">
+      <c r="C115" s="4">
         <v>110</v>
       </c>
-      <c r="D115" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="5">
+      <c r="D115" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="6">
         <v>105</v>
       </c>
-      <c r="F115" s="5" t="s">
+      <c r="F115" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G115" s="2" t="s">
+      <c r="G115" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="H115" s="12"/>
+      <c r="H115" s="13"/>
     </row>
     <row r="116" spans="3:8">
-      <c r="C116" s="3">
+      <c r="C116" s="4">
         <v>111</v>
       </c>
-      <c r="D116" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="5">
+      <c r="D116" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="6">
         <v>105</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="F116" s="6" t="s">
         <v>223</v>
       </c>
       <c r="G116" t="s">
         <v>224</v>
       </c>
-      <c r="H116" s="12"/>
+      <c r="H116" s="13"/>
     </row>
     <row r="117" spans="3:8">
-      <c r="C117" s="3">
+      <c r="C117" s="4">
         <v>112</v>
       </c>
-      <c r="D117" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" s="5">
+      <c r="D117" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="6">
         <v>105</v>
       </c>
-      <c r="F117" s="5" t="s">
+      <c r="F117" s="6" t="s">
         <v>225</v>
       </c>
       <c r="G117" t="s">
         <v>226</v>
       </c>
-      <c r="H117" s="12"/>
+      <c r="H117" s="13"/>
     </row>
     <row r="118" spans="3:8">
-      <c r="C118" s="3">
+      <c r="C118" s="4">
         <v>113</v>
       </c>
-      <c r="D118" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="5">
+      <c r="D118" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="6">
         <v>105</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="F118" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="G118" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="H118" s="12"/>
+      <c r="H118" s="13"/>
     </row>
     <row r="119" spans="3:8">
-      <c r="C119" s="3">
+      <c r="C119" s="4">
         <v>114</v>
       </c>
-      <c r="D119" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E119" s="5">
+      <c r="D119" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="6">
         <v>105</v>
       </c>
-      <c r="F119" s="5" t="s">
+      <c r="F119" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G119" s="13" t="s">
+      <c r="G119" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="H119" s="12"/>
+      <c r="H119" s="13"/>
     </row>
     <row r="120" spans="3:8">
-      <c r="C120" s="3">
+      <c r="C120" s="4">
         <v>115</v>
       </c>
-      <c r="D120" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" s="5">
+      <c r="D120" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="6">
         <v>105</v>
       </c>
-      <c r="F120" s="5" t="s">
+      <c r="F120" s="6" t="s">
         <v>231</v>
       </c>
       <c r="G120" t="s">
         <v>232</v>
       </c>
-      <c r="H120" s="12"/>
+      <c r="H120" s="13"/>
     </row>
     <row r="121" spans="3:8">
-      <c r="C121" s="3">
+      <c r="C121" s="4">
         <v>116</v>
       </c>
-      <c r="D121" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="5">
+      <c r="D121" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="6">
         <v>105</v>
       </c>
-      <c r="F121" s="5" t="s">
+      <c r="F121" s="6" t="s">
         <v>233</v>
       </c>
       <c r="G121" t="s">
         <v>234</v>
       </c>
-      <c r="H121" s="12"/>
+      <c r="H121" s="13"/>
     </row>
     <row r="122" spans="3:8">
-      <c r="C122" s="3">
+      <c r="C122" s="4">
         <v>117</v>
       </c>
-      <c r="D122" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="5">
+      <c r="D122" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="6">
         <v>105</v>
       </c>
-      <c r="F122" s="5" t="s">
+      <c r="F122" s="6" t="s">
         <v>235</v>
       </c>
       <c r="G122" t="s">
         <v>236</v>
       </c>
-      <c r="H122" s="12"/>
+      <c r="H122" s="13"/>
     </row>
     <row r="123" spans="3:8">
-      <c r="C123" s="3">
+      <c r="C123" s="4">
         <v>118</v>
       </c>
-      <c r="D123" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" s="5">
+      <c r="D123" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="6">
         <v>105</v>
       </c>
-      <c r="F123" s="5" t="s">
+      <c r="F123" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="G123" s="13" t="s">
+      <c r="G123" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="H123" s="12"/>
+      <c r="H123" s="13"/>
     </row>
     <row r="124" spans="3:8">
-      <c r="C124" s="3">
+      <c r="C124" s="4">
         <v>119</v>
       </c>
-      <c r="D124" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="5">
+      <c r="D124" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="6">
         <v>105</v>
       </c>
-      <c r="F124" s="5" t="s">
+      <c r="F124" s="6" t="s">
         <v>239</v>
       </c>
       <c r="G124" t="s">
         <v>240</v>
       </c>
-      <c r="H124" s="12"/>
+      <c r="H124" s="13"/>
     </row>
     <row r="125" spans="3:8">
-      <c r="C125" s="3">
+      <c r="C125" s="4">
         <v>120</v>
       </c>
-      <c r="D125" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" s="5">
+      <c r="D125" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="6">
         <v>105</v>
       </c>
-      <c r="F125" s="5" t="s">
+      <c r="F125" s="6" t="s">
         <v>241</v>
       </c>
       <c r="G125" t="s">
         <v>242</v>
       </c>
-      <c r="H125" s="12"/>
+      <c r="H125" s="13"/>
     </row>
     <row r="126" spans="3:8">
-      <c r="C126" s="3">
+      <c r="C126" s="4">
         <v>121</v>
       </c>
-      <c r="D126" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" s="5">
+      <c r="D126" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="6">
         <v>121</v>
       </c>
-      <c r="F126" s="5" t="s">
+      <c r="F126" s="6" t="s">
         <v>243</v>
       </c>
       <c r="G126" t="s">
         <v>244</v>
       </c>
-      <c r="H126" s="10"/>
+      <c r="H126" s="11"/>
     </row>
     <row r="127" spans="3:8">
-      <c r="C127" s="3">
+      <c r="C127" s="4">
         <v>122</v>
       </c>
-      <c r="D127" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" s="5">
+      <c r="D127" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="6">
         <v>121</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="F127" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G127" s="13" t="s">
+      <c r="G127" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="H127" s="10"/>
+      <c r="H127" s="11"/>
     </row>
     <row r="128" spans="3:8">
-      <c r="C128" s="3">
+      <c r="C128" s="4">
         <v>123</v>
       </c>
-      <c r="D128" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="5">
+      <c r="D128" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="6">
         <v>121</v>
       </c>
-      <c r="F128" s="5" t="s">
+      <c r="F128" s="6" t="s">
         <v>246</v>
       </c>
       <c r="G128" t="s">
         <v>247</v>
       </c>
-      <c r="H128" s="10"/>
+      <c r="H128" s="11"/>
     </row>
     <row r="129" spans="3:9">
-      <c r="C129" s="3">
+      <c r="C129" s="4">
         <v>124</v>
       </c>
-      <c r="D129" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E129" s="5">
+      <c r="D129" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="6">
         <v>121</v>
       </c>
-      <c r="F129" s="5" t="s">
+      <c r="F129" s="6" t="s">
         <v>248</v>
       </c>
       <c r="G129" t="s">
         <v>249</v>
       </c>
-      <c r="H129" s="10"/>
+      <c r="H129" s="11"/>
     </row>
     <row r="130" spans="3:9">
-      <c r="C130" s="3">
+      <c r="C130" s="4">
         <v>125</v>
       </c>
-      <c r="D130" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E130" s="5">
+      <c r="D130" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" s="6">
         <v>121</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="F130" s="6" t="s">
         <v>250</v>
       </c>
       <c r="G130" t="s">
         <v>251</v>
       </c>
-      <c r="H130" s="10"/>
+      <c r="H130" s="11"/>
     </row>
     <row r="131" spans="3:9">
-      <c r="C131" s="3">
+      <c r="C131" s="4">
         <v>126</v>
       </c>
-      <c r="D131" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E131" s="5">
+      <c r="D131" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="6">
         <v>121</v>
       </c>
-      <c r="F131" s="5" t="s">
+      <c r="F131" s="6" t="s">
         <v>252</v>
       </c>
       <c r="G131" t="s">
         <v>253</v>
       </c>
-      <c r="H131" s="10"/>
+      <c r="H131" s="11"/>
     </row>
     <row r="132" spans="3:9">
-      <c r="C132" s="3">
+      <c r="C132" s="4">
         <v>127</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" s="5">
+      <c r="D132" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="6">
         <v>121</v>
       </c>
-      <c r="F132" s="5" t="s">
+      <c r="F132" s="6" t="s">
         <v>254</v>
       </c>
       <c r="G132" t="s">
         <v>255</v>
       </c>
-      <c r="H132" s="10"/>
+      <c r="H132" s="11"/>
     </row>
     <row r="133" spans="3:9">
-      <c r="C133" s="3">
+      <c r="C133" s="4">
         <v>128</v>
       </c>
-      <c r="D133" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" s="5">
+      <c r="D133" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="6">
         <v>128</v>
       </c>
-      <c r="F133" s="5" t="s">
+      <c r="F133" s="6" t="s">
         <v>256</v>
       </c>
       <c r="G133" t="s">
         <v>257</v>
       </c>
-      <c r="I133" s="12"/>
+      <c r="I133" s="13"/>
     </row>
     <row r="134" spans="3:9">
-      <c r="C134" s="3">
+      <c r="C134" s="4">
         <v>129</v>
       </c>
-      <c r="D134" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" s="5">
+      <c r="D134" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="6">
         <v>121</v>
       </c>
-      <c r="F134" s="5" t="s">
+      <c r="F134" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="G134" s="13" t="s">
+      <c r="G134" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="H134" s="10"/>
+      <c r="H134" s="11"/>
     </row>
     <row r="135" spans="3:9">
-      <c r="C135" s="3">
+      <c r="C135" s="4">
         <v>130</v>
       </c>
-      <c r="D135" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E135" s="5">
+      <c r="D135" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="6">
         <v>121</v>
       </c>
-      <c r="F135" s="5" t="s">
+      <c r="F135" s="6" t="s">
         <v>260</v>
       </c>
       <c r="G135" t="s">
         <v>261</v>
       </c>
-      <c r="H135" s="10"/>
+      <c r="H135" s="11"/>
     </row>
     <row r="136" spans="3:9">
-      <c r="C136" s="3">
+      <c r="C136" s="4">
         <v>131</v>
       </c>
-      <c r="D136" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E136" s="5">
+      <c r="D136" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" s="6">
         <v>121</v>
       </c>
-      <c r="F136" s="5" t="s">
+      <c r="F136" s="6" t="s">
         <v>262</v>
       </c>
       <c r="G136" t="s">
         <v>263</v>
       </c>
-      <c r="H136" s="10"/>
+      <c r="H136" s="11"/>
     </row>
     <row r="137" spans="3:9">
-      <c r="C137" s="3">
+      <c r="C137" s="4">
         <v>132</v>
       </c>
-      <c r="D137" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E137" s="5">
+      <c r="D137" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" s="6">
         <v>121</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="F137" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="G137" s="13" t="s">
+      <c r="G137" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="H137" s="10"/>
+      <c r="H137" s="11"/>
     </row>
     <row r="138" spans="3:9">
-      <c r="C138" s="3">
+      <c r="C138" s="4">
         <v>133</v>
       </c>
-      <c r="D138" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E138" s="5">
+      <c r="D138" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" s="6">
         <v>121</v>
       </c>
-      <c r="F138" s="5" t="s">
+      <c r="F138" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G138" s="13" t="s">
+      <c r="G138" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="H138" s="10"/>
+      <c r="H138" s="11"/>
     </row>
     <row r="139" spans="3:9">
-      <c r="C139" s="3">
+      <c r="C139" s="4">
         <v>134</v>
       </c>
-      <c r="D139" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E139" s="5">
+      <c r="D139" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="6">
         <v>121</v>
       </c>
-      <c r="F139" s="5" t="s">
+      <c r="F139" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G139" s="13" t="s">
+      <c r="G139" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="H139" s="10"/>
+      <c r="H139" s="11"/>
     </row>
     <row r="140" spans="3:9">
-      <c r="C140" s="3">
+      <c r="C140" s="4">
         <v>135</v>
       </c>
-      <c r="D140" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" s="5">
+      <c r="D140" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" s="6">
         <v>121</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="F140" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="G140" s="13" t="s">
+      <c r="G140" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="H140" s="10"/>
+      <c r="H140" s="11"/>
     </row>
     <row r="141" spans="3:9">
-      <c r="C141" s="3">
+      <c r="C141" s="4">
         <v>136</v>
       </c>
-      <c r="D141" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" s="5">
+      <c r="D141" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" s="6">
         <v>121</v>
       </c>
-      <c r="F141" s="5" t="s">
+      <c r="F141" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="G141" s="13" t="s">
+      <c r="G141" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="H141" s="10"/>
+      <c r="H141" s="11"/>
     </row>
     <row r="142" spans="3:9">
-      <c r="C142" s="3">
+      <c r="C142" s="4">
         <v>137</v>
       </c>
-      <c r="D142" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E142" s="5">
+      <c r="D142" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" s="6">
         <v>121</v>
       </c>
-      <c r="F142" s="5" t="s">
+      <c r="F142" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="G142" s="13" t="s">
+      <c r="G142" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="H142" s="10"/>
+      <c r="H142" s="11"/>
     </row>
     <row r="143" spans="3:9">
-      <c r="C143" s="3">
+      <c r="C143" s="4">
         <v>138</v>
       </c>
-      <c r="D143" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E143" s="5">
+      <c r="D143" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" s="6">
         <v>121</v>
       </c>
-      <c r="F143" s="5" t="s">
+      <c r="F143" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="G143" s="13" t="s">
+      <c r="G143" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="H143" s="10"/>
+      <c r="H143" s="11"/>
     </row>
     <row r="144" spans="3:9">
-      <c r="C144" s="3">
+      <c r="C144" s="4">
         <v>139</v>
       </c>
-      <c r="D144" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E144" s="5">
+      <c r="D144" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144" s="6">
         <v>139</v>
       </c>
-      <c r="F144" s="5" t="s">
+      <c r="F144" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="G144" s="13" t="s">
+      <c r="G144" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="H144" s="11"/>
+      <c r="H144" s="12"/>
     </row>
     <row r="145" spans="3:8">
-      <c r="C145" s="3">
+      <c r="C145" s="4">
         <v>140</v>
       </c>
-      <c r="D145" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E145" s="5">
+      <c r="D145" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E145" s="6">
         <v>139</v>
       </c>
-      <c r="F145" s="5" t="s">
+      <c r="F145" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="G145" s="13" t="s">
+      <c r="G145" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="H145" s="11"/>
+      <c r="H145" s="12"/>
     </row>
     <row r="146" spans="3:8">
-      <c r="C146" s="3">
+      <c r="C146" s="4">
         <v>141</v>
       </c>
-      <c r="D146" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" s="5">
+      <c r="D146" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146" s="6">
         <v>139</v>
       </c>
-      <c r="F146" s="5" t="s">
+      <c r="F146" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="G146" s="13" t="s">
+      <c r="G146" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="H146" s="11"/>
+      <c r="H146" s="12"/>
     </row>
     <row r="147" spans="3:8">
-      <c r="C147" s="3">
+      <c r="C147" s="4">
         <v>142</v>
       </c>
-      <c r="D147" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" s="5">
+      <c r="D147" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" s="6">
         <v>139</v>
       </c>
-      <c r="F147" s="5" t="s">
+      <c r="F147" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="G147" s="13" t="s">
+      <c r="G147" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H147" s="11"/>
+      <c r="H147" s="12"/>
     </row>
     <row r="148" spans="3:8">
-      <c r="C148" s="3">
+      <c r="C148" s="4">
         <v>143</v>
       </c>
-      <c r="D148" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E148" s="5">
+      <c r="D148" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" s="6">
         <v>139</v>
       </c>
-      <c r="F148" s="5" t="s">
+      <c r="F148" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="G148" s="13" t="s">
+      <c r="G148" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="H148" s="14"/>
+      <c r="H148" s="15"/>
     </row>
     <row r="149" spans="3:8">
-      <c r="C149" s="3">
+      <c r="C149" s="4">
         <v>144</v>
       </c>
-      <c r="D149" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E149" s="5">
+      <c r="D149" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" s="6">
         <v>139</v>
       </c>
-      <c r="F149" s="5" t="s">
+      <c r="F149" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="G149" s="13" t="s">
+      <c r="G149" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="H149" s="14"/>
+      <c r="H149" s="15"/>
     </row>
     <row r="150" spans="3:8">
-      <c r="C150" s="3">
+      <c r="C150" s="4">
         <v>145</v>
       </c>
-      <c r="D150" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" s="5">
+      <c r="D150" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="6">
         <v>139</v>
       </c>
-      <c r="F150" s="5" t="s">
+      <c r="F150" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="G150" s="13" t="s">
+      <c r="G150" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="H150" s="14"/>
+      <c r="H150" s="15"/>
     </row>
     <row r="151" spans="3:8">
-      <c r="C151" s="3">
+      <c r="C151" s="4">
         <v>146</v>
       </c>
-      <c r="D151" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" s="5">
+      <c r="D151" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="6">
         <v>139</v>
       </c>
-      <c r="F151" s="5" t="s">
+      <c r="F151" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="G151" s="13" t="s">
+      <c r="G151" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="H151" s="14"/>
+      <c r="H151" s="15"/>
     </row>
     <row r="152" spans="3:8">
-      <c r="C152" s="3">
+      <c r="C152" s="4">
         <v>147</v>
       </c>
-      <c r="D152" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E152" s="5">
+      <c r="D152" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="6">
         <v>139</v>
       </c>
-      <c r="F152" s="5" t="s">
+      <c r="F152" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="G152" s="13" t="s">
+      <c r="G152" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="H152" s="11"/>
+      <c r="H152" s="12"/>
     </row>
     <row r="153" spans="3:8">
-      <c r="C153" s="3">
+      <c r="C153" s="4">
         <v>148</v>
       </c>
-      <c r="D153" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="5">
+      <c r="D153" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="6">
         <v>139</v>
       </c>
-      <c r="F153" s="5" t="s">
+      <c r="F153" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="G153" s="13" t="s">
+      <c r="G153" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="H153" s="11"/>
+      <c r="H153" s="12"/>
     </row>
     <row r="154" spans="3:8">
-      <c r="C154" s="3">
+      <c r="C154" s="4">
         <v>149</v>
       </c>
-      <c r="D154" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="5">
+      <c r="D154" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="6">
         <v>139</v>
       </c>
-      <c r="F154" s="5" t="s">
+      <c r="F154" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="G154" s="13" t="s">
+      <c r="G154" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="H154" s="11"/>
+      <c r="H154" s="12"/>
     </row>
     <row r="155" spans="3:8">
-      <c r="C155" s="3">
+      <c r="C155" s="4">
         <v>150</v>
       </c>
-      <c r="D155" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" s="5">
+      <c r="D155" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="6">
         <v>139</v>
       </c>
-      <c r="F155" s="5" t="s">
+      <c r="F155" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="G155" s="13" t="s">
+      <c r="G155" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="H155" s="11"/>
+      <c r="H155" s="12"/>
     </row>
     <row r="156" spans="3:8">
-      <c r="C156" s="3">
+      <c r="C156" s="4">
         <v>151</v>
       </c>
-      <c r="D156" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" s="5">
+      <c r="D156" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="6">
         <v>139</v>
       </c>
-      <c r="F156" s="5" t="s">
+      <c r="F156" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="G156" s="15" t="s">
+      <c r="G156" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="11"/>
+      <c r="H156" s="12"/>
     </row>
     <row r="157" spans="3:8">
-      <c r="C157" s="3">
+      <c r="C157" s="4">
         <v>152</v>
       </c>
-      <c r="D157" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" s="5">
+      <c r="D157" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="6">
         <v>139</v>
       </c>
-      <c r="F157" s="5" t="s">
+      <c r="F157" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="G157" s="13" t="s">
+      <c r="G157" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="11"/>
+      <c r="H157" s="12"/>
     </row>
     <row r="158" spans="3:8">
-      <c r="C158" s="3">
+      <c r="C158" s="4">
         <v>153</v>
       </c>
-      <c r="D158" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E158" s="5">
+      <c r="D158" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="6">
         <v>139</v>
       </c>
-      <c r="F158" s="5" t="s">
+      <c r="F158" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="G158" s="13" t="s">
+      <c r="G158" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="11"/>
+      <c r="H158" s="12"/>
     </row>
     <row r="159" spans="3:8">
-      <c r="C159" s="3">
+      <c r="C159" s="4">
         <v>154</v>
       </c>
-      <c r="D159" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E159" s="5">
+      <c r="D159" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="6">
         <v>139</v>
       </c>
-      <c r="F159" s="5" t="s">
+      <c r="F159" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="G159" s="13" t="s">
+      <c r="G159" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="11"/>
+      <c r="H159" s="12"/>
     </row>
     <row r="160" spans="3:8">
-      <c r="C160" s="3">
+      <c r="C160" s="4">
         <v>155</v>
       </c>
-      <c r="D160" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E160" s="5">
+      <c r="D160" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="6">
         <v>155</v>
       </c>
-      <c r="F160" s="5" t="s">
+      <c r="F160" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="G160" s="13" t="s">
+      <c r="G160" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="H160" s="6"/>
+      <c r="H160" s="7"/>
     </row>
     <row r="161" spans="3:8">
-      <c r="C161" s="3">
+      <c r="C161" s="4">
         <v>156</v>
       </c>
-      <c r="D161" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E161" s="5">
+      <c r="D161" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="6">
         <v>155</v>
       </c>
-      <c r="F161" s="5" t="s">
+      <c r="F161" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="G161" s="13" t="s">
+      <c r="G161" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="6"/>
+      <c r="H161" s="7"/>
     </row>
     <row r="162" spans="3:8">
-      <c r="C162" s="3">
+      <c r="C162" s="4">
         <v>157</v>
       </c>
-      <c r="D162" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E162" s="5">
+      <c r="D162" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="6">
         <v>155</v>
       </c>
-      <c r="F162" s="5" t="s">
+      <c r="F162" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="G162" s="13" t="s">
+      <c r="G162" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="H162" s="6"/>
+      <c r="H162" s="7"/>
     </row>
     <row r="163" spans="3:8">
-      <c r="C163" s="3">
+      <c r="C163" s="4">
         <v>158</v>
       </c>
-      <c r="D163" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E163" s="5">
+      <c r="D163" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="6">
         <v>155</v>
       </c>
-      <c r="F163" s="5" t="s">
+      <c r="F163" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="G163" s="13" t="s">
+      <c r="G163" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="H163" s="6"/>
+      <c r="H163" s="7"/>
     </row>
     <row r="164" spans="3:8">
-      <c r="C164" s="3">
+      <c r="C164" s="4">
         <v>159</v>
       </c>
-      <c r="D164" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E164" s="5">
+      <c r="D164" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="6">
         <v>155</v>
       </c>
-      <c r="F164" s="5" t="s">
+      <c r="F164" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="G164" s="13" t="s">
+      <c r="G164" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="H164" s="6"/>
+      <c r="H164" s="7"/>
     </row>
     <row r="165" spans="3:8">
-      <c r="C165" s="3">
+      <c r="C165" s="4">
         <v>160</v>
       </c>
-      <c r="D165" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E165" s="5">
+      <c r="D165" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="6">
         <v>155</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="F165" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G165" s="13" t="s">
+      <c r="G165" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="H165" s="6"/>
+      <c r="H165" s="7"/>
     </row>
     <row r="166" spans="3:8">
-      <c r="C166" s="3">
+      <c r="C166" s="4">
         <v>161</v>
       </c>
-      <c r="D166" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" s="5">
+      <c r="D166" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="6">
         <v>155</v>
       </c>
-      <c r="F166" s="5" t="s">
+      <c r="F166" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="G166" s="13" t="s">
+      <c r="G166" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="H166" s="6"/>
+      <c r="H166" s="7"/>
     </row>
     <row r="167" spans="3:8">
-      <c r="C167" s="3">
+      <c r="C167" s="4">
         <v>162</v>
       </c>
-      <c r="D167" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E167" s="5">
+      <c r="D167" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="6">
         <v>155</v>
       </c>
-      <c r="F167" s="5" t="s">
+      <c r="F167" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G167" s="13" t="s">
+      <c r="G167" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="H167" s="6"/>
+      <c r="H167" s="7"/>
     </row>
     <row r="168" spans="3:8">
-      <c r="C168" s="3">
+      <c r="C168" s="4">
         <v>163</v>
       </c>
-      <c r="D168" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E168" s="5">
+      <c r="D168" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="6">
         <v>163</v>
       </c>
-      <c r="F168" s="5" t="s">
+      <c r="F168" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="G168" s="13" t="s">
+      <c r="G168" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="H168" s="11"/>
+      <c r="H168" s="12"/>
     </row>
     <row r="169" spans="3:8">
-      <c r="C169" s="3">
+      <c r="C169" s="4">
         <v>164</v>
       </c>
-      <c r="D169" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E169" s="5">
+      <c r="D169" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="6">
         <v>163</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="F169" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="G169" s="13" t="s">
+      <c r="G169" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="H169" s="11"/>
+      <c r="H169" s="12"/>
     </row>
     <row r="170" spans="3:8">
-      <c r="C170" s="3">
+      <c r="C170" s="4">
         <v>165</v>
       </c>
-      <c r="D170" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E170" s="5">
+      <c r="D170" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" s="6">
         <v>163</v>
       </c>
-      <c r="F170" s="5" t="s">
+      <c r="F170" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="G170" s="13" t="s">
+      <c r="G170" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="H170" s="11"/>
+      <c r="H170" s="12"/>
     </row>
     <row r="171" spans="3:8">
-      <c r="C171" s="3">
+      <c r="C171" s="4">
         <v>166</v>
       </c>
-      <c r="D171" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E171" s="5">
+      <c r="D171" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" s="6">
         <v>163</v>
       </c>
-      <c r="F171" s="5" t="s">
+      <c r="F171" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="G171" s="13" t="s">
+      <c r="G171" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="H171" s="11"/>
+      <c r="H171" s="12"/>
     </row>
     <row r="172" spans="3:8">
-      <c r="C172" s="3">
+      <c r="C172" s="4">
         <v>167</v>
       </c>
-      <c r="D172" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E172" s="5">
+      <c r="D172" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="6">
         <v>163</v>
       </c>
-      <c r="F172" s="5" t="s">
+      <c r="F172" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="G172" s="13" t="s">
+      <c r="G172" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="H172" s="11"/>
+      <c r="H172" s="12"/>
     </row>
     <row r="173" spans="3:8">
-      <c r="C173" s="3">
+      <c r="C173" s="4">
         <v>168</v>
       </c>
-      <c r="D173" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E173" s="5">
+      <c r="D173" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" s="6">
         <v>163</v>
       </c>
-      <c r="F173" s="5" t="s">
+      <c r="F173" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="G173" s="13" t="s">
+      <c r="G173" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="H173" s="11"/>
+      <c r="H173" s="12"/>
     </row>
     <row r="174" spans="3:8">
-      <c r="C174" s="3">
+      <c r="C174" s="4">
         <v>169</v>
       </c>
-      <c r="D174" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E174" s="5">
+      <c r="D174" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="6">
         <v>163</v>
       </c>
-      <c r="F174" s="5" t="s">
+      <c r="F174" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="G174" s="13" t="s">
+      <c r="G174" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="H174" s="11"/>
+      <c r="H174" s="12"/>
     </row>
     <row r="175" spans="3:8">
-      <c r="C175" s="3">
+      <c r="C175" s="4">
         <v>170</v>
       </c>
-      <c r="D175" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E175" s="5">
+      <c r="D175" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="6">
         <v>163</v>
       </c>
-      <c r="F175" s="5" t="s">
+      <c r="F175" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="G175" s="13" t="s">
+      <c r="G175" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="H175" s="11"/>
+      <c r="H175" s="12"/>
     </row>
     <row r="176" spans="3:8">
-      <c r="C176" s="3">
+      <c r="C176" s="4">
         <v>172</v>
       </c>
-      <c r="D176" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E176" s="5">
+      <c r="D176" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="6">
         <v>172</v>
       </c>
-      <c r="F176" s="5" t="s">
+      <c r="F176" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G176" s="13" t="s">
+      <c r="G176" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="H176" s="6"/>
+      <c r="H176" s="7"/>
     </row>
     <row r="177" spans="3:8">
-      <c r="C177" s="3">
+      <c r="C177" s="4">
         <v>173</v>
       </c>
-      <c r="D177" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E177" s="5">
+      <c r="D177" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="6">
         <v>172</v>
       </c>
-      <c r="F177" s="5" t="s">
+      <c r="F177" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="13" t="s">
+      <c r="G177" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="H177" s="6"/>
+      <c r="H177" s="7"/>
     </row>
     <row r="178" spans="3:8">
-      <c r="C178" s="3">
+      <c r="C178" s="4">
         <v>174</v>
       </c>
-      <c r="D178" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E178" s="5">
+      <c r="D178" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="6">
         <v>172</v>
       </c>
-      <c r="F178" s="5" t="s">
+      <c r="F178" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="G178" s="13" t="s">
+      <c r="G178" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="H178" s="6"/>
+      <c r="H178" s="7"/>
     </row>
     <row r="179" spans="3:8">
-      <c r="C179" s="3">
+      <c r="C179" s="4">
         <v>175</v>
       </c>
-      <c r="D179" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E179" s="5">
+      <c r="D179" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="6">
         <v>172</v>
       </c>
-      <c r="F179" s="5" t="s">
+      <c r="F179" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G179" s="13" t="s">
+      <c r="G179" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="H179" s="6"/>
+      <c r="H179" s="7"/>
     </row>
     <row r="180" spans="3:8">
-      <c r="C180" s="3">
+      <c r="C180" s="4">
         <v>176</v>
       </c>
-      <c r="D180" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E180" s="5">
+      <c r="D180" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="6">
         <v>176</v>
       </c>
-      <c r="F180" s="5" t="s">
+      <c r="F180" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="G180" s="13" t="s">
+      <c r="G180" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="H180" s="11"/>
+      <c r="H180" s="12"/>
     </row>
     <row r="181" spans="3:8">
-      <c r="C181" s="3">
+      <c r="C181" s="4">
         <v>177</v>
       </c>
-      <c r="D181" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E181" s="5">
+      <c r="D181" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="6">
         <v>176</v>
       </c>
-      <c r="F181" s="5" t="s">
+      <c r="F181" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="G181" s="13" t="s">
+      <c r="G181" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="H181" s="11"/>
+      <c r="H181" s="12"/>
     </row>
     <row r="182" spans="3:8">
-      <c r="C182" s="3">
+      <c r="C182" s="4">
         <v>178</v>
       </c>
-      <c r="D182" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E182" s="5">
+      <c r="D182" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="6">
         <v>176</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="F182" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G182" s="13" t="s">
+      <c r="G182" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="H182" s="11"/>
+      <c r="H182" s="12"/>
     </row>
     <row r="183" spans="3:8">
-      <c r="C183" s="3">
+      <c r="C183" s="4">
         <v>179</v>
       </c>
-      <c r="D183" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E183" s="5">
+      <c r="D183" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" s="6">
         <v>176</v>
       </c>
-      <c r="F183" s="5" t="s">
+      <c r="F183" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G183" s="13" t="s">
+      <c r="G183" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="H183" s="11"/>
+      <c r="H183" s="12"/>
     </row>
     <row r="184" spans="3:8">
-      <c r="C184" s="3">
+      <c r="C184" s="4">
         <v>180</v>
       </c>
-      <c r="D184" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E184" s="5">
+      <c r="D184" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" s="6">
         <v>180</v>
       </c>
-      <c r="F184" s="5" t="s">
+      <c r="F184" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="G184" s="13" t="s">
+      <c r="G184" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="H184" s="6"/>
+      <c r="H184" s="7"/>
     </row>
     <row r="185" spans="3:8">
-      <c r="C185" s="3">
+      <c r="C185" s="4">
         <v>181</v>
       </c>
-      <c r="D185" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E185" s="5">
+      <c r="D185" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="6">
         <v>180</v>
       </c>
-      <c r="F185" s="5" t="s">
+      <c r="F185" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="G185" s="13" t="s">
+      <c r="G185" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="H185" s="6"/>
+      <c r="H185" s="7"/>
     </row>
     <row r="186" spans="3:8">
-      <c r="C186" s="3">
+      <c r="C186" s="4">
         <v>182</v>
       </c>
-      <c r="D186" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E186" s="5">
+      <c r="D186" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" s="6">
         <v>180</v>
       </c>
-      <c r="F186" s="5" t="s">
+      <c r="F186" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="G186" s="13" t="s">
+      <c r="G186" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="H186" s="6"/>
+      <c r="H186" s="7"/>
     </row>
     <row r="187" spans="3:8">
-      <c r="C187" s="3">
+      <c r="C187" s="4">
         <v>183</v>
       </c>
-      <c r="D187" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E187" s="5">
+      <c r="D187" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="6">
         <v>180</v>
       </c>
-      <c r="F187" s="5" t="s">
+      <c r="F187" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="G187" s="13" t="s">
+      <c r="G187" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="H187" s="6"/>
+      <c r="H187" s="7"/>
     </row>
     <row r="188" spans="3:8">
-      <c r="C188" s="3">
+      <c r="C188" s="4">
         <v>184</v>
       </c>
-      <c r="D188" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E188" s="5">
+      <c r="D188" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="6">
         <v>184</v>
       </c>
-      <c r="F188" s="5" t="s">
+      <c r="F188" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G188" s="13" t="s">
+      <c r="G188" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="H188" s="10"/>
+      <c r="H188" s="11"/>
     </row>
     <row r="189" spans="3:8">
-      <c r="C189" s="3">
+      <c r="C189" s="4">
         <v>185</v>
       </c>
-      <c r="D189" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E189" s="5">
+      <c r="D189" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="6">
         <v>184</v>
       </c>
-      <c r="F189" s="5" t="s">
+      <c r="F189" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="G189" s="15" t="s">
+      <c r="G189" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="H189" s="10"/>
+      <c r="H189" s="11"/>
     </row>
     <row r="190" spans="3:8">
-      <c r="C190" s="3">
+      <c r="C190" s="4">
         <v>186</v>
       </c>
-      <c r="D190" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E190" s="5">
+      <c r="D190" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="6">
         <v>186</v>
       </c>
-      <c r="F190" s="5" t="s">
+      <c r="F190" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="G190" s="15" t="s">
+      <c r="G190" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="H190" s="7"/>
+      <c r="H190" s="8"/>
     </row>
     <row r="191" spans="3:8">
-      <c r="C191" s="3">
+      <c r="C191" s="4">
         <v>187</v>
       </c>
-      <c r="D191" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E191" s="5">
+      <c r="D191" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="6">
         <v>186</v>
       </c>
-      <c r="F191" s="5" t="s">
+      <c r="F191" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G191" s="13" t="s">
+      <c r="G191" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="H191" s="7"/>
+      <c r="H191" s="8"/>
     </row>
     <row r="192" spans="3:8">
-      <c r="C192" s="3">
+      <c r="C192" s="4">
         <v>188</v>
       </c>
-      <c r="D192" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E192" s="5">
+      <c r="D192" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="6">
         <v>188</v>
       </c>
-      <c r="F192" s="5" t="s">
+      <c r="F192" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="G192" s="15" t="s">
+      <c r="G192" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="H192" s="16"/>
-    </row>
-    <row r="193" spans="3:8">
-      <c r="C193" s="3">
+      <c r="H192" s="17"/>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="C193" s="4">
         <v>189</v>
       </c>
-      <c r="D193" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E193" s="5">
+      <c r="D193" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="6">
         <v>188</v>
       </c>
-      <c r="F193" s="5" t="s">
+      <c r="F193" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="G193" s="15" t="s">
+      <c r="G193" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="H193" s="16"/>
-    </row>
-    <row r="194" spans="3:8">
-      <c r="C194" s="3">
+      <c r="H193" s="17"/>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="C194" s="4">
         <v>190</v>
       </c>
-      <c r="D194" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E194" s="5">
+      <c r="D194" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="6">
         <v>190</v>
       </c>
-      <c r="F194" s="5" t="s">
+      <c r="F194" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="G194" s="15" t="s">
+      <c r="G194" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="H194" s="6"/>
-    </row>
-    <row r="195" spans="3:8">
-      <c r="C195" s="3">
+      <c r="H194" s="7"/>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="C195" s="4">
         <v>191</v>
       </c>
-      <c r="D195" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E195" s="5">
+      <c r="D195" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="6">
         <v>190</v>
       </c>
-      <c r="F195" s="5" t="s">
+      <c r="F195" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G195" s="15" t="s">
+      <c r="G195" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="H195" s="6"/>
-    </row>
-    <row r="196" spans="3:8">
-      <c r="C196" s="3">
+      <c r="H195" s="7"/>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="C196" s="4">
         <v>192</v>
       </c>
-      <c r="D196" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E196" s="5">
+      <c r="D196" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="6">
         <v>192</v>
       </c>
-      <c r="F196" s="5" t="s">
+      <c r="F196" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="G196" s="15" t="s">
+      <c r="G196" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="H196" s="10"/>
-    </row>
-    <row r="197" spans="3:8">
-      <c r="C197" s="3">
+      <c r="H196" s="11"/>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="C197" s="4">
         <v>193</v>
       </c>
-      <c r="D197" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E197" s="5">
+      <c r="D197" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" s="6">
         <v>192</v>
       </c>
-      <c r="F197" s="5" t="s">
+      <c r="F197" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="G197" s="15" t="s">
+      <c r="G197" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="H197" s="10"/>
-    </row>
-    <row r="198" spans="3:8">
-      <c r="C198" s="3">
+      <c r="H197" s="11"/>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="C198" s="4">
         <v>194</v>
       </c>
-      <c r="D198" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E198" s="5">
+      <c r="D198" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="6">
         <v>194</v>
       </c>
-      <c r="F198" s="5" t="s">
+      <c r="F198" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="G198" s="15" t="s">
+      <c r="G198" s="16" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="199" spans="3:8">
-      <c r="C199" s="3">
+    <row r="199" spans="1:8">
+      <c r="C199" s="4">
         <v>195</v>
       </c>
-      <c r="D199" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E199" s="5">
+      <c r="D199" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="6">
         <v>195</v>
       </c>
-      <c r="F199" s="5" t="s">
+      <c r="F199" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="G199" s="15" t="s">
+      <c r="G199" s="16" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="200" spans="3:8">
-      <c r="C200" s="3">
+    <row r="200" spans="1:8">
+      <c r="C200" s="4">
         <v>196</v>
       </c>
-      <c r="D200" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E200" s="5">
+      <c r="D200" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="6">
         <v>196</v>
       </c>
-      <c r="F200" s="5" t="s">
+      <c r="F200" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="G200" s="15" t="s">
+      <c r="G200" s="16" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="201" spans="3:8">
-      <c r="C201" s="3">
+    <row r="201" spans="1:8">
+      <c r="C201" s="4">
         <v>197</v>
       </c>
-      <c r="D201" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E201" s="5">
+      <c r="D201" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="6">
         <v>197</v>
       </c>
-      <c r="F201" s="5" t="s">
+      <c r="F201" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="G201" s="15" t="s">
+      <c r="G201" s="16" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="202" spans="3:8">
-      <c r="C202" s="3">
+    <row r="202" spans="1:8">
+      <c r="C202" s="4">
         <v>198</v>
       </c>
-      <c r="D202" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E202" s="5">
+      <c r="D202" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202" s="6">
         <v>198</v>
       </c>
-      <c r="F202" s="5" t="s">
+      <c r="F202" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="G202" s="15" t="s">
+      <c r="G202" s="16" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="203" spans="3:8">
-      <c r="C203" s="3">
+    <row r="203" spans="1:8">
+      <c r="C203" s="4">
         <v>199</v>
       </c>
-      <c r="D203" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E203" s="5">
+      <c r="D203" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" s="6">
         <v>199</v>
       </c>
-      <c r="F203" s="5" t="s">
+      <c r="F203" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="G203" s="15" t="s">
+      <c r="G203" s="16" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="204" spans="3:8">
-      <c r="C204" s="3">
+    <row r="204" spans="1:8">
+      <c r="C204" s="4">
         <v>200</v>
       </c>
-      <c r="D204" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E204" s="5">
+      <c r="D204" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204" s="6">
         <v>200</v>
       </c>
-      <c r="F204" s="5" t="s">
+      <c r="F204" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="G204" s="15" t="s">
+      <c r="G204" s="16" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="205" spans="3:8">
-      <c r="C205" s="3">
+    <row r="205" s="2" customFormat="1" spans="1:8">
+      <c r="C205" s="18">
         <v>202</v>
       </c>
-      <c r="D205" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E205" s="5">
+      <c r="D205" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="19">
         <v>202</v>
       </c>
-      <c r="F205" s="5" t="s">
+      <c r="F205" s="19" t="s">
         <v>395</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="206" spans="3:8">
-      <c r="C206" s="3">
+    <row r="206" s="2" customFormat="1" spans="1:8">
+      <c r="C206" s="18">
         <v>203</v>
       </c>
-      <c r="D206" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" s="5">
+      <c r="D206" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="19">
         <v>203</v>
       </c>
-      <c r="F206" s="5" t="s">
+      <c r="F206" s="19" t="s">
         <v>397</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>398</v>
       </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C207" s="4">
+        <v>211</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" s="6">
+        <v>211</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="G207" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -5200,7 +5200,7 @@
       <c r="G160" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="H160" s="7"/>
+      <c r="H160" s="11"/>
     </row>
     <row r="161" spans="3:8">
       <c r="C161" s="4">
@@ -5218,7 +5218,7 @@
       <c r="G161" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="7"/>
+      <c r="H161" s="11"/>
     </row>
     <row r="162" spans="3:8">
       <c r="C162" s="4">
@@ -5236,7 +5236,7 @@
       <c r="G162" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="H162" s="7"/>
+      <c r="H162" s="11"/>
     </row>
     <row r="163" spans="3:8">
       <c r="C163" s="4">
@@ -5254,7 +5254,7 @@
       <c r="G163" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="H163" s="7"/>
+      <c r="H163" s="11"/>
     </row>
     <row r="164" spans="3:8">
       <c r="C164" s="4">
@@ -5272,7 +5272,7 @@
       <c r="G164" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="H164" s="7"/>
+      <c r="H164" s="11"/>
     </row>
     <row r="165" spans="3:8">
       <c r="C165" s="4">
@@ -5290,7 +5290,7 @@
       <c r="G165" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="H165" s="7"/>
+      <c r="H165" s="11"/>
     </row>
     <row r="166" spans="3:8">
       <c r="C166" s="4">
@@ -5308,7 +5308,7 @@
       <c r="G166" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="H166" s="7"/>
+      <c r="H166" s="11"/>
     </row>
     <row r="167" spans="3:8">
       <c r="C167" s="4">
@@ -5326,7 +5326,7 @@
       <c r="G167" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="H167" s="7"/>
+      <c r="H167" s="11"/>
     </row>
     <row r="168" spans="3:8">
       <c r="C168" s="4">
@@ -5336,7 +5336,7 @@
         <v>9</v>
       </c>
       <c r="E168" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>322</v>
@@ -5344,7 +5344,7 @@
       <c r="G168" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="H168" s="12"/>
+      <c r="H168" s="11"/>
     </row>
     <row r="169" spans="3:8">
       <c r="C169" s="4">
@@ -5354,7 +5354,7 @@
         <v>9</v>
       </c>
       <c r="E169" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>324</v>
@@ -5362,7 +5362,7 @@
       <c r="G169" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="H169" s="12"/>
+      <c r="H169" s="11"/>
     </row>
     <row r="170" spans="3:8">
       <c r="C170" s="4">
@@ -5372,7 +5372,7 @@
         <v>9</v>
       </c>
       <c r="E170" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>326</v>
@@ -5380,7 +5380,7 @@
       <c r="G170" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="H170" s="12"/>
+      <c r="H170" s="11"/>
     </row>
     <row r="171" spans="3:8">
       <c r="C171" s="4">
@@ -5390,7 +5390,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>328</v>
@@ -5398,7 +5398,7 @@
       <c r="G171" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="H171" s="12"/>
+      <c r="H171" s="11"/>
     </row>
     <row r="172" spans="3:8">
       <c r="C172" s="4">
@@ -5408,7 +5408,7 @@
         <v>9</v>
       </c>
       <c r="E172" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>329</v>
@@ -5416,7 +5416,7 @@
       <c r="G172" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="H172" s="12"/>
+      <c r="H172" s="11"/>
     </row>
     <row r="173" spans="3:8">
       <c r="C173" s="4">
@@ -5426,7 +5426,7 @@
         <v>9</v>
       </c>
       <c r="E173" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>331</v>
@@ -5434,7 +5434,7 @@
       <c r="G173" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="H173" s="12"/>
+      <c r="H173" s="11"/>
     </row>
     <row r="174" spans="3:8">
       <c r="C174" s="4">
@@ -5444,7 +5444,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>333</v>
@@ -5452,7 +5452,7 @@
       <c r="G174" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="H174" s="12"/>
+      <c r="H174" s="11"/>
     </row>
     <row r="175" spans="3:8">
       <c r="C175" s="4">
@@ -5462,7 +5462,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="6">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>335</v>
@@ -5470,7 +5470,7 @@
       <c r="G175" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="H175" s="12"/>
+      <c r="H175" s="11"/>
     </row>
     <row r="176" spans="3:8">
       <c r="C176" s="4">
@@ -5488,7 +5488,7 @@
       <c r="G176" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="H176" s="7"/>
+      <c r="H176" s="12"/>
     </row>
     <row r="177" spans="3:8">
       <c r="C177" s="4">
@@ -5506,7 +5506,7 @@
       <c r="G177" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="H177" s="7"/>
+      <c r="H177" s="12"/>
     </row>
     <row r="178" spans="3:8">
       <c r="C178" s="4">
@@ -5524,7 +5524,7 @@
       <c r="G178" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="H178" s="7"/>
+      <c r="H178" s="12"/>
     </row>
     <row r="179" spans="3:8">
       <c r="C179" s="4">
@@ -5542,7 +5542,7 @@
       <c r="G179" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="H179" s="7"/>
+      <c r="H179" s="12"/>
     </row>
     <row r="180" spans="3:8">
       <c r="C180" s="4">
@@ -5552,7 +5552,7 @@
         <v>9</v>
       </c>
       <c r="E180" s="6">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>345</v>
@@ -5570,7 +5570,7 @@
         <v>9</v>
       </c>
       <c r="E181" s="6">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F181" s="6" t="s">
         <v>347</v>
@@ -5588,7 +5588,7 @@
         <v>9</v>
       </c>
       <c r="E182" s="6">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>349</v>
@@ -5606,7 +5606,7 @@
         <v>9</v>
       </c>
       <c r="E183" s="6">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F183" s="6" t="s">
         <v>351</v>
@@ -5884,6 +5884,7 @@
       <c r="G198" s="16" t="s">
         <v>382</v>
       </c>
+      <c r="H198" s="12"/>
     </row>
     <row r="199" spans="1:8">
       <c r="C199" s="4">
@@ -5893,7 +5894,7 @@
         <v>9</v>
       </c>
       <c r="E199" s="6">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F199" s="6" t="s">
         <v>383</v>
@@ -5901,6 +5902,7 @@
       <c r="G199" s="16" t="s">
         <v>384</v>
       </c>
+      <c r="H199" s="12"/>
     </row>
     <row r="200" spans="1:8">
       <c r="C200" s="4">
@@ -5918,6 +5920,7 @@
       <c r="G200" s="16" t="s">
         <v>386</v>
       </c>
+      <c r="H200" s="11"/>
     </row>
     <row r="201" spans="1:8">
       <c r="C201" s="4">
@@ -5927,7 +5930,7 @@
         <v>9</v>
       </c>
       <c r="E201" s="6">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F201" s="6" t="s">
         <v>387</v>
@@ -5935,6 +5938,7 @@
       <c r="G201" s="16" t="s">
         <v>388</v>
       </c>
+      <c r="H201" s="11"/>
     </row>
     <row r="202" spans="1:8">
       <c r="C202" s="4">

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="403">
   <si>
     <t>Id</t>
   </si>
@@ -1279,6 +1279,12 @@
   </si>
   <si>
     <t>WJBeta211</t>
+  </si>
+  <si>
+    <t>月见之森</t>
+  </si>
+  <si>
+    <t>WJBeta212</t>
   </si>
 </sst>
 </file>
@@ -2363,7 +2369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I207"/>
+  <dimension ref="A3:I208"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6041,7 +6047,24 @@
       <c r="F207" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="G207" s="16"/>
+      <c r="G207" s="16" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="C208" s="4">
+        <v>212</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" s="6">
+        <v>212</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="G208" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="402">
   <si>
     <t>Id</t>
   </si>
@@ -1279,9 +1279,6 @@
   </si>
   <si>
     <t>WJBeta211</t>
-  </si>
-  <si>
-    <t>月见之森</t>
   </si>
   <si>
     <t>WJBeta212</t>
@@ -6047,9 +6044,7 @@
       <c r="F207" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="G207" s="16" t="s">
-        <v>401</v>
-      </c>
+      <c r="G207" s="16"/>
     </row>
     <row r="208" spans="1:8">
       <c r="C208" s="4">
@@ -6062,7 +6057,7 @@
         <v>212</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G208" s="16"/>
     </row>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="20145" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="404">
   <si>
     <t>Id</t>
   </si>
@@ -1281,7 +1281,13 @@
     <t>WJBeta211</t>
   </si>
   <si>
+    <t>月见之森</t>
+  </si>
+  <si>
     <t>WJBeta212</t>
+  </si>
+  <si>
+    <t>天地同归</t>
   </si>
 </sst>
 </file>
@@ -2366,7 +2372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I208"/>
+  <dimension ref="A3:I211"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6044,7 +6050,10 @@
       <c r="F207" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="G207" s="16"/>
+      <c r="G207" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="H207" s="16"/>
     </row>
     <row r="208" spans="1:8">
       <c r="C208" s="4">
@@ -6057,9 +6066,24 @@
         <v>212</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="G208" s="16"/>
+        <v>402</v>
+      </c>
+      <c r="G208" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="H208" s="16"/>
+    </row>
+    <row r="209" spans="7:8">
+      <c r="G209" s="16"/>
+      <c r="H209" s="16"/>
+    </row>
+    <row r="210" spans="7:8">
+      <c r="G210" s="16"/>
+      <c r="H210" s="16"/>
+    </row>
+    <row r="211" spans="7:8">
+      <c r="G211" s="16"/>
+      <c r="H211" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20145" windowHeight="4560"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="405">
   <si>
     <t>Id</t>
   </si>
@@ -1288,6 +1288,9 @@
   </si>
   <si>
     <t>天地同归</t>
+  </si>
+  <si>
+    <t>WJBeta213</t>
   </si>
 </sst>
 </file>
@@ -6073,15 +6076,27 @@
       </c>
       <c r="H208" s="16"/>
     </row>
-    <row r="209" spans="7:8">
+    <row r="209" spans="3:8">
+      <c r="C209" s="4">
+        <v>213</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E209" s="6">
+        <v>213</v>
+      </c>
+      <c r="F209" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="G209" s="16"/>
       <c r="H209" s="16"/>
     </row>
-    <row r="210" spans="7:8">
+    <row r="210" spans="3:8">
       <c r="G210" s="16"/>
       <c r="H210" s="16"/>
     </row>
-    <row r="211" spans="7:8">
+    <row r="211" spans="3:8">
       <c r="G211" s="16"/>
       <c r="H211" s="16"/>
     </row>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="406">
   <si>
     <t>Id</t>
   </si>
@@ -1291,6 +1291,9 @@
   </si>
   <si>
     <t>WJBeta213</t>
+  </si>
+  <si>
+    <t>盛世华章</t>
   </si>
 </sst>
 </file>
@@ -6089,7 +6092,9 @@
       <c r="F209" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="G209" s="16"/>
+      <c r="G209" s="16" t="s">
+        <v>405</v>
+      </c>
       <c r="H209" s="16"/>
     </row>
     <row r="210" spans="3:8">

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="407">
   <si>
     <t>Id</t>
   </si>
@@ -1294,6 +1294,9 @@
   </si>
   <si>
     <t>盛世华章</t>
+  </si>
+  <si>
+    <t>WJBeta214</t>
   </si>
 </sst>
 </file>
@@ -6098,6 +6101,18 @@
       <c r="H209" s="16"/>
     </row>
     <row r="210" spans="3:8">
+      <c r="C210" s="4">
+        <v>214</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" s="6">
+        <v>214</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>406</v>
+      </c>
       <c r="G210" s="16"/>
       <c r="H210" s="16"/>
     </row>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="408">
   <si>
     <t>Id</t>
   </si>
@@ -1297,6 +1297,9 @@
   </si>
   <si>
     <t>WJBeta214</t>
+  </si>
+  <si>
+    <t>烽火王座</t>
   </si>
 </sst>
 </file>
@@ -6113,7 +6116,9 @@
       <c r="F210" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="G210" s="16"/>
+      <c r="G210" s="16" t="s">
+        <v>407</v>
+      </c>
       <c r="H210" s="16"/>
     </row>
     <row r="211" spans="3:8">

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="409">
   <si>
     <t>Id</t>
   </si>
@@ -1300,6 +1300,9 @@
   </si>
   <si>
     <t>烽火王座</t>
+  </si>
+  <si>
+    <t>WJBeta215</t>
   </si>
 </sst>
 </file>
@@ -6122,6 +6125,18 @@
       <c r="H210" s="16"/>
     </row>
     <row r="211" spans="3:8">
+      <c r="C211" s="4">
+        <v>215</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E211" s="6">
+        <v>215</v>
+      </c>
+      <c r="F211" s="6" t="s">
+        <v>408</v>
+      </c>
       <c r="G211" s="16"/>
       <c r="H211" s="16"/>
     </row>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="410">
   <si>
     <t>Id</t>
   </si>
@@ -1303,6 +1303,9 @@
   </si>
   <si>
     <t>WJBeta215</t>
+  </si>
+  <si>
+    <t>凌云九霄</t>
   </si>
 </sst>
 </file>
@@ -6137,7 +6140,9 @@
       <c r="F211" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="G211" s="16"/>
+      <c r="G211" s="16" t="s">
+        <v>409</v>
+      </c>
       <c r="H211" s="16"/>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="411">
   <si>
     <t>Id</t>
   </si>
@@ -1306,6 +1306,9 @@
   </si>
   <si>
     <t>凌云九霄</t>
+  </si>
+  <si>
+    <t>WJBeta216</t>
   </si>
 </sst>
 </file>
@@ -2390,7 +2393,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I211"/>
+  <dimension ref="A3:I212"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6145,6 +6148,22 @@
       </c>
       <c r="H211" s="16"/>
     </row>
+    <row r="212" spans="3:8">
+      <c r="C212" s="4">
+        <v>216</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E212" s="6">
+        <v>216</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="G212" s="16"/>
+      <c r="H212" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="412">
   <si>
     <t>Id</t>
   </si>
@@ -1309,6 +1309,9 @@
   </si>
   <si>
     <t>WJBeta216</t>
+  </si>
+  <si>
+    <t>沧澜城</t>
   </si>
 </sst>
 </file>
@@ -2012,7 +2015,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2045,6 +2048,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6161,7 +6165,9 @@
       <c r="F212" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="G212" s="16"/>
+      <c r="G212" s="20" t="s">
+        <v>411</v>
+      </c>
       <c r="H212" s="16"/>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="413">
   <si>
     <t>Id</t>
   </si>
@@ -1312,6 +1312,9 @@
   </si>
   <si>
     <t>沧澜城</t>
+  </si>
+  <si>
+    <t>WJBeta217</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +2018,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2048,7 +2051,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2397,7 +2399,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I212"/>
+  <dimension ref="A3:I213"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6165,10 +6167,25 @@
       <c r="F212" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="G212" s="20" t="s">
+      <c r="G212" s="14" t="s">
         <v>411</v>
       </c>
       <c r="H212" s="16"/>
+    </row>
+    <row r="213" spans="3:8">
+      <c r="C213" s="4">
+        <v>217</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E213" s="6">
+        <v>217</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="G213" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="414">
   <si>
     <t>Id</t>
   </si>
@@ -1315,6 +1315,9 @@
   </si>
   <si>
     <t>WJBeta217</t>
+  </si>
+  <si>
+    <t>惊鸿</t>
   </si>
 </sst>
 </file>
@@ -2018,7 +2021,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2044,6 +2047,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2051,6 +2055,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5768,7 +5774,7 @@
         <v>9</v>
       </c>
       <c r="E190" s="6">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>365</v>
@@ -5776,7 +5782,7 @@
       <c r="G190" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="H190" s="8"/>
+      <c r="H190" s="17"/>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="4">
@@ -5786,7 +5792,7 @@
         <v>9</v>
       </c>
       <c r="E191" s="6">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>367</v>
@@ -5794,7 +5800,7 @@
       <c r="G191" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="H191" s="8"/>
+      <c r="H191" s="17"/>
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="4">
@@ -5812,9 +5818,9 @@
       <c r="G192" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="H192" s="17"/>
-    </row>
-    <row r="193" spans="1:8">
+      <c r="H192" s="18"/>
+    </row>
+    <row r="193" spans="1:9">
       <c r="C193" s="4">
         <v>189</v>
       </c>
@@ -5830,9 +5836,9 @@
       <c r="G193" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="H193" s="17"/>
-    </row>
-    <row r="194" spans="1:8">
+      <c r="H193" s="18"/>
+    </row>
+    <row r="194" spans="1:9">
       <c r="C194" s="4">
         <v>190</v>
       </c>
@@ -5840,7 +5846,7 @@
         <v>9</v>
       </c>
       <c r="E194" s="6">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>373</v>
@@ -5848,9 +5854,9 @@
       <c r="G194" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="H194" s="7"/>
-    </row>
-    <row r="195" spans="1:8">
+      <c r="H194" s="12"/>
+    </row>
+    <row r="195" spans="1:9">
       <c r="C195" s="4">
         <v>191</v>
       </c>
@@ -5858,7 +5864,7 @@
         <v>9</v>
       </c>
       <c r="E195" s="6">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F195" s="6" t="s">
         <v>375</v>
@@ -5866,9 +5872,9 @@
       <c r="G195" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="H195" s="7"/>
-    </row>
-    <row r="196" spans="1:8">
+      <c r="H195" s="12"/>
+    </row>
+    <row r="196" spans="1:9">
       <c r="C196" s="4">
         <v>192</v>
       </c>
@@ -5886,7 +5892,7 @@
       </c>
       <c r="H196" s="11"/>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:9">
       <c r="C197" s="4">
         <v>193</v>
       </c>
@@ -5904,7 +5910,7 @@
       </c>
       <c r="H197" s="11"/>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:9">
       <c r="C198" s="4">
         <v>194</v>
       </c>
@@ -5922,7 +5928,7 @@
       </c>
       <c r="H198" s="12"/>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:9">
       <c r="C199" s="4">
         <v>195</v>
       </c>
@@ -5940,7 +5946,7 @@
       </c>
       <c r="H199" s="12"/>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:9">
       <c r="C200" s="4">
         <v>196</v>
       </c>
@@ -5958,7 +5964,7 @@
       </c>
       <c r="H200" s="11"/>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:9">
       <c r="C201" s="4">
         <v>197</v>
       </c>
@@ -5976,7 +5982,7 @@
       </c>
       <c r="H201" s="11"/>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:9">
       <c r="C202" s="4">
         <v>198</v>
       </c>
@@ -5992,8 +5998,9 @@
       <c r="G202" s="16" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="203" spans="1:8">
+      <c r="H202" s="12"/>
+    </row>
+    <row r="203" spans="1:9">
       <c r="C203" s="4">
         <v>199</v>
       </c>
@@ -6001,7 +6008,7 @@
         <v>9</v>
       </c>
       <c r="E203" s="6">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F203" s="6" t="s">
         <v>391</v>
@@ -6009,8 +6016,9 @@
       <c r="G203" s="16" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="204" spans="1:8">
+      <c r="H203" s="12"/>
+    </row>
+    <row r="204" spans="1:9">
       <c r="C204" s="4">
         <v>200</v>
       </c>
@@ -6026,42 +6034,45 @@
       <c r="G204" s="16" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="205" s="2" customFormat="1" spans="1:8">
-      <c r="C205" s="18">
+      <c r="H204" s="11"/>
+    </row>
+    <row r="205" s="2" customFormat="1" spans="1:9">
+      <c r="C205" s="19">
         <v>202</v>
       </c>
-      <c r="D205" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E205" s="19">
+      <c r="D205" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="20">
         <v>202</v>
       </c>
-      <c r="F205" s="19" t="s">
+      <c r="F205" s="20" t="s">
         <v>395</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="206" s="2" customFormat="1" spans="1:8">
-      <c r="C206" s="18">
+      <c r="I205" s="17"/>
+    </row>
+    <row r="206" s="2" customFormat="1" spans="1:9">
+      <c r="C206" s="19">
         <v>203</v>
       </c>
-      <c r="D206" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" s="19">
+      <c r="D206" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="20">
         <v>203</v>
       </c>
-      <c r="F206" s="19" t="s">
+      <c r="F206" s="20" t="s">
         <v>397</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="207" spans="1:8">
+      <c r="I206" s="17"/>
+    </row>
+    <row r="207" spans="1:9">
       <c r="A207" s="3" t="s">
         <v>399</v>
       </c>
@@ -6072,7 +6083,7 @@
         <v>9</v>
       </c>
       <c r="E207" s="6">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>400</v>
@@ -6080,9 +6091,9 @@
       <c r="G207" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="H207" s="16"/>
-    </row>
-    <row r="208" spans="1:8">
+      <c r="H207" s="21"/>
+    </row>
+    <row r="208" spans="1:9">
       <c r="C208" s="4">
         <v>212</v>
       </c>
@@ -6098,7 +6109,7 @@
       <c r="G208" s="16" t="s">
         <v>403</v>
       </c>
-      <c r="H208" s="16"/>
+      <c r="H208" s="22"/>
     </row>
     <row r="209" spans="3:8">
       <c r="C209" s="4">
@@ -6108,7 +6119,7 @@
         <v>9</v>
       </c>
       <c r="E209" s="6">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F209" s="6" t="s">
         <v>404</v>
@@ -6116,7 +6127,7 @@
       <c r="G209" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="H209" s="16"/>
+      <c r="H209" s="22"/>
     </row>
     <row r="210" spans="3:8">
       <c r="C210" s="4">
@@ -6185,7 +6196,9 @@
       <c r="F213" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="G213" s="16"/>
+      <c r="G213" s="16" t="s">
+        <v>413</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="415">
   <si>
     <t>Id</t>
   </si>
@@ -1318,6 +1318,9 @@
   </si>
   <si>
     <t>惊鸿</t>
+  </si>
+  <si>
+    <t>WJBeta218</t>
   </si>
 </sst>
 </file>
@@ -2405,7 +2408,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I213"/>
+  <dimension ref="A3:I214"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6200,6 +6203,21 @@
         <v>413</v>
       </c>
     </row>
+    <row r="214" spans="3:8">
+      <c r="C214" s="4">
+        <v>218</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E214" s="6">
+        <v>218</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G214" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="416">
   <si>
     <t>Id</t>
   </si>
@@ -1321,6 +1321,9 @@
   </si>
   <si>
     <t>WJBeta218</t>
+  </si>
+  <si>
+    <t>观星台</t>
   </si>
 </sst>
 </file>
@@ -6216,7 +6219,9 @@
       <c r="F214" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="G214" s="16"/>
+      <c r="G214" s="16" t="s">
+        <v>415</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="417">
   <si>
     <t>Id</t>
   </si>
@@ -1324,6 +1324,9 @@
   </si>
   <si>
     <t>观星台</t>
+  </si>
+  <si>
+    <t>WJBeta219</t>
   </si>
 </sst>
 </file>
@@ -2411,7 +2414,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I214"/>
+  <dimension ref="A3:I215"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6223,6 +6226,21 @@
         <v>415</v>
       </c>
     </row>
+    <row r="215" spans="3:8">
+      <c r="C215" s="4">
+        <v>219</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E215" s="6">
+        <v>219</v>
+      </c>
+      <c r="F215" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="G215" s="14"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="418">
   <si>
     <t>Id</t>
   </si>
@@ -1327,6 +1327,9 @@
   </si>
   <si>
     <t>WJBeta219</t>
+  </si>
+  <si>
+    <t>星月同辉</t>
   </si>
 </sst>
 </file>
@@ -6239,7 +6242,9 @@
       <c r="F215" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="G215" s="14"/>
+      <c r="G215" s="14" t="s">
+        <v>417</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="419">
   <si>
     <t>Id</t>
   </si>
@@ -1330,6 +1330,9 @@
   </si>
   <si>
     <t>星月同辉</t>
+  </si>
+  <si>
+    <t>WJBeta220</t>
   </si>
 </sst>
 </file>
@@ -2417,7 +2420,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I215"/>
+  <dimension ref="A3:I216"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6246,6 +6249,21 @@
         <v>417</v>
       </c>
     </row>
+    <row r="216" spans="3:8">
+      <c r="C216" s="4">
+        <v>220</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E216" s="6">
+        <v>220</v>
+      </c>
+      <c r="F216" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="G216" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="420">
   <si>
     <t>Id</t>
   </si>
@@ -1333,6 +1333,9 @@
   </si>
   <si>
     <t>WJBeta220</t>
+  </si>
+  <si>
+    <t>九天揽星</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +2039,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2072,6 +2075,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6262,7 +6266,9 @@
       <c r="F216" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="G216" s="16"/>
+      <c r="G216" s="23" t="s">
+        <v>419</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="421">
   <si>
     <t>Id</t>
   </si>
@@ -1336,6 +1336,9 @@
   </si>
   <si>
     <t>九天揽星</t>
+  </si>
+  <si>
+    <t>WJBeta221</t>
   </si>
 </sst>
 </file>
@@ -2039,7 +2042,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2075,7 +2078,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2424,7 +2426,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I216"/>
+  <dimension ref="A3:I217"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6266,8 +6268,25 @@
       <c r="F216" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="G216" s="23" t="s">
+      <c r="G216" s="14" t="s">
         <v>419</v>
+      </c>
+    </row>
+    <row r="217" spans="3:8">
+      <c r="C217" s="4">
+        <v>221</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E217" s="6">
+        <v>221</v>
+      </c>
+      <c r="F217" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="G217" s="16" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="422">
   <si>
     <t>Id</t>
   </si>
@@ -1339,6 +1339,9 @@
   </si>
   <si>
     <t>WJBeta221</t>
+  </si>
+  <si>
+    <t>WJBeta222</t>
   </si>
 </sst>
 </file>
@@ -2426,7 +2429,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I217"/>
+  <dimension ref="A3:I218"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6289,6 +6292,21 @@
         <v>40</v>
       </c>
     </row>
+    <row r="218" spans="3:8">
+      <c r="C218" s="4">
+        <v>222</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218" s="6">
+        <v>222</v>
+      </c>
+      <c r="F218" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="G218" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="423">
   <si>
     <t>Id</t>
   </si>
@@ -1342,6 +1342,9 @@
   </si>
   <si>
     <t>WJBeta222</t>
+  </si>
+  <si>
+    <t>绿茵世界</t>
   </si>
 </sst>
 </file>
@@ -2045,7 +2048,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2081,6 +2084,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5914,7 +5918,7 @@
       <c r="G196" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="H196" s="11"/>
+      <c r="H196" s="7"/>
     </row>
     <row r="197" spans="1:9">
       <c r="C197" s="4">
@@ -5932,7 +5936,7 @@
       <c r="G197" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="H197" s="11"/>
+      <c r="H197" s="7"/>
     </row>
     <row r="198" spans="1:9">
       <c r="C198" s="4">
@@ -5942,7 +5946,7 @@
         <v>9</v>
       </c>
       <c r="E198" s="6">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>381</v>
@@ -5950,7 +5954,7 @@
       <c r="G198" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="H198" s="12"/>
+      <c r="H198" s="7"/>
     </row>
     <row r="199" spans="1:9">
       <c r="C199" s="4">
@@ -5960,7 +5964,7 @@
         <v>9</v>
       </c>
       <c r="E199" s="6">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F199" s="6" t="s">
         <v>383</v>
@@ -5968,7 +5972,7 @@
       <c r="G199" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="H199" s="12"/>
+      <c r="H199" s="7"/>
     </row>
     <row r="200" spans="1:9">
       <c r="C200" s="4">
@@ -5986,7 +5990,7 @@
       <c r="G200" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="H200" s="11"/>
+      <c r="H200" s="12"/>
     </row>
     <row r="201" spans="1:9">
       <c r="C201" s="4">
@@ -6004,7 +6008,7 @@
       <c r="G201" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="H201" s="11"/>
+      <c r="H201" s="12"/>
     </row>
     <row r="202" spans="1:9">
       <c r="C202" s="4">
@@ -6014,7 +6018,7 @@
         <v>9</v>
       </c>
       <c r="E202" s="6">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>389</v>
@@ -6032,7 +6036,7 @@
         <v>9</v>
       </c>
       <c r="E203" s="6">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F203" s="6" t="s">
         <v>391</v>
@@ -6169,7 +6173,7 @@
       <c r="G210" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="H210" s="16"/>
+      <c r="H210" s="23"/>
     </row>
     <row r="211" spans="3:8">
       <c r="C211" s="4">
@@ -6179,7 +6183,7 @@
         <v>9</v>
       </c>
       <c r="E211" s="6">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F211" s="6" t="s">
         <v>408</v>
@@ -6187,7 +6191,7 @@
       <c r="G211" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="H211" s="16"/>
+      <c r="H211" s="23"/>
     </row>
     <row r="212" spans="3:8">
       <c r="C212" s="4">
@@ -6205,7 +6209,7 @@
       <c r="G212" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="H212" s="16"/>
+      <c r="H212" s="21"/>
     </row>
     <row r="213" spans="3:8">
       <c r="C213" s="4">
@@ -6215,7 +6219,7 @@
         <v>9</v>
       </c>
       <c r="E213" s="6">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F213" s="6" t="s">
         <v>412</v>
@@ -6223,6 +6227,7 @@
       <c r="G213" s="16" t="s">
         <v>413</v>
       </c>
+      <c r="H213" s="11"/>
     </row>
     <row r="214" spans="3:8">
       <c r="C214" s="4">
@@ -6305,7 +6310,9 @@
       <c r="F218" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="G218" s="16"/>
+      <c r="G218" s="16" t="s">
+        <v>422</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="425">
   <si>
     <t>Id</t>
   </si>
@@ -1345,6 +1345,12 @@
   </si>
   <si>
     <t>绿茵世界</t>
+  </si>
+  <si>
+    <t>WJBeta223</t>
+  </si>
+  <si>
+    <t>飞龙在天</t>
   </si>
 </sst>
 </file>
@@ -2433,7 +2439,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I218"/>
+  <dimension ref="A3:I219"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6314,6 +6320,23 @@
         <v>422</v>
       </c>
     </row>
+    <row r="219" spans="3:8">
+      <c r="C219" s="4">
+        <v>223</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E219" s="6">
+        <v>223</v>
+      </c>
+      <c r="F219" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="G219" s="14" t="s">
+        <v>424</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="427">
   <si>
     <t>Id</t>
   </si>
@@ -1351,6 +1351,12 @@
   </si>
   <si>
     <t>飞龙在天</t>
+  </si>
+  <si>
+    <t>WJBeta224</t>
+  </si>
+  <si>
+    <t>永恒秘境</t>
   </si>
 </sst>
 </file>
@@ -2439,7 +2445,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I219"/>
+  <dimension ref="A3:I220"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6337,6 +6343,23 @@
         <v>424</v>
       </c>
     </row>
+    <row r="220" spans="3:8">
+      <c r="C220" s="4">
+        <v>224</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E220" s="6">
+        <v>224</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="G220" s="14" t="s">
+        <v>426</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="428">
   <si>
     <t>Id</t>
   </si>
@@ -1357,6 +1357,9 @@
   </si>
   <si>
     <t>永恒秘境</t>
+  </si>
+  <si>
+    <t>WJBeta225</t>
   </si>
 </sst>
 </file>
@@ -2445,7 +2448,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I220"/>
+  <dimension ref="A3:I221"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6360,6 +6363,21 @@
         <v>426</v>
       </c>
     </row>
+    <row r="221" spans="3:8">
+      <c r="C221" s="4">
+        <v>225</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E221" s="6">
+        <v>225</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G221" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="429">
   <si>
     <t>Id</t>
   </si>
@@ -1360,6 +1360,9 @@
   </si>
   <si>
     <t>WJBeta225</t>
+  </si>
+  <si>
+    <t>陌上花开</t>
   </si>
 </sst>
 </file>
@@ -1568,12 +1571,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6376,7 +6379,9 @@
       <c r="F221" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="G221" s="16"/>
+      <c r="G221" s="16" t="s">
+        <v>428</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="431">
   <si>
     <t>Id</t>
   </si>
@@ -1363,6 +1363,12 @@
   </si>
   <si>
     <t>陌上花开</t>
+  </si>
+  <si>
+    <t>WJBeta226</t>
+  </si>
+  <si>
+    <t>一剑惊鸿</t>
   </si>
 </sst>
 </file>
@@ -1571,12 +1577,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2451,7 +2457,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I221"/>
+  <dimension ref="A3:I222"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6383,6 +6389,23 @@
         <v>428</v>
       </c>
     </row>
+    <row r="222" spans="3:8">
+      <c r="C222" s="4">
+        <v>226</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" s="6">
+        <v>226</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="G222" s="14" t="s">
+        <v>430</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="432">
   <si>
     <t>Id</t>
   </si>
@@ -1369,6 +1369,9 @@
   </si>
   <si>
     <t>一剑惊鸿</t>
+  </si>
+  <si>
+    <t>WJBeta227</t>
   </si>
 </sst>
 </file>
@@ -2457,7 +2460,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I222"/>
+  <dimension ref="A3:I223"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6406,6 +6409,21 @@
         <v>430</v>
       </c>
     </row>
+    <row r="223" spans="3:8">
+      <c r="C223" s="4">
+        <v>227</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" s="6">
+        <v>227</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G223" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="433">
   <si>
     <t>Id</t>
   </si>
@@ -1372,6 +1372,9 @@
   </si>
   <si>
     <t>WJBeta227</t>
+  </si>
+  <si>
+    <t>逐光</t>
   </si>
 </sst>
 </file>
@@ -6422,7 +6425,9 @@
       <c r="F223" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="G223" s="16"/>
+      <c r="G223" s="16" t="s">
+        <v>432</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="434">
   <si>
     <t>Id</t>
   </si>
@@ -1375,6 +1375,9 @@
   </si>
   <si>
     <t>逐光</t>
+  </si>
+  <si>
+    <t>WJBeta228</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2466,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I223"/>
+  <dimension ref="A3:I224"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6429,6 +6432,21 @@
         <v>432</v>
       </c>
     </row>
+    <row r="224" spans="3:8">
+      <c r="C224" s="4">
+        <v>228</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="6">
+        <v>228</v>
+      </c>
+      <c r="F224" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="G224" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -2081,7 +2081,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2107,8 +2107,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2116,7 +2115,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -5799,7 +5797,7 @@
         <v>9</v>
       </c>
       <c r="E188" s="6">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>361</v>
@@ -5807,7 +5805,7 @@
       <c r="G188" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="H188" s="11"/>
+      <c r="H188" s="7"/>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="4">
@@ -5817,7 +5815,7 @@
         <v>9</v>
       </c>
       <c r="E189" s="6">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F189" s="6" t="s">
         <v>363</v>
@@ -5825,7 +5823,7 @@
       <c r="G189" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="H189" s="11"/>
+      <c r="H189" s="7"/>
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="4">
@@ -5835,7 +5833,7 @@
         <v>9</v>
       </c>
       <c r="E190" s="6">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>365</v>
@@ -5843,7 +5841,7 @@
       <c r="G190" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="H190" s="17"/>
+      <c r="H190" s="8"/>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="4">
@@ -5853,7 +5851,7 @@
         <v>9</v>
       </c>
       <c r="E191" s="6">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>367</v>
@@ -5861,7 +5859,7 @@
       <c r="G191" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="H191" s="17"/>
+      <c r="H191" s="8"/>
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="4">
@@ -5879,7 +5877,7 @@
       <c r="G192" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="H192" s="18"/>
+      <c r="H192" s="17"/>
     </row>
     <row r="193" spans="1:9">
       <c r="C193" s="4">
@@ -5897,7 +5895,7 @@
       <c r="G193" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="H193" s="18"/>
+      <c r="H193" s="17"/>
     </row>
     <row r="194" spans="1:9">
       <c r="C194" s="4">
@@ -5915,7 +5913,7 @@
       <c r="G194" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="H194" s="12"/>
+      <c r="H194" s="11"/>
     </row>
     <row r="195" spans="1:9">
       <c r="C195" s="4">
@@ -5933,7 +5931,7 @@
       <c r="G195" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="H195" s="12"/>
+      <c r="H195" s="11"/>
     </row>
     <row r="196" spans="1:9">
       <c r="C196" s="4">
@@ -5943,7 +5941,7 @@
         <v>9</v>
       </c>
       <c r="E196" s="6">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>377</v>
@@ -5951,7 +5949,7 @@
       <c r="G196" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="H196" s="7"/>
+      <c r="H196" s="11"/>
     </row>
     <row r="197" spans="1:9">
       <c r="C197" s="4">
@@ -5961,7 +5959,7 @@
         <v>9</v>
       </c>
       <c r="E197" s="6">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F197" s="6" t="s">
         <v>379</v>
@@ -5969,7 +5967,7 @@
       <c r="G197" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="H197" s="7"/>
+      <c r="H197" s="11"/>
     </row>
     <row r="198" spans="1:9">
       <c r="C198" s="4">
@@ -5979,7 +5977,7 @@
         <v>9</v>
       </c>
       <c r="E198" s="6">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>381</v>
@@ -5987,7 +5985,7 @@
       <c r="G198" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="H198" s="7"/>
+      <c r="H198" s="11"/>
     </row>
     <row r="199" spans="1:9">
       <c r="C199" s="4">
@@ -5997,7 +5995,7 @@
         <v>9</v>
       </c>
       <c r="E199" s="6">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F199" s="6" t="s">
         <v>383</v>
@@ -6005,7 +6003,7 @@
       <c r="G199" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="H199" s="7"/>
+      <c r="H199" s="11"/>
     </row>
     <row r="200" spans="1:9">
       <c r="C200" s="4">
@@ -6098,40 +6096,40 @@
       <c r="H204" s="11"/>
     </row>
     <row r="205" s="2" customFormat="1" spans="1:9">
-      <c r="C205" s="19">
+      <c r="C205" s="18">
         <v>202</v>
       </c>
-      <c r="D205" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E205" s="20">
+      <c r="D205" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="19">
         <v>202</v>
       </c>
-      <c r="F205" s="20" t="s">
+      <c r="F205" s="19" t="s">
         <v>395</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="I205" s="17"/>
+      <c r="I205" s="8"/>
     </row>
     <row r="206" s="2" customFormat="1" spans="1:9">
-      <c r="C206" s="19">
+      <c r="C206" s="18">
         <v>203</v>
       </c>
-      <c r="D206" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" s="20">
+      <c r="D206" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="19">
         <v>203</v>
       </c>
-      <c r="F206" s="20" t="s">
+      <c r="F206" s="19" t="s">
         <v>397</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="I206" s="17"/>
+      <c r="I206" s="8"/>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="3" t="s">
@@ -6152,7 +6150,7 @@
       <c r="G207" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="H207" s="21"/>
+      <c r="H207" s="20"/>
     </row>
     <row r="208" spans="1:9">
       <c r="C208" s="4">
@@ -6162,7 +6160,7 @@
         <v>9</v>
       </c>
       <c r="E208" s="6">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>402</v>
@@ -6170,7 +6168,7 @@
       <c r="G208" s="16" t="s">
         <v>403</v>
       </c>
-      <c r="H208" s="22"/>
+      <c r="H208" s="20"/>
     </row>
     <row r="209" spans="3:8">
       <c r="C209" s="4">
@@ -6180,7 +6178,7 @@
         <v>9</v>
       </c>
       <c r="E209" s="6">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F209" s="6" t="s">
         <v>404</v>
@@ -6188,7 +6186,7 @@
       <c r="G209" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="H209" s="22"/>
+      <c r="H209" s="20"/>
     </row>
     <row r="210" spans="3:8">
       <c r="C210" s="4">
@@ -6206,7 +6204,7 @@
       <c r="G210" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="H210" s="23"/>
+      <c r="H210" s="21"/>
     </row>
     <row r="211" spans="3:8">
       <c r="C211" s="4">
@@ -6224,7 +6222,7 @@
       <c r="G211" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="H211" s="23"/>
+      <c r="H211" s="21"/>
     </row>
     <row r="212" spans="3:8">
       <c r="C212" s="4">
@@ -6242,7 +6240,7 @@
       <c r="G212" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="H212" s="21"/>
+      <c r="H212" s="20"/>
     </row>
     <row r="213" spans="3:8">
       <c r="C213" s="4">
@@ -6278,6 +6276,7 @@
       <c r="G214" s="16" t="s">
         <v>415</v>
       </c>
+      <c r="H214" s="12"/>
     </row>
     <row r="215" spans="3:8">
       <c r="C215" s="4">
@@ -6287,7 +6286,7 @@
         <v>9</v>
       </c>
       <c r="E215" s="6">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F215" s="6" t="s">
         <v>416</v>
@@ -6295,6 +6294,7 @@
       <c r="G215" s="14" t="s">
         <v>417</v>
       </c>
+      <c r="H215" s="12"/>
     </row>
     <row r="216" spans="3:8">
       <c r="C216" s="4">
@@ -6312,6 +6312,7 @@
       <c r="G216" s="14" t="s">
         <v>419</v>
       </c>
+      <c r="H216" s="11"/>
     </row>
     <row r="217" spans="3:8">
       <c r="C217" s="4">
@@ -6321,7 +6322,7 @@
         <v>9</v>
       </c>
       <c r="E217" s="6">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F217" s="6" t="s">
         <v>420</v>
@@ -6329,6 +6330,7 @@
       <c r="G217" s="16" t="s">
         <v>40</v>
       </c>
+      <c r="H217" s="11"/>
     </row>
     <row r="218" spans="3:8">
       <c r="C218" s="4">
@@ -6346,6 +6348,7 @@
       <c r="G218" s="16" t="s">
         <v>422</v>
       </c>
+      <c r="H218" s="12"/>
     </row>
     <row r="219" spans="3:8">
       <c r="C219" s="4">
@@ -6355,7 +6358,7 @@
         <v>9</v>
       </c>
       <c r="E219" s="6">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F219" s="6" t="s">
         <v>423</v>
@@ -6363,6 +6366,7 @@
       <c r="G219" s="14" t="s">
         <v>424</v>
       </c>
+      <c r="H219" s="12"/>
     </row>
     <row r="220" spans="3:8">
       <c r="C220" s="4">

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="14385" windowHeight="12945"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="436">
   <si>
     <t>Id</t>
   </si>
@@ -1378,6 +1378,12 @@
   </si>
   <si>
     <t>WJBeta228</t>
+  </si>
+  <si>
+    <t>长安故梦</t>
+  </si>
+  <si>
+    <t>WJBeta229</t>
   </si>
 </sst>
 </file>
@@ -2464,7 +2470,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I224"/>
+  <dimension ref="A3:I225"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6449,7 +6455,24 @@
       <c r="F224" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="G224" s="16"/>
+      <c r="G224" s="16" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="225" spans="3:7">
+      <c r="C225" s="4">
+        <v>229</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" s="6">
+        <v>229</v>
+      </c>
+      <c r="F225" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G225" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14385" windowHeight="12945"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="437">
   <si>
     <t>Id</t>
   </si>
@@ -1384,6 +1384,9 @@
   </si>
   <si>
     <t>WJBeta229</t>
+  </si>
+  <si>
+    <t>星尘圣殿</t>
   </si>
 </sst>
 </file>
@@ -2087,7 +2090,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2122,6 +2125,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6472,7 +6476,9 @@
       <c r="F225" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="G225" s="14"/>
+      <c r="G225" s="22" t="s">
+        <v>436</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -59,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="438">
   <si>
     <t>Id</t>
   </si>
@@ -1387,6 +1392,9 @@
   </si>
   <si>
     <t>星尘圣殿</t>
+  </si>
+  <si>
+    <t>WJBeta230</t>
   </si>
 </sst>
 </file>
@@ -1595,12 +1603,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2090,7 +2098,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2125,7 +2133,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2474,7 +2481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I225"/>
+  <dimension ref="A3:I226"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6476,9 +6483,24 @@
       <c r="F225" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="G225" s="22" t="s">
+      <c r="G225" s="14" t="s">
         <v>436</v>
       </c>
+    </row>
+    <row r="226" spans="3:7">
+      <c r="C226" s="4">
+        <v>230</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" s="6">
+        <v>230</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G226" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="440">
   <si>
     <t>Id</t>
   </si>
@@ -1395,6 +1395,12 @@
   </si>
   <si>
     <t>WJBeta230</t>
+  </si>
+  <si>
+    <t>风语神殿</t>
+  </si>
+  <si>
+    <t>WJBeta231</t>
   </si>
 </sst>
 </file>
@@ -1603,12 +1609,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2481,7 +2487,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I226"/>
+  <dimension ref="A3:I227"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6500,7 +6506,24 @@
       <c r="F226" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="G226" s="14"/>
+      <c r="G226" s="14" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="227" spans="3:7">
+      <c r="C227" s="4">
+        <v>231</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227" s="6">
+        <v>231</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G227" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="441">
   <si>
     <t>Id</t>
   </si>
@@ -1401,6 +1401,9 @@
   </si>
   <si>
     <t>WJBeta231</t>
+  </si>
+  <si>
+    <t>霜烬王座</t>
   </si>
 </sst>
 </file>
@@ -2104,7 +2107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2139,6 +2142,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6523,7 +6527,9 @@
       <c r="F227" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="G227" s="16"/>
+      <c r="G227" s="22" t="s">
+        <v>440</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="442">
   <si>
     <t>Id</t>
   </si>
@@ -1404,6 +1404,9 @@
   </si>
   <si>
     <t>霜烬王座</t>
+  </si>
+  <si>
+    <t>WJBeta232</t>
   </si>
 </sst>
 </file>
@@ -2107,7 +2110,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2142,7 +2145,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2491,7 +2493,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I227"/>
+  <dimension ref="A3:I228"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6527,9 +6529,24 @@
       <c r="F227" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="G227" s="22" t="s">
+      <c r="G227" s="14" t="s">
         <v>440</v>
       </c>
+    </row>
+    <row r="228" spans="3:7">
+      <c r="C228" s="4">
+        <v>232</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E228" s="6">
+        <v>232</v>
+      </c>
+      <c r="F228" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G228" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="443">
   <si>
     <t>Id</t>
   </si>
@@ -1407,6 +1407,9 @@
   </si>
   <si>
     <t>WJBeta232</t>
+  </si>
+  <si>
+    <t>神之岛屿</t>
   </si>
 </sst>
 </file>
@@ -6546,7 +6549,9 @@
       <c r="F228" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="G228" s="16"/>
+      <c r="G228" s="16" t="s">
+        <v>442</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="444">
   <si>
     <t>Id</t>
   </si>
@@ -1410,6 +1410,9 @@
   </si>
   <si>
     <t>神之岛屿</t>
+  </si>
+  <si>
+    <t>WJBeta233</t>
   </si>
 </sst>
 </file>
@@ -2496,7 +2499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I228"/>
+  <dimension ref="A3:I229"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6553,6 +6556,21 @@
         <v>442</v>
       </c>
     </row>
+    <row r="229" spans="3:7">
+      <c r="C229" s="4">
+        <v>233</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229" s="6">
+        <v>233</v>
+      </c>
+      <c r="F229" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="G229" s="14"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="445">
   <si>
     <t>Id</t>
   </si>
@@ -1413,6 +1413,9 @@
   </si>
   <si>
     <t>WJBeta233</t>
+  </si>
+  <si>
+    <t>炽焰圣殿</t>
   </si>
 </sst>
 </file>
@@ -6569,7 +6572,9 @@
       <c r="F229" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="G229" s="14"/>
+      <c r="G229" s="14" t="s">
+        <v>444</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="447">
   <si>
     <t>Id</t>
   </si>
@@ -1416,6 +1416,12 @@
   </si>
   <si>
     <t>炽焰圣殿</t>
+  </si>
+  <si>
+    <t>WJBeta234</t>
+  </si>
+  <si>
+    <t>不朽之城</t>
   </si>
 </sst>
 </file>
@@ -2119,7 +2125,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2154,6 +2160,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2502,7 +2509,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I229"/>
+  <dimension ref="A3:I230"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6576,6 +6583,23 @@
         <v>444</v>
       </c>
     </row>
+    <row r="230" spans="3:7">
+      <c r="C230" s="4">
+        <v>234</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E230" s="6">
+        <v>234</v>
+      </c>
+      <c r="F230" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="G230" s="22" t="s">
+        <v>446</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="448">
   <si>
     <t>Id</t>
   </si>
@@ -1422,6 +1422,9 @@
   </si>
   <si>
     <t>不朽之城</t>
+  </si>
+  <si>
+    <t>WJBeta235</t>
   </si>
 </sst>
 </file>
@@ -1630,12 +1633,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2125,7 +2128,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2160,7 +2163,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2509,7 +2511,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I230"/>
+  <dimension ref="A3:I231"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6596,9 +6598,24 @@
       <c r="F230" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="G230" s="22" t="s">
+      <c r="G230" s="14" t="s">
         <v>446</v>
       </c>
+    </row>
+    <row r="231" spans="3:7">
+      <c r="C231" s="4">
+        <v>235</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E231" s="6">
+        <v>235</v>
+      </c>
+      <c r="F231" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="G231" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Beta/StartZoneConfig@s.xlsx
@@ -1644,7 +1644,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1665,13 +1665,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1683,7 +1683,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2004,7 +2010,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2028,16 +2034,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2046,89 +2052,89 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2146,23 +2152,26 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3126,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="E37" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>71</v>
@@ -3134,7 +3143,7 @@
       <c r="G37" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H37" s="9"/>
+      <c r="H37" s="7"/>
     </row>
     <row r="38" spans="3:8">
       <c r="C38" s="4">
@@ -3144,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="E38" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>73</v>
@@ -3152,7 +3161,7 @@
       <c r="G38" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H38" s="9"/>
+      <c r="H38" s="7"/>
     </row>
     <row r="39" spans="3:8">
       <c r="C39" s="4">
@@ -3162,7 +3171,7 @@
         <v>9</v>
       </c>
       <c r="E39" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>75</v>
@@ -3170,7 +3179,7 @@
       <c r="G39" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H39" s="9"/>
+      <c r="H39" s="7"/>
     </row>
     <row r="40" spans="3:8">
       <c r="C40" s="4">
@@ -3180,7 +3189,7 @@
         <v>9</v>
       </c>
       <c r="E40" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>77</v>
@@ -3188,7 +3197,7 @@
       <c r="G40" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H40" s="9"/>
+      <c r="H40" s="7"/>
     </row>
     <row r="41" spans="3:8">
       <c r="C41" s="4">
@@ -3198,7 +3207,7 @@
         <v>9</v>
       </c>
       <c r="E41" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>79</v>
@@ -3206,7 +3215,7 @@
       <c r="G41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H41" s="9"/>
+      <c r="H41" s="7"/>
     </row>
     <row r="42" spans="3:8">
       <c r="C42" s="4">
@@ -3216,7 +3225,7 @@
         <v>9</v>
       </c>
       <c r="E42" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>81</v>
@@ -3224,7 +3233,7 @@
       <c r="G42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H42" s="9"/>
+      <c r="H42" s="7"/>
     </row>
     <row r="43" spans="3:8">
       <c r="C43" s="4">
@@ -3234,7 +3243,7 @@
         <v>9</v>
       </c>
       <c r="E43" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>83</v>
@@ -3242,7 +3251,7 @@
       <c r="G43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H43" s="10"/>
+      <c r="H43" s="9"/>
     </row>
     <row r="44" spans="3:8">
       <c r="C44" s="4">
@@ -3252,7 +3261,7 @@
         <v>9</v>
       </c>
       <c r="E44" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>85</v>
@@ -3260,7 +3269,7 @@
       <c r="G44" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H44" s="10"/>
+      <c r="H44" s="9"/>
     </row>
     <row r="45" spans="3:8">
       <c r="C45" s="4">
@@ -3270,7 +3279,7 @@
         <v>9</v>
       </c>
       <c r="E45" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>87</v>
@@ -3278,7 +3287,7 @@
       <c r="G45" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H45" s="9"/>
+      <c r="H45" s="7"/>
     </row>
     <row r="46" spans="3:8">
       <c r="C46" s="4">
@@ -3288,7 +3297,7 @@
         <v>9</v>
       </c>
       <c r="E46" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>89</v>
@@ -3296,7 +3305,7 @@
       <c r="G46" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H46" s="9"/>
+      <c r="H46" s="7"/>
     </row>
     <row r="47" spans="3:8">
       <c r="C47" s="4">
@@ -3306,7 +3315,7 @@
         <v>9</v>
       </c>
       <c r="E47" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>91</v>
@@ -3314,7 +3323,7 @@
       <c r="G47" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H47" s="9"/>
+      <c r="H47" s="7"/>
     </row>
     <row r="48" spans="3:8">
       <c r="C48" s="4">
@@ -3324,7 +3333,7 @@
         <v>9</v>
       </c>
       <c r="E48" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>93</v>
@@ -3332,7 +3341,7 @@
       <c r="G48" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H48" s="9"/>
+      <c r="H48" s="7"/>
     </row>
     <row r="49" spans="3:8">
       <c r="C49" s="4">
@@ -3342,7 +3351,7 @@
         <v>9</v>
       </c>
       <c r="E49" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>95</v>
@@ -3350,7 +3359,7 @@
       <c r="G49" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H49" s="9"/>
+      <c r="H49" s="7"/>
     </row>
     <row r="50" spans="3:8">
       <c r="C50" s="4">
@@ -3360,7 +3369,7 @@
         <v>9</v>
       </c>
       <c r="E50" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>97</v>
@@ -3368,7 +3377,7 @@
       <c r="G50" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H50" s="9"/>
+      <c r="H50" s="7"/>
     </row>
     <row r="51" spans="3:8">
       <c r="C51" s="4">
@@ -3378,7 +3387,7 @@
         <v>9</v>
       </c>
       <c r="E51" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>99</v>
@@ -3386,7 +3395,7 @@
       <c r="G51" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H51" s="9"/>
+      <c r="H51" s="7"/>
     </row>
     <row r="52" ht="13" customHeight="1" spans="3:8">
       <c r="C52" s="4">
@@ -3396,7 +3405,7 @@
         <v>9</v>
       </c>
       <c r="E52" s="6">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>101</v>
@@ -3404,7 +3413,7 @@
       <c r="G52" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H52" s="9"/>
+      <c r="H52" s="7"/>
     </row>
     <row r="53" spans="3:8">
       <c r="C53" s="4">
@@ -3422,7 +3431,7 @@
       <c r="G53" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H53" s="11"/>
+      <c r="H53" s="10"/>
     </row>
     <row r="54" spans="3:8">
       <c r="C54" s="4">
@@ -3440,7 +3449,7 @@
       <c r="G54" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H54" s="11"/>
+      <c r="H54" s="10"/>
     </row>
     <row r="55" spans="3:8">
       <c r="C55" s="4">
@@ -3458,7 +3467,7 @@
       <c r="G55" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H55" s="11"/>
+      <c r="H55" s="10"/>
     </row>
     <row r="56" spans="3:8">
       <c r="C56" s="4">
@@ -3476,7 +3485,7 @@
       <c r="G56" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H56" s="11"/>
+      <c r="H56" s="10"/>
     </row>
     <row r="57" spans="3:8">
       <c r="C57" s="4">
@@ -3494,7 +3503,7 @@
       <c r="G57" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H57" s="11"/>
+      <c r="H57" s="10"/>
     </row>
     <row r="58" spans="3:8">
       <c r="C58" s="4">
@@ -3512,7 +3521,7 @@
       <c r="G58" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H58" s="11"/>
+      <c r="H58" s="10"/>
     </row>
     <row r="59" spans="3:8">
       <c r="C59" s="4">
@@ -3530,7 +3539,7 @@
       <c r="G59" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="H59" s="11"/>
+      <c r="H59" s="10"/>
     </row>
     <row r="60" spans="3:8">
       <c r="C60" s="4">
@@ -3548,7 +3557,7 @@
       <c r="G60" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H60" s="11"/>
+      <c r="H60" s="10"/>
     </row>
     <row r="61" spans="3:8">
       <c r="C61" s="4">
@@ -3566,7 +3575,7 @@
       <c r="G61" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H61" s="11"/>
+      <c r="H61" s="10"/>
     </row>
     <row r="62" spans="3:8">
       <c r="C62" s="4">
@@ -3584,7 +3593,7 @@
       <c r="G62" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H62" s="11"/>
+      <c r="H62" s="10"/>
     </row>
     <row r="63" spans="3:8">
       <c r="C63" s="4">
@@ -3602,7 +3611,7 @@
       <c r="G63" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H63" s="11"/>
+      <c r="H63" s="10"/>
     </row>
     <row r="64" spans="3:8">
       <c r="C64" s="4">
@@ -3620,7 +3629,7 @@
       <c r="G64" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H64" s="11"/>
+      <c r="H64" s="10"/>
     </row>
     <row r="65" spans="3:8">
       <c r="C65" s="4">
@@ -3638,7 +3647,7 @@
       <c r="G65" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H65" s="11"/>
+      <c r="H65" s="10"/>
     </row>
     <row r="66" spans="3:8">
       <c r="C66" s="4">
@@ -3656,7 +3665,7 @@
       <c r="G66" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H66" s="11"/>
+      <c r="H66" s="10"/>
     </row>
     <row r="67" spans="3:8">
       <c r="C67" s="4">
@@ -3674,7 +3683,7 @@
       <c r="G67" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H67" s="11"/>
+      <c r="H67" s="10"/>
     </row>
     <row r="68" spans="3:8">
       <c r="C68" s="4">
@@ -3692,7 +3701,7 @@
       <c r="G68" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H68" s="11"/>
+      <c r="H68" s="10"/>
     </row>
     <row r="69" spans="3:8">
       <c r="C69" s="4">
@@ -3702,7 +3711,7 @@
         <v>9</v>
       </c>
       <c r="E69" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>134</v>
@@ -3710,7 +3719,7 @@
       <c r="G69" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H69" s="12"/>
+      <c r="H69" s="10"/>
     </row>
     <row r="70" spans="3:8">
       <c r="C70" s="4">
@@ -3720,7 +3729,7 @@
         <v>9</v>
       </c>
       <c r="E70" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>135</v>
@@ -3728,7 +3737,7 @@
       <c r="G70" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H70" s="12"/>
+      <c r="H70" s="10"/>
     </row>
     <row r="71" spans="3:8">
       <c r="C71" s="4">
@@ -3738,7 +3747,7 @@
         <v>9</v>
       </c>
       <c r="E71" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F71" s="6" t="s">
         <v>137</v>
@@ -3746,7 +3755,7 @@
       <c r="G71" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H71" s="12"/>
+      <c r="H71" s="10"/>
     </row>
     <row r="72" spans="3:8">
       <c r="C72" s="4">
@@ -3756,7 +3765,7 @@
         <v>9</v>
       </c>
       <c r="E72" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>139</v>
@@ -3764,7 +3773,7 @@
       <c r="G72" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H72" s="12"/>
+      <c r="H72" s="10"/>
     </row>
     <row r="73" spans="3:8">
       <c r="C73" s="4">
@@ -3774,7 +3783,7 @@
         <v>9</v>
       </c>
       <c r="E73" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>140</v>
@@ -3782,7 +3791,7 @@
       <c r="G73" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H73" s="12"/>
+      <c r="H73" s="10"/>
     </row>
     <row r="74" spans="3:8">
       <c r="C74" s="4">
@@ -3792,7 +3801,7 @@
         <v>9</v>
       </c>
       <c r="E74" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>142</v>
@@ -3800,7 +3809,7 @@
       <c r="G74" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H74" s="12"/>
+      <c r="H74" s="10"/>
     </row>
     <row r="75" spans="3:8">
       <c r="C75" s="4">
@@ -3810,7 +3819,7 @@
         <v>9</v>
       </c>
       <c r="E75" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>144</v>
@@ -3818,7 +3827,7 @@
       <c r="G75" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H75" s="12"/>
+      <c r="H75" s="10"/>
     </row>
     <row r="76" spans="3:8">
       <c r="C76" s="4">
@@ -3828,7 +3837,7 @@
         <v>9</v>
       </c>
       <c r="E76" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>146</v>
@@ -3836,7 +3845,7 @@
       <c r="G76" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H76" s="12"/>
+      <c r="H76" s="10"/>
     </row>
     <row r="77" spans="3:8">
       <c r="C77" s="4">
@@ -3846,7 +3855,7 @@
         <v>9</v>
       </c>
       <c r="E77" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>148</v>
@@ -3854,7 +3863,7 @@
       <c r="G77" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H77" s="12"/>
+      <c r="H77" s="10"/>
     </row>
     <row r="78" spans="3:8">
       <c r="C78" s="4">
@@ -3864,7 +3873,7 @@
         <v>9</v>
       </c>
       <c r="E78" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>149</v>
@@ -3872,7 +3881,7 @@
       <c r="G78" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H78" s="12"/>
+      <c r="H78" s="10"/>
     </row>
     <row r="79" spans="3:8">
       <c r="C79" s="4">
@@ -3882,7 +3891,7 @@
         <v>9</v>
       </c>
       <c r="E79" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>151</v>
@@ -3890,7 +3899,7 @@
       <c r="G79" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H79" s="12"/>
+      <c r="H79" s="10"/>
     </row>
     <row r="80" spans="3:8">
       <c r="C80" s="4">
@@ -3900,7 +3909,7 @@
         <v>9</v>
       </c>
       <c r="E80" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>153</v>
@@ -3908,7 +3917,7 @@
       <c r="G80" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H80" s="12"/>
+      <c r="H80" s="10"/>
     </row>
     <row r="81" spans="3:9">
       <c r="C81" s="4">
@@ -3918,7 +3927,7 @@
         <v>9</v>
       </c>
       <c r="E81" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>155</v>
@@ -3926,7 +3935,7 @@
       <c r="G81" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H81" s="12"/>
+      <c r="H81" s="10"/>
     </row>
     <row r="82" spans="3:9">
       <c r="C82" s="4">
@@ -3936,7 +3945,7 @@
         <v>9</v>
       </c>
       <c r="E82" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>157</v>
@@ -3944,7 +3953,7 @@
       <c r="G82" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H82" s="12"/>
+      <c r="H82" s="10"/>
     </row>
     <row r="83" spans="3:9">
       <c r="C83" s="4">
@@ -3954,7 +3963,7 @@
         <v>9</v>
       </c>
       <c r="E83" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F83" s="6" t="s">
         <v>158</v>
@@ -3962,7 +3971,7 @@
       <c r="G83" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H83" s="12"/>
+      <c r="H83" s="10"/>
     </row>
     <row r="84" spans="3:9">
       <c r="C84" s="4">
@@ -3972,7 +3981,7 @@
         <v>9</v>
       </c>
       <c r="E84" s="6">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>159</v>
@@ -3980,7 +3989,7 @@
       <c r="G84" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H84" s="12"/>
+      <c r="H84" s="10"/>
     </row>
     <row r="85" spans="3:9">
       <c r="C85" s="4">
@@ -4152,7 +4161,7 @@
         <v>9</v>
       </c>
       <c r="E94" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>179</v>
@@ -4160,7 +4169,7 @@
       <c r="G94" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="H94" s="11"/>
+      <c r="H94" s="7"/>
     </row>
     <row r="95" spans="3:9">
       <c r="C95" s="4">
@@ -4170,7 +4179,7 @@
         <v>9</v>
       </c>
       <c r="E95" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>181</v>
@@ -4178,7 +4187,7 @@
       <c r="G95" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="H95" s="11"/>
+      <c r="H95" s="7"/>
     </row>
     <row r="96" spans="3:9">
       <c r="C96" s="4">
@@ -4188,7 +4197,7 @@
         <v>9</v>
       </c>
       <c r="E96" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>183</v>
@@ -4196,7 +4205,7 @@
       <c r="G96" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="H96" s="11"/>
+      <c r="H96" s="7"/>
     </row>
     <row r="97" spans="3:8">
       <c r="C97" s="4">
@@ -4206,7 +4215,7 @@
         <v>9</v>
       </c>
       <c r="E97" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>185</v>
@@ -4214,7 +4223,7 @@
       <c r="G97" t="s">
         <v>186</v>
       </c>
-      <c r="H97" s="11"/>
+      <c r="H97" s="7"/>
     </row>
     <row r="98" spans="3:8">
       <c r="C98" s="4">
@@ -4224,7 +4233,7 @@
         <v>9</v>
       </c>
       <c r="E98" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>187</v>
@@ -4232,7 +4241,7 @@
       <c r="G98" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="H98" s="11"/>
+      <c r="H98" s="7"/>
     </row>
     <row r="99" spans="3:8">
       <c r="C99" s="4">
@@ -4242,7 +4251,7 @@
         <v>9</v>
       </c>
       <c r="E99" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>189</v>
@@ -4250,7 +4259,7 @@
       <c r="G99" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="H99" s="11"/>
+      <c r="H99" s="7"/>
     </row>
     <row r="100" spans="3:8">
       <c r="C100" s="4">
@@ -4260,7 +4269,7 @@
         <v>9</v>
       </c>
       <c r="E100" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>191</v>
@@ -4268,7 +4277,7 @@
       <c r="G100" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H100" s="11"/>
+      <c r="H100" s="7"/>
     </row>
     <row r="101" spans="3:8">
       <c r="C101" s="4">
@@ -4278,7 +4287,7 @@
         <v>9</v>
       </c>
       <c r="E101" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>193</v>
@@ -4286,7 +4295,7 @@
       <c r="G101" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H101" s="11"/>
+      <c r="H101" s="7"/>
     </row>
     <row r="102" spans="3:8">
       <c r="C102" s="4">
@@ -4296,7 +4305,7 @@
         <v>9</v>
       </c>
       <c r="E102" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>195</v>
@@ -4304,7 +4313,7 @@
       <c r="G102" t="s">
         <v>196</v>
       </c>
-      <c r="H102" s="11"/>
+      <c r="H102" s="7"/>
     </row>
     <row r="103" spans="3:8">
       <c r="C103" s="4">
@@ -4314,7 +4323,7 @@
         <v>9</v>
       </c>
       <c r="E103" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>197</v>
@@ -4322,7 +4331,7 @@
       <c r="G103" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="H103" s="11"/>
+      <c r="H103" s="7"/>
     </row>
     <row r="104" spans="3:8">
       <c r="C104" s="4">
@@ -4332,7 +4341,7 @@
         <v>9</v>
       </c>
       <c r="E104" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>199</v>
@@ -4340,7 +4349,7 @@
       <c r="G104" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H104" s="11"/>
+      <c r="H104" s="7"/>
     </row>
     <row r="105" spans="3:8">
       <c r="C105" s="4">
@@ -4350,7 +4359,7 @@
         <v>9</v>
       </c>
       <c r="E105" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>201</v>
@@ -4358,7 +4367,7 @@
       <c r="G105" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H105" s="11"/>
+      <c r="H105" s="7"/>
     </row>
     <row r="106" spans="3:8">
       <c r="C106" s="4">
@@ -4368,7 +4377,7 @@
         <v>9</v>
       </c>
       <c r="E106" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>203</v>
@@ -4376,7 +4385,7 @@
       <c r="G106" t="s">
         <v>204</v>
       </c>
-      <c r="H106" s="11"/>
+      <c r="H106" s="7"/>
     </row>
     <row r="107" spans="3:8">
       <c r="C107" s="4">
@@ -4386,7 +4395,7 @@
         <v>9</v>
       </c>
       <c r="E107" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>205</v>
@@ -4394,7 +4403,7 @@
       <c r="G107" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H107" s="11"/>
+      <c r="H107" s="7"/>
     </row>
     <row r="108" spans="3:8">
       <c r="C108" s="4">
@@ -4404,7 +4413,7 @@
         <v>9</v>
       </c>
       <c r="E108" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>207</v>
@@ -4412,7 +4421,7 @@
       <c r="G108" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="H108" s="11"/>
+      <c r="H108" s="7"/>
     </row>
     <row r="109" spans="3:8">
       <c r="C109" s="4">
@@ -4422,7 +4431,7 @@
         <v>9</v>
       </c>
       <c r="E109" s="6">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>209</v>
@@ -4430,7 +4439,7 @@
       <c r="G109" t="s">
         <v>210</v>
       </c>
-      <c r="H109" s="11"/>
+      <c r="H109" s="7"/>
     </row>
     <row r="110" spans="3:8">
       <c r="C110" s="4">
@@ -4448,7 +4457,7 @@
       <c r="G110" t="s">
         <v>212</v>
       </c>
-      <c r="H110" s="13"/>
+      <c r="H110" s="7"/>
     </row>
     <row r="111" spans="3:8">
       <c r="C111" s="4">
@@ -4466,7 +4475,7 @@
       <c r="G111" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="H111" s="13"/>
+      <c r="H111" s="11"/>
     </row>
     <row r="112" spans="3:8">
       <c r="C112" s="4">
@@ -4484,7 +4493,7 @@
       <c r="G112" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="H112" s="13"/>
+      <c r="H112" s="11"/>
     </row>
     <row r="113" spans="3:8">
       <c r="C113" s="4">
@@ -4502,7 +4511,7 @@
       <c r="G113" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H113" s="13"/>
+      <c r="H113" s="11"/>
     </row>
     <row r="114" spans="3:8">
       <c r="C114" s="4">
@@ -4520,7 +4529,7 @@
       <c r="G114" t="s">
         <v>220</v>
       </c>
-      <c r="H114" s="13"/>
+      <c r="H114" s="11"/>
     </row>
     <row r="115" spans="3:8">
       <c r="C115" s="4">
@@ -4538,7 +4547,7 @@
       <c r="G115" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="H115" s="13"/>
+      <c r="H115" s="11"/>
     </row>
     <row r="116" spans="3:8">
       <c r="C116" s="4">
@@ -4556,7 +4565,7 @@
       <c r="G116" t="s">
         <v>224</v>
       </c>
-      <c r="H116" s="13"/>
+      <c r="H116" s="11"/>
     </row>
     <row r="117" spans="3:8">
       <c r="C117" s="4">
@@ -4574,7 +4583,7 @@
       <c r="G117" t="s">
         <v>226</v>
       </c>
-      <c r="H117" s="13"/>
+      <c r="H117" s="11"/>
     </row>
     <row r="118" spans="3:8">
       <c r="C118" s="4">
@@ -4592,7 +4601,7 @@
       <c r="G118" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="H118" s="13"/>
+      <c r="H118" s="11"/>
     </row>
     <row r="119" spans="3:8">
       <c r="C119" s="4">
@@ -4607,10 +4616,10 @@
       <c r="F119" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G119" s="14" t="s">
+      <c r="G119" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="H119" s="13"/>
+      <c r="H119" s="11"/>
     </row>
     <row r="120" spans="3:8">
       <c r="C120" s="4">
@@ -4628,7 +4637,7 @@
       <c r="G120" t="s">
         <v>232</v>
       </c>
-      <c r="H120" s="13"/>
+      <c r="H120" s="11"/>
     </row>
     <row r="121" spans="3:8">
       <c r="C121" s="4">
@@ -4646,7 +4655,7 @@
       <c r="G121" t="s">
         <v>234</v>
       </c>
-      <c r="H121" s="13"/>
+      <c r="H121" s="11"/>
     </row>
     <row r="122" spans="3:8">
       <c r="C122" s="4">
@@ -4664,7 +4673,7 @@
       <c r="G122" t="s">
         <v>236</v>
       </c>
-      <c r="H122" s="13"/>
+      <c r="H122" s="11"/>
     </row>
     <row r="123" spans="3:8">
       <c r="C123" s="4">
@@ -4679,10 +4688,10 @@
       <c r="F123" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="G123" s="14" t="s">
+      <c r="G123" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="H123" s="13"/>
+      <c r="H123" s="11"/>
     </row>
     <row r="124" spans="3:8">
       <c r="C124" s="4">
@@ -4700,7 +4709,7 @@
       <c r="G124" t="s">
         <v>240</v>
       </c>
-      <c r="H124" s="13"/>
+      <c r="H124" s="11"/>
     </row>
     <row r="125" spans="3:8">
       <c r="C125" s="4">
@@ -4718,7 +4727,7 @@
       <c r="G125" t="s">
         <v>242</v>
       </c>
-      <c r="H125" s="13"/>
+      <c r="H125" s="11"/>
     </row>
     <row r="126" spans="3:8">
       <c r="C126" s="4">
@@ -4728,7 +4737,7 @@
         <v>9</v>
       </c>
       <c r="E126" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>243</v>
@@ -4746,12 +4755,12 @@
         <v>9</v>
       </c>
       <c r="E127" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G127" s="14" t="s">
+      <c r="G127" s="12" t="s">
         <v>106</v>
       </c>
       <c r="H127" s="11"/>
@@ -4764,7 +4773,7 @@
         <v>9</v>
       </c>
       <c r="E128" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>246</v>
@@ -4782,7 +4791,7 @@
         <v>9</v>
       </c>
       <c r="E129" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>248</v>
@@ -4800,7 +4809,7 @@
         <v>9</v>
       </c>
       <c r="E130" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>250</v>
@@ -4818,7 +4827,7 @@
         <v>9</v>
       </c>
       <c r="E131" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>252</v>
@@ -4836,7 +4845,7 @@
         <v>9</v>
       </c>
       <c r="E132" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>254</v>
@@ -4872,12 +4881,12 @@
         <v>9</v>
       </c>
       <c r="E134" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="G134" s="14" t="s">
+      <c r="G134" s="12" t="s">
         <v>259</v>
       </c>
       <c r="H134" s="11"/>
@@ -4890,7 +4899,7 @@
         <v>9</v>
       </c>
       <c r="E135" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>260</v>
@@ -4908,7 +4917,7 @@
         <v>9</v>
       </c>
       <c r="E136" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>262</v>
@@ -4926,12 +4935,12 @@
         <v>9</v>
       </c>
       <c r="E137" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="G137" s="14" t="s">
+      <c r="G137" s="12" t="s">
         <v>265</v>
       </c>
       <c r="H137" s="11"/>
@@ -4944,12 +4953,12 @@
         <v>9</v>
       </c>
       <c r="E138" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G138" s="14" t="s">
+      <c r="G138" s="12" t="s">
         <v>267</v>
       </c>
       <c r="H138" s="11"/>
@@ -4962,12 +4971,12 @@
         <v>9</v>
       </c>
       <c r="E139" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G139" s="14" t="s">
+      <c r="G139" s="12" t="s">
         <v>269</v>
       </c>
       <c r="H139" s="11"/>
@@ -4980,12 +4989,12 @@
         <v>9</v>
       </c>
       <c r="E140" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="G140" s="14" t="s">
+      <c r="G140" s="12" t="s">
         <v>271</v>
       </c>
       <c r="H140" s="11"/>
@@ -4998,12 +5007,12 @@
         <v>9</v>
       </c>
       <c r="E141" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="G141" s="14" t="s">
+      <c r="G141" s="12" t="s">
         <v>273</v>
       </c>
       <c r="H141" s="11"/>
@@ -5016,12 +5025,12 @@
         <v>9</v>
       </c>
       <c r="E142" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="G142" s="14" t="s">
+      <c r="G142" s="12" t="s">
         <v>275</v>
       </c>
       <c r="H142" s="11"/>
@@ -5034,12 +5043,12 @@
         <v>9</v>
       </c>
       <c r="E143" s="6">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="G143" s="14" t="s">
+      <c r="G143" s="12" t="s">
         <v>277</v>
       </c>
       <c r="H143" s="11"/>
@@ -5057,10 +5066,10 @@
       <c r="F144" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="G144" s="14" t="s">
+      <c r="G144" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="H144" s="12"/>
+      <c r="H144" s="14"/>
     </row>
     <row r="145" spans="3:8">
       <c r="C145" s="4">
@@ -5075,10 +5084,10 @@
       <c r="F145" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="G145" s="14" t="s">
+      <c r="G145" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="H145" s="12"/>
+      <c r="H145" s="14"/>
     </row>
     <row r="146" spans="3:8">
       <c r="C146" s="4">
@@ -5093,10 +5102,10 @@
       <c r="F146" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="G146" s="14" t="s">
+      <c r="G146" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="H146" s="12"/>
+      <c r="H146" s="14"/>
     </row>
     <row r="147" spans="3:8">
       <c r="C147" s="4">
@@ -5111,10 +5120,10 @@
       <c r="F147" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="G147" s="14" t="s">
+      <c r="G147" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H147" s="12"/>
+      <c r="H147" s="14"/>
     </row>
     <row r="148" spans="3:8">
       <c r="C148" s="4">
@@ -5129,7 +5138,7 @@
       <c r="F148" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="G148" s="14" t="s">
+      <c r="G148" s="12" t="s">
         <v>284</v>
       </c>
       <c r="H148" s="15"/>
@@ -5147,7 +5156,7 @@
       <c r="F149" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="G149" s="14" t="s">
+      <c r="G149" s="12" t="s">
         <v>286</v>
       </c>
       <c r="H149" s="15"/>
@@ -5165,7 +5174,7 @@
       <c r="F150" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="G150" s="14" t="s">
+      <c r="G150" s="12" t="s">
         <v>288</v>
       </c>
       <c r="H150" s="15"/>
@@ -5183,7 +5192,7 @@
       <c r="F151" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="G151" s="14" t="s">
+      <c r="G151" s="12" t="s">
         <v>290</v>
       </c>
       <c r="H151" s="15"/>
@@ -5201,10 +5210,10 @@
       <c r="F152" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="G152" s="14" t="s">
+      <c r="G152" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H152" s="12"/>
+      <c r="H152" s="14"/>
     </row>
     <row r="153" spans="3:8">
       <c r="C153" s="4">
@@ -5219,10 +5228,10 @@
       <c r="F153" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="G153" s="14" t="s">
+      <c r="G153" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="H153" s="12"/>
+      <c r="H153" s="14"/>
     </row>
     <row r="154" spans="3:8">
       <c r="C154" s="4">
@@ -5237,10 +5246,10 @@
       <c r="F154" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="G154" s="14" t="s">
+      <c r="G154" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="H154" s="12"/>
+      <c r="H154" s="14"/>
     </row>
     <row r="155" spans="3:8">
       <c r="C155" s="4">
@@ -5255,10 +5264,10 @@
       <c r="F155" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="G155" s="14" t="s">
+      <c r="G155" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="H155" s="12"/>
+      <c r="H155" s="14"/>
     </row>
     <row r="156" spans="3:8">
       <c r="C156" s="4">
@@ -5276,7 +5285,7 @@
       <c r="G156" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="H156" s="12"/>
+      <c r="H156" s="14"/>
     </row>
     <row r="157" spans="3:8">
       <c r="C157" s="4">
@@ -5291,10 +5300,10 @@
       <c r="F157" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="G157" s="14" t="s">
+      <c r="G157" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="H157" s="12"/>
+      <c r="H157" s="14"/>
     </row>
     <row r="158" spans="3:8">
       <c r="C158" s="4">
@@ -5309,10 +5318,10 @@
       <c r="F158" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="G158" s="14" t="s">
+      <c r="G158" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="H158" s="12"/>
+      <c r="H158" s="14"/>
     </row>
     <row r="159" spans="3:8">
       <c r="C159" s="4">
@@ -5327,10 +5336,10 @@
       <c r="F159" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="G159" s="14" t="s">
+      <c r="G159" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="H159" s="12"/>
+      <c r="H159" s="14"/>
     </row>
     <row r="160" spans="3:8">
       <c r="C160" s="4">
@@ -5340,15 +5349,15 @@
         <v>9</v>
       </c>
       <c r="E160" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="G160" s="14" t="s">
+      <c r="G160" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="H160" s="11"/>
+      <c r="H160" s="14"/>
     </row>
     <row r="161" spans="3:8">
       <c r="C161" s="4">
@@ -5358,15 +5367,15 @@
         <v>9</v>
       </c>
       <c r="E161" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F161" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="G161" s="14" t="s">
+      <c r="G161" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="11"/>
+      <c r="H161" s="14"/>
     </row>
     <row r="162" spans="3:8">
       <c r="C162" s="4">
@@ -5376,15 +5385,15 @@
         <v>9</v>
       </c>
       <c r="E162" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="G162" s="14" t="s">
+      <c r="G162" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="H162" s="11"/>
+      <c r="H162" s="14"/>
     </row>
     <row r="163" spans="3:8">
       <c r="C163" s="4">
@@ -5394,15 +5403,15 @@
         <v>9</v>
       </c>
       <c r="E163" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F163" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="G163" s="14" t="s">
+      <c r="G163" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="H163" s="11"/>
+      <c r="H163" s="14"/>
     </row>
     <row r="164" spans="3:8">
       <c r="C164" s="4">
@@ -5412,15 +5421,15 @@
         <v>9</v>
       </c>
       <c r="E164" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="G164" s="14" t="s">
+      <c r="G164" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="H164" s="11"/>
+      <c r="H164" s="14"/>
     </row>
     <row r="165" spans="3:8">
       <c r="C165" s="4">
@@ -5430,15 +5439,15 @@
         <v>9</v>
       </c>
       <c r="E165" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F165" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G165" s="14" t="s">
+      <c r="G165" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="H165" s="11"/>
+      <c r="H165" s="14"/>
     </row>
     <row r="166" spans="3:8">
       <c r="C166" s="4">
@@ -5448,15 +5457,15 @@
         <v>9</v>
       </c>
       <c r="E166" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="G166" s="14" t="s">
+      <c r="G166" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="H166" s="11"/>
+      <c r="H166" s="14"/>
     </row>
     <row r="167" spans="3:8">
       <c r="C167" s="4">
@@ -5466,15 +5475,15 @@
         <v>9</v>
       </c>
       <c r="E167" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F167" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G167" s="14" t="s">
+      <c r="G167" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="H167" s="11"/>
+      <c r="H167" s="14"/>
     </row>
     <row r="168" spans="3:8">
       <c r="C168" s="4">
@@ -5484,15 +5493,15 @@
         <v>9</v>
       </c>
       <c r="E168" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="G168" s="14" t="s">
+      <c r="G168" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="H168" s="11"/>
+      <c r="H168" s="14"/>
     </row>
     <row r="169" spans="3:8">
       <c r="C169" s="4">
@@ -5502,15 +5511,15 @@
         <v>9</v>
       </c>
       <c r="E169" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="G169" s="14" t="s">
+      <c r="G169" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="H169" s="11"/>
+      <c r="H169" s="14"/>
     </row>
     <row r="170" spans="3:8">
       <c r="C170" s="4">
@@ -5520,15 +5529,15 @@
         <v>9</v>
       </c>
       <c r="E170" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="G170" s="14" t="s">
+      <c r="G170" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="H170" s="11"/>
+      <c r="H170" s="14"/>
     </row>
     <row r="171" spans="3:8">
       <c r="C171" s="4">
@@ -5538,15 +5547,15 @@
         <v>9</v>
       </c>
       <c r="E171" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="G171" s="14" t="s">
+      <c r="G171" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="H171" s="11"/>
+      <c r="H171" s="14"/>
     </row>
     <row r="172" spans="3:8">
       <c r="C172" s="4">
@@ -5556,15 +5565,15 @@
         <v>9</v>
       </c>
       <c r="E172" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="G172" s="14" t="s">
+      <c r="G172" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="H172" s="11"/>
+      <c r="H172" s="14"/>
     </row>
     <row r="173" spans="3:8">
       <c r="C173" s="4">
@@ -5574,15 +5583,15 @@
         <v>9</v>
       </c>
       <c r="E173" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="G173" s="14" t="s">
+      <c r="G173" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="H173" s="11"/>
+      <c r="H173" s="14"/>
     </row>
     <row r="174" spans="3:8">
       <c r="C174" s="4">
@@ -5592,15 +5601,15 @@
         <v>9</v>
       </c>
       <c r="E174" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="G174" s="14" t="s">
+      <c r="G174" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="H174" s="11"/>
+      <c r="H174" s="14"/>
     </row>
     <row r="175" spans="3:8">
       <c r="C175" s="4">
@@ -5610,15 +5619,15 @@
         <v>9</v>
       </c>
       <c r="E175" s="6">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="G175" s="14" t="s">
+      <c r="G175" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="H175" s="11"/>
+      <c r="H175" s="14"/>
     </row>
     <row r="176" spans="3:8">
       <c r="C176" s="4">
@@ -5633,10 +5642,10 @@
       <c r="F176" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G176" s="14" t="s">
+      <c r="G176" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="H176" s="12"/>
+      <c r="H176" s="13"/>
     </row>
     <row r="177" spans="3:8">
       <c r="C177" s="4">
@@ -5651,10 +5660,10 @@
       <c r="F177" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="G177" s="14" t="s">
+      <c r="G177" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="H177" s="12"/>
+      <c r="H177" s="13"/>
     </row>
     <row r="178" spans="3:8">
       <c r="C178" s="4">
@@ -5669,10 +5678,10 @@
       <c r="F178" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="G178" s="14" t="s">
+      <c r="G178" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="H178" s="12"/>
+      <c r="H178" s="13"/>
     </row>
     <row r="179" spans="3:8">
       <c r="C179" s="4">
@@ -5687,10 +5696,10 @@
       <c r="F179" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G179" s="14" t="s">
+      <c r="G179" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="H179" s="12"/>
+      <c r="H179" s="13"/>
     </row>
     <row r="180" spans="3:8">
       <c r="C180" s="4">
@@ -5705,10 +5714,10 @@
       <c r="F180" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="G180" s="14" t="s">
+      <c r="G180" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="H180" s="12"/>
+      <c r="H180" s="13"/>
     </row>
     <row r="181" spans="3:8">
       <c r="C181" s="4">
@@ -5723,10 +5732,10 @@
       <c r="F181" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="G181" s="14" t="s">
+      <c r="G181" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="H181" s="12"/>
+      <c r="H181" s="13"/>
     </row>
     <row r="182" spans="3:8">
       <c r="C182" s="4">
@@ -5741,10 +5750,10 @@
       <c r="F182" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G182" s="14" t="s">
+      <c r="G182" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="H182" s="12"/>
+      <c r="H182" s="13"/>
     </row>
     <row r="183" spans="3:8">
       <c r="C183" s="4">
@@ -5759,10 +5768,10 @@
       <c r="F183" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G183" s="14" t="s">
+      <c r="G183" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="H183" s="12"/>
+      <c r="H183" s="13"/>
     </row>
     <row r="184" spans="3:8">
       <c r="C184" s="4">
@@ -5772,15 +5781,15 @@
         <v>9</v>
       </c>
       <c r="E184" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="G184" s="14" t="s">
+      <c r="G184" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="H184" s="7"/>
+      <c r="H184" s="13"/>
     </row>
     <row r="185" spans="3:8">
       <c r="C185" s="4">
@@ -5790,15 +5799,15 @@
         <v>9</v>
       </c>
       <c r="E185" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F185" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="G185" s="14" t="s">
+      <c r="G185" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="H185" s="7"/>
+      <c r="H185" s="13"/>
     </row>
     <row r="186" spans="3:8">
       <c r="C186" s="4">
@@ -5808,15 +5817,15 @@
         <v>9</v>
       </c>
       <c r="E186" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="G186" s="14" t="s">
+      <c r="G186" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="H186" s="7"/>
+      <c r="H186" s="13"/>
     </row>
     <row r="187" spans="3:8">
       <c r="C187" s="4">
@@ -5826,15 +5835,15 @@
         <v>9</v>
       </c>
       <c r="E187" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F187" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="G187" s="14" t="s">
+      <c r="G187" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="H187" s="7"/>
+      <c r="H187" s="13"/>
     </row>
     <row r="188" spans="3:8">
       <c r="C188" s="4">
@@ -5844,15 +5853,15 @@
         <v>9</v>
       </c>
       <c r="E188" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G188" s="14" t="s">
+      <c r="G188" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="H188" s="7"/>
+      <c r="H188" s="13"/>
     </row>
     <row r="189" spans="3:8">
       <c r="C189" s="4">
@@ -5862,7 +5871,7 @@
         <v>9</v>
       </c>
       <c r="E189" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F189" s="6" t="s">
         <v>363</v>
@@ -5870,7 +5879,7 @@
       <c r="G189" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="H189" s="7"/>
+      <c r="H189" s="13"/>
     </row>
     <row r="190" spans="3:8">
       <c r="C190" s="4">
@@ -5880,7 +5889,7 @@
         <v>9</v>
       </c>
       <c r="E190" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>365</v>
@@ -5888,7 +5897,7 @@
       <c r="G190" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="H190" s="8"/>
+      <c r="H190" s="17"/>
     </row>
     <row r="191" spans="3:8">
       <c r="C191" s="4">
@@ -5898,15 +5907,15 @@
         <v>9</v>
       </c>
       <c r="E191" s="6">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G191" s="14" t="s">
+      <c r="G191" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="H191" s="8"/>
+      <c r="H191" s="17"/>
     </row>
     <row r="192" spans="3:8">
       <c r="C192" s="4">
@@ -5924,7 +5933,7 @@
       <c r="G192" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="H192" s="17"/>
+      <c r="H192" s="18"/>
     </row>
     <row r="193" spans="1:9">
       <c r="C193" s="4">
@@ -5942,7 +5951,7 @@
       <c r="G193" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="H193" s="17"/>
+      <c r="H193" s="18"/>
     </row>
     <row r="194" spans="1:9">
       <c r="C194" s="4">
@@ -5960,7 +5969,7 @@
       <c r="G194" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="H194" s="11"/>
+      <c r="H194" s="10"/>
     </row>
     <row r="195" spans="1:9">
       <c r="C195" s="4">
@@ -5978,7 +5987,7 @@
       <c r="G195" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="H195" s="11"/>
+      <c r="H195" s="10"/>
     </row>
     <row r="196" spans="1:9">
       <c r="C196" s="4">
@@ -5996,7 +6005,7 @@
       <c r="G196" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="H196" s="11"/>
+      <c r="H196" s="10"/>
     </row>
     <row r="197" spans="1:9">
       <c r="C197" s="4">
@@ -6014,7 +6023,7 @@
       <c r="G197" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="H197" s="11"/>
+      <c r="H197" s="10"/>
     </row>
     <row r="198" spans="1:9">
       <c r="C198" s="4">
@@ -6032,7 +6041,7 @@
       <c r="G198" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="H198" s="11"/>
+      <c r="H198" s="10"/>
     </row>
     <row r="199" spans="1:9">
       <c r="C199" s="4">
@@ -6050,7 +6059,7 @@
       <c r="G199" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="H199" s="11"/>
+      <c r="H199" s="10"/>
     </row>
     <row r="200" spans="1:9">
       <c r="C200" s="4">
@@ -6068,7 +6077,7 @@
       <c r="G200" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="H200" s="12"/>
+      <c r="H200" s="19"/>
     </row>
     <row r="201" spans="1:9">
       <c r="C201" s="4">
@@ -6086,7 +6095,7 @@
       <c r="G201" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="H201" s="12"/>
+      <c r="H201" s="19"/>
     </row>
     <row r="202" spans="1:9">
       <c r="C202" s="4">
@@ -6104,7 +6113,7 @@
       <c r="G202" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="H202" s="12"/>
+      <c r="H202" s="19"/>
     </row>
     <row r="203" spans="1:9">
       <c r="C203" s="4">
@@ -6122,7 +6131,7 @@
       <c r="G203" s="16" t="s">
         <v>392</v>
       </c>
-      <c r="H203" s="12"/>
+      <c r="H203" s="19"/>
     </row>
     <row r="204" spans="1:9">
       <c r="C204" s="4">
@@ -6132,7 +6141,7 @@
         <v>9</v>
       </c>
       <c r="E204" s="6">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>393</v>
@@ -6140,19 +6149,19 @@
       <c r="G204" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="H204" s="11"/>
+      <c r="H204" s="19"/>
     </row>
     <row r="205" s="2" customFormat="1" spans="1:9">
-      <c r="C205" s="18">
+      <c r="C205" s="20">
         <v>202</v>
       </c>
-      <c r="D205" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E205" s="19">
+      <c r="D205" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="21">
         <v>202</v>
       </c>
-      <c r="F205" s="19" t="s">
+      <c r="F205" s="21" t="s">
         <v>395</v>
       </c>
       <c r="G205" s="2" t="s">
@@ -6161,16 +6170,16 @@
       <c r="I205" s="8"/>
     </row>
     <row r="206" s="2" customFormat="1" spans="1:9">
-      <c r="C206" s="18">
+      <c r="C206" s="20">
         <v>203</v>
       </c>
-      <c r="D206" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" s="19">
+      <c r="D206" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="21">
         <v>203</v>
       </c>
-      <c r="F206" s="19" t="s">
+      <c r="F206" s="21" t="s">
         <v>397</v>
       </c>
       <c r="G206" s="2" t="s">
@@ -6189,7 +6198,7 @@
         <v>9</v>
       </c>
       <c r="E207" s="6">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>400</v>
@@ -6197,7 +6206,7 @@
       <c r="G207" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="H207" s="20"/>
+      <c r="H207" s="22"/>
     </row>
     <row r="208" spans="1:9">
       <c r="C208" s="4">
@@ -6207,7 +6216,7 @@
         <v>9</v>
       </c>
       <c r="E208" s="6">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>402</v>
@@ -6215,7 +6224,7 @@
       <c r="G208" s="16" t="s">
         <v>403</v>
       </c>
-      <c r="H208" s="20"/>
+      <c r="H208" s="22"/>
     </row>
     <row r="209" spans="3:8">
       <c r="C209" s="4">
@@ -6225,7 +6234,7 @@
         <v>9</v>
       </c>
       <c r="E209" s="6">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F209" s="6" t="s">
         <v>404</v>
@@ -6233,7 +6242,7 @@
       <c r="G209" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="H209" s="20"/>
+      <c r="H209" s="22"/>
     </row>
     <row r="210" spans="3:8">
       <c r="C210" s="4">
@@ -6251,7 +6260,7 @@
       <c r="G210" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="H210" s="21"/>
+      <c r="H210" s="23"/>
     </row>
     <row r="211" spans="3:8">
       <c r="C211" s="4">
@@ -6269,7 +6278,7 @@
       <c r="G211" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="H211" s="21"/>
+      <c r="H211" s="23"/>
     </row>
     <row r="212" spans="3:8">
       <c r="C212" s="4">
@@ -6279,15 +6288,15 @@
         <v>9</v>
       </c>
       <c r="E212" s="6">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="G212" s="14" t="s">
+      <c r="G212" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="H212" s="20"/>
+      <c r="H212" s="23"/>
     </row>
     <row r="213" spans="3:8">
       <c r="C213" s="4">
@@ -6297,7 +6306,7 @@
         <v>9</v>
       </c>
       <c r="E213" s="6">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F213" s="6" t="s">
         <v>412</v>
@@ -6323,7 +6332,7 @@
       <c r="G214" s="16" t="s">
         <v>415</v>
       </c>
-      <c r="H214" s="12"/>
+      <c r="H214" s="13"/>
     </row>
     <row r="215" spans="3:8">
       <c r="C215" s="4">
@@ -6338,10 +6347,10 @@
       <c r="F215" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="G215" s="14" t="s">
+      <c r="G215" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="H215" s="12"/>
+      <c r="H215" s="13"/>
     </row>
     <row r="216" spans="3:8">
       <c r="C216" s="4">
@@ -6351,15 +6360,15 @@
         <v>9</v>
       </c>
       <c r="E216" s="6">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="G216" s="14" t="s">
+      <c r="G216" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="H216" s="11"/>
+      <c r="H216" s="13"/>
     </row>
     <row r="217" spans="3:8">
       <c r="C217" s="4">
@@ -6369,7 +6378,7 @@
         <v>9</v>
       </c>
       <c r="E217" s="6">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F217" s="6" t="s">
         <v>420</v>
@@ -6377,7 +6386,7 @@
       <c r="G217" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H217" s="11"/>
+      <c r="H217" s="13"/>
     </row>
     <row r="218" spans="3:8">
       <c r="C218" s="4">
@@ -6395,7 +6404,7 @@
       <c r="G218" s="16" t="s">
         <v>422</v>
       </c>
-      <c r="H218" s="12"/>
+      <c r="H218" s="13"/>
     </row>
     <row r="219" spans="3:8">
       <c r="C219" s="4">
@@ -6410,10 +6419,10 @@
       <c r="F219" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="G219" s="14" t="s">
+      <c r="G219" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="H219" s="12"/>
+      <c r="H219" s="13"/>
     </row>
     <row r="220" spans="3:8">
       <c r="C220" s="4">
@@ -6428,9 +6437,10 @@
       <c r="F220" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="G220" s="14" t="s">
+      <c r="G220" s="12" t="s">
         <v>426</v>
       </c>
+      <c r="H220" s="24"/>
     </row>
     <row r="221" spans="3:8">
       <c r="C221" s="4">
@@ -6440,7 +6450,7 @@
         <v>9</v>
       </c>
       <c r="E221" s="6">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F221" s="6" t="s">
         <v>427</v>
@@ -6448,6 +6458,7 @@
       <c r="G221" s="16" t="s">
         <v>428</v>
       </c>
+      <c r="H221" s="24"/>
     </row>
     <row r="222" spans="3:8">
       <c r="C222" s="4">
@@ -6462,9 +6473,10 @@
       <c r="F222" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="G222" s="14" t="s">
+      <c r="G222" s="12" t="s">
         <v>430</v>
       </c>
+      <c r="H222" s="13"/>
     </row>
     <row r="223" spans="3:8">
       <c r="C223" s="4">
@@ -6474,7 +6486,7 @@
         <v>9</v>
       </c>
       <c r="E223" s="6">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F223" s="6" t="s">
         <v>431</v>
@@ -6482,6 +6494,7 @@
       <c r="G223" s="16" t="s">
         <v>432</v>
       </c>
+      <c r="H223" s="13"/>
     </row>
     <row r="224" spans="3:8">
       <c r="C224" s="4">
@@ -6499,8 +6512,9 @@
       <c r="G224" s="16" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="225" spans="3:7">
+      <c r="H224" s="10"/>
+    </row>
+    <row r="225" spans="3:8">
       <c r="C225" s="4">
         <v>229</v>
       </c>
@@ -6508,16 +6522,17 @@
         <v>9</v>
       </c>
       <c r="E225" s="6">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F225" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="G225" s="14" t="s">
+      <c r="G225" s="12" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="226" spans="3:7">
+      <c r="H225" s="10"/>
+    </row>
+    <row r="226" spans="3:8">
       <c r="C226" s="4">
         <v>230</v>
       </c>
@@ -6530,11 +6545,12 @@
       <c r="F226" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="G226" s="14" t="s">
+      <c r="G226" s="12" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="227" spans="3:7">
+      <c r="H226" s="17"/>
+    </row>
+    <row r="227" spans="3:8">
       <c r="C227" s="4">
         <v>231</v>
       </c>
@@ -6542,16 +6558,17 @@
         <v>9</v>
       </c>
       <c r="E227" s="6">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F227" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="G227" s="14" t="s">
+      <c r="G227" s="12" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="228" spans="3:7">
+      <c r="H227" s="17"/>
+    </row>
+    <row r="228" spans="3:8">
       <c r="C228" s="4">
         <v>232</v>
       </c>
@@ -6568,7 +6585,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="229" spans="3:7">
+    <row r="229" spans="3:8">
       <c r="C229" s="4">
         <v>233</v>
       </c>
@@ -6581,11 +6598,11 @@
       <c r="F229" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="G229" s="14" t="s">
+      <c r="G229" s="12" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="230" spans="3:7">
+    <row r="230" spans="3:8">
       <c r="C230" s="4">
         <v>234</v>
       </c>
@@ -6598,11 +6615,11 @@
       <c r="F230" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="G230" s="14" t="s">
+      <c r="G230" s="12" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="231" spans="3:7">
+    <row r="231" spans="3:8">
       <c r="C231" s="4">
         <v>235</v>
       </c>
@@ -6615,7 +6632,7 @@
       <c r="F231" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="G231" s="14"/>
+      <c r="G231" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
